--- a/docs/kiem_thu/KET_QUA_KIEM_THU.xlsx
+++ b/docs/kiem_thu/KET_QUA_KIEM_THU.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -484,14 +484,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Thời điểm chạy: 16/10/2026 05:55 · Python 3.11.15 · CSDL: kiểm thử dựng lại assessment_db</t>
+          <t>Thời điểm chạy: 17/10/2026 11:03 · Python 3.11.15 · CSDL: kiểm thử dựng lại assessment_db</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Ca kiểm thử tự động: 92/92 đạt · Độ phủ API: 126/126 endpoint được gọi thành công</t>
+          <t>Ca kiểm thử tự động: 99/99 đạt · Độ phủ API: 133/133 endpoint được gọi thành công</t>
         </is>
       </c>
     </row>
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>0</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0</v>
@@ -777,14 +777,14 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>TỔNG</t>
+          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>92</v>
+        <v>4</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>92</v>
+        <v>4</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>0</v>
@@ -795,8 +795,29 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>TỔNG</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Kiểm thử bổ sung (ngoài pytest): tools/moodle_e2e/run_real_moodle_e2e.py (Moodle 4.5 thật), tools/moodle_e2e/kiem_tra_dong_bo_cau_hoi.py, tools/kiem_tra_do_luong.py (tính lại độc lập các độ đo), tools/omr/kiem_tra_omr.py (độ bền chấm phiếu), backend/tests/ui_screens.py (duyệt giao diện).</t>
         </is>
@@ -813,7 +834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -904,7 +925,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>17.18</v>
+        <v>33.01</v>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
@@ -943,7 +964,7 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
@@ -982,7 +1003,7 @@
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
@@ -1021,7 +1042,7 @@
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -1060,7 +1081,7 @@
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -1099,7 +1120,7 @@
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -1216,7 +1237,7 @@
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
@@ -1294,7 +1315,7 @@
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
@@ -1333,7 +1354,7 @@
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
@@ -1372,7 +1393,7 @@
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.3</v>
+        <v>0.52</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
@@ -1411,7 +1432,7 @@
         </is>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -1450,7 +1471,7 @@
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
@@ -1489,7 +1510,7 @@
         </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -1528,7 +1549,7 @@
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
@@ -1567,7 +1588,7 @@
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -1801,7 +1822,7 @@
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.42</v>
+        <v>0.59</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -1840,7 +1861,7 @@
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
@@ -1879,7 +1900,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -1918,7 +1939,7 @@
         </is>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
@@ -1996,7 +2017,7 @@
         </is>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
@@ -2191,7 +2212,7 @@
         </is>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
@@ -2211,17 +2232,17 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Dùng đề cho lớp khác, sửa câu/ý, sinh lại mã đề</t>
+          <t>Tạo bài kiểm tra ở trang môn học (đề của môn)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Sao chép đề sang lớp 02; sửa câu/ý bài nhập điểm; xóa mã đề chưa chấm</t>
+          <t>Sinh đề theo ma trận cấp môn rồi lưu đề chưa gắn lớp; gọi tạo Quiz, đồng bộ, thống kê; GV khác; gửi cả lớp và môn</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Đủ câu; GV khác 403; cấu trúc mới đúng</t>
+          <t>Đề lưu ở môn; thao tác cần lớp 409 kèm hướng dẫn chọn lớp; Moodle XML được; GV khác 403; 422</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -2230,11 +2251,11 @@
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.29</v>
+        <v>0.35</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>test_z_toan_bo_chuc_nang::test_copy_exam_manual_items_and_paper_versions</t>
+          <t>test_de_cua_mon::test_course_exam_create_and_blocked_actions</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr"/>
@@ -2245,22 +2266,22 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>5. Đồng bộ Moodle, giải xáo trộn, phân tích</t>
+          <t>4. Đề thi: ma trận đề, Moodle XML, đề giấy</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ bài làm khớp điểm Moodle</t>
+          <t>Giao đề của môn cho lớp HP khi xuất</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ Quiz từ CSDL Moodle mô phỏng</t>
+          <t>Giao đề giấy cho 2 lớp, sinh mã đề ở bài của lớp, giao lại lớp đã có, xóa đề của môn</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Tổng điểm từng SV = sumgrades của Moodle</t>
+          <t>Mỗi lớp một bài cùng câu hỏi; không tạo trùng; xóa đề gốc không mất bài của lớp</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -2269,11 +2290,11 @@
         </is>
       </c>
       <c r="G37" s="4" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_moodle_sync_matches_moodle_grades</t>
+          <t>test_de_cua_mon::test_course_exam_deploy_to_sections</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr"/>
@@ -2284,22 +2305,22 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>5. Đồng bộ Moodle, giải xáo trộn, phân tích</t>
+          <t>4. Đề thi: ma trận đề, Moodle XML, đề giấy</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Chọn lượt theo cách tính điểm của Quiz</t>
+          <t>Dùng đề cho lớp khác, sửa câu/ý, sinh lại mã đề</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Quiz cho nhiều lượt: lượt cuối / lượt đầu / điểm cao nhất; lượt xem trước của GV</t>
+          <t>Sao chép đề sang lớp 02; sửa câu/ý bài nhập điểm; xóa mã đề chưa chấm</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Đúng lượt Moodle dùng tính điểm; bỏ lượt xem trước</t>
+          <t>Đủ câu; GV khác 403; cấu trúc mới đúng</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -2308,11 +2329,11 @@
         </is>
       </c>
       <c r="G38" s="4" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_moodle_sync_follows_grade_method_and_skips_preview</t>
+          <t>test_z_toan_bo_chuc_nang::test_copy_exam_manual_items_and_paper_versions</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr"/>
@@ -2328,17 +2349,17 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Ghi nhận SV vắng thi</t>
+          <t>Đồng bộ bài làm khớp điểm Moodle</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>SV ghi danh nhưng không làm bài</t>
+          <t>Đồng bộ Quiz từ CSDL Moodle mô phỏng</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Lượt absent, không tính vào p/DI</t>
+          <t>Tổng điểm từng SV = sumgrades của Moodle</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -2351,7 +2372,7 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_absent_students_recorded</t>
+          <t>test_api::test_moodle_sync_matches_moodle_grades</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr"/>
@@ -2367,17 +2388,17 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ lại không trùng lặp</t>
+          <t>Chọn lượt theo cách tính điểm của Quiz</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ 2 lần liên tiếp</t>
+          <t>Quiz cho nhiều lượt: lượt cuối / lượt đầu / điểm cao nhất; lượt xem trước của GV</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Số lượt, kết quả không đổi</t>
+          <t>Đúng lượt Moodle dùng tính điểm; bỏ lượt xem trước</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -2386,11 +2407,11 @@
         </is>
       </c>
       <c r="G40" s="4" t="n">
-        <v>5.92</v>
+        <v>0</v>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_resync_is_idempotent</t>
+          <t>test_api::test_moodle_sync_follows_grade_method_and_skips_preview</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr"/>
@@ -2406,17 +2427,17 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Cảnh báo cách tính 'trung bình các lượt'</t>
+          <t>Ghi nhận SV vắng thi</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Quiz đặt grademethod = trung bình</t>
+          <t>SV ghi danh nhưng không làm bài</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ lượt cuối kèm cảnh báo</t>
+          <t>Lượt absent, không tính vào p/DI</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -2425,11 +2446,11 @@
         </is>
       </c>
       <c r="G41" s="4" t="n">
-        <v>11.92</v>
+        <v>0</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_sync_warns_average_grade_method</t>
+          <t>test_api::test_absent_students_recorded</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr"/>
@@ -2445,17 +2466,17 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Phát hiện câu bị sửa trên Moodle</t>
+          <t>Đồng bộ lại không trùng lặp</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Đổi số phương án/đáp án trên Moodle rồi đồng bộ</t>
+          <t>Đồng bộ 2 lần liên tiếp</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>409, không ghi kết quả sai</t>
+          <t>Số lượt, kết quả không đổi</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -2464,11 +2485,11 @@
         </is>
       </c>
       <c r="G42" s="4" t="n">
-        <v>9.24</v>
+        <v>14.15</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_sync_stops_when_question_edited_on_moodle</t>
+          <t>test_api::test_resync_is_idempotent</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr"/>
@@ -2484,17 +2505,17 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ bài giấy từ Offline Quiz</t>
+          <t>Cảnh báo cách tính 'trung bình các lượt'</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Kéo kết quả phiếu Moodle đã chấm</t>
+          <t>Quiz đặt grademethod = trung bình</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Đủ bài làm, đúng điểm</t>
+          <t>Đồng bộ lượt cuối kèm cảnh báo</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -2503,11 +2524,11 @@
         </is>
       </c>
       <c r="G43" s="4" t="n">
-        <v>0</v>
+        <v>30.51</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_paper_sync_reads_moodle_offlinequiz</t>
+          <t>test_api::test_sync_warns_average_grade_method</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr"/>
@@ -2523,17 +2544,17 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Ánh xạ nhóm đề A/B sang mã đề</t>
+          <t>Phát hiện câu bị sửa trên Moodle</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ bài giấy 2 nhóm đề</t>
+          <t>Đổi số phương án/đáp án trên Moodle rồi đồng bộ</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Mỗi lượt gắn đúng nhóm đề</t>
+          <t>409, không ghi kết quả sai</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -2542,11 +2563,11 @@
         </is>
       </c>
       <c r="G44" s="4" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_paper_sync_maps_groups_to_versions</t>
+          <t>test_api::test_sync_stops_when_question_edited_on_moodle</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr"/>
@@ -2562,17 +2583,17 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Giải xáo trộn theo từng nhóm đề</t>
+          <t>Đồng bộ bài giấy từ Offline Quiz</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Phương án bị xáo khác nhau giữa nhóm A, B</t>
+          <t>Kéo kết quả phiếu Moodle đã chấm</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Lựa chọn quy về đúng phương án gốc</t>
+          <t>Đủ bài làm, đúng điểm</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -2581,11 +2602,11 @@
         </is>
       </c>
       <c r="G45" s="4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_paper_reverse_shuffle_per_group</t>
+          <t>test_api::test_paper_sync_reads_moodle_offlinequiz</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr"/>
@@ -2601,17 +2622,17 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Bài giấy chưa có Offline Quiz</t>
+          <t>Ánh xạ nhóm đề A/B sang mã đề</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ bài giấy chưa liên kết</t>
+          <t>Đồng bộ bài giấy 2 nhóm đề</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>422/409 kèm hướng dẫn</t>
+          <t>Mỗi lượt gắn đúng nhóm đề</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -2620,11 +2641,11 @@
         </is>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_paper_sync_requires_offlinequiz</t>
+          <t>test_api::test_paper_sync_maps_groups_to_versions</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr"/>
@@ -2640,17 +2661,17 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ lại bài giấy</t>
+          <t>Giải xáo trộn theo từng nhóm đề</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ bài giấy 2 lần</t>
+          <t>Phương án bị xáo khác nhau giữa nhóm A, B</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Không trùng lặp</t>
+          <t>Lựa chọn quy về đúng phương án gốc</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -2659,11 +2680,11 @@
         </is>
       </c>
       <c r="G47" s="4" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_paper_resync_is_idempotent</t>
+          <t>test_api::test_paper_reverse_shuffle_per_group</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr"/>
@@ -2679,17 +2700,17 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Phân tích lại, nhật ký, trạng thái và cài cầu nối</t>
+          <t>Bài giấy chưa có Offline Quiz</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Phân tích lại bài, xem nhật ký, trạng thái CSDL Moodle, cài lại cầu nối, minh chứng CLO</t>
+          <t>Đồng bộ bài giấy chưa liên kết</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Đúng; GV không cài cầu nối</t>
+          <t>422/409 kèm hướng dẫn</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -2698,11 +2719,11 @@
         </is>
       </c>
       <c r="G48" s="4" t="n">
-        <v>0.37</v>
+        <v>0.04</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>test_z_toan_bo_chuc_nang::test_sync_analyze_runs_and_bridge</t>
+          <t>test_api::test_paper_sync_requires_offlinequiz</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr"/>
@@ -2713,22 +2734,22 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>6. Analysis Engine (p, DI, KR-20, CLO, BM6)</t>
+          <t>5. Đồng bộ Moodle, giải xáo trộn, phân tích</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Phát hiện câu hỏi lỗi (DI âm)</t>
+          <t>Đồng bộ lại bài giấy</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Phân tích bài có câu bẫy</t>
+          <t>Đồng bộ bài giấy 2 lần</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Câu 24 DI âm, phân loại 'Loại bỏ/xem lại'</t>
+          <t>Không trùng lặp</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -2737,11 +2758,11 @@
         </is>
       </c>
       <c r="G49" s="4" t="n">
-        <v>0.06</v>
+        <v>7.85</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_item_stats_flags_trap_question</t>
+          <t>test_api::test_paper_resync_is_idempotent</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr"/>
@@ -2752,22 +2773,22 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>6. Analysis Engine (p, DI, KR-20, CLO, BM6)</t>
+          <t>5. Đồng bộ Moodle, giải xáo trộn, phân tích</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Kết quả CLO lớp HP (BM6b)</t>
+          <t>Phân tích lại, nhật ký, trạng thái và cài cầu nối</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Tính số SV đạt/đánh giá từng CLO</t>
+          <t>Phân tích lại bài, xem nhật ký, trạng thái CSDL Moodle, cài lại cầu nối, minh chứng CLO</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Khớp số liệu tính tay; kết luận Đạt/Không đạt</t>
+          <t>Đúng; GV không cài cầu nối</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -2776,11 +2797,11 @@
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>0.01</v>
+        <v>0.48</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_clo_results_bm6b</t>
+          <t>test_z_toan_bo_chuc_nang::test_sync_analyze_runs_and_bridge</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr"/>
@@ -2796,17 +2817,17 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Mức đạt CLO một bài (BM6c)</t>
+          <t>Phát hiện câu hỏi lỗi (DI âm)</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Số liệu mẫu của biểu mẫu</t>
+          <t>Phân tích bài có câu bẫy</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Khớp BM6c mẫu</t>
+          <t>Câu 24 DI âm, phân loại 'Loại bỏ/xem lại'</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
@@ -2815,11 +2836,11 @@
         </is>
       </c>
       <c r="G51" s="4" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>test_engine::test_bm6c_single_test</t>
+          <t>test_api::test_item_stats_flags_trap_question</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr"/>
@@ -2835,17 +2856,17 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>SV 0 điểm vẫn tính vào mẫu số</t>
+          <t>Kết quả CLO lớp HP (BM6b)</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>SV làm bài được 0 điểm</t>
+          <t>Tính số SV đạt/đánh giá từng CLO</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Có trong số SV đánh giá</t>
+          <t>Khớp số liệu tính tay; kết luận Đạt/Không đạt</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -2854,11 +2875,11 @@
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>test_engine::test_bm6d_zero_score_stays_in_denominator</t>
+          <t>test_api::test_clo_results_bm6b</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr"/>
@@ -2874,17 +2895,17 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Cộng dồn nhiều bài (BM6d)</t>
+          <t>Mức đạt CLO một bài (BM6c)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>CLO đo bởi 2 bài</t>
+          <t>Số liệu mẫu của biểu mẫu</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Cộng dồn lượt đánh giá đúng biểu mẫu</t>
+          <t>Khớp BM6c mẫu</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
@@ -2893,11 +2914,11 @@
         </is>
       </c>
       <c r="G53" s="4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>test_engine::test_bm6d_multi_test_aggregation</t>
+          <t>test_engine::test_bm6c_single_test</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr"/>
@@ -2913,17 +2934,17 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Ngưỡng đạt so sánh ≥</t>
+          <t>SV 0 điểm vẫn tính vào mẫu số</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Điểm đúng bằng ngưỡng</t>
+          <t>SV làm bài được 0 điểm</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Tính là Đạt</t>
+          <t>Có trong số SV đánh giá</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -2932,11 +2953,11 @@
         </is>
       </c>
       <c r="G54" s="4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>test_engine::test_threshold_boundary_is_inclusive</t>
+          <t>test_engine::test_bm6d_zero_score_stays_in_denominator</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr"/>
@@ -2952,17 +2973,17 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Điểm CLO có trọng số</t>
+          <t>Cộng dồn nhiều bài (BM6d)</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Câu đo 2 CLO trọng số 0,5</t>
+          <t>CLO đo bởi 2 bài</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Công thức (3.1) đúng</t>
+          <t>Cộng dồn lượt đánh giá đúng biểu mẫu</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
@@ -2971,11 +2992,11 @@
         </is>
       </c>
       <c r="G55" s="4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>test_engine::test_weighted_clo_score</t>
+          <t>test_engine::test_bm6d_multi_test_aggregation</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr"/>
@@ -2991,17 +3012,17 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Độ khó p và độ phân biệt DI (27%)</t>
+          <t>Ngưỡng đạt so sánh ≥</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Dữ liệu mẫu</t>
+          <t>Điểm đúng bằng ngưỡng</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Khớp tính tay</t>
+          <t>Tính là Đạt</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
@@ -3014,7 +3035,7 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>test_engine::test_p_and_di_kelley</t>
+          <t>test_engine::test_threshold_boundary_is_inclusive</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr"/>
@@ -3030,17 +3051,17 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Bỏ trống tính là sai</t>
+          <t>Điểm CLO có trọng số</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Câu bỏ trống</t>
+          <t>Câu đo 2 CLO trọng số 0,5</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>is_correct = 0</t>
+          <t>Công thức (3.1) đúng</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -3049,11 +3070,11 @@
         </is>
       </c>
       <c r="G57" s="4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>test_engine::test_blank_counts_as_wrong</t>
+          <t>test_engine::test_weighted_clo_score</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr"/>
@@ -3069,17 +3090,17 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Lộ trình ôn tập cá nhân</t>
+          <t>Độ khó p và độ phân biệt DI (27%)</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>SV chưa đạt nhiều CLO</t>
+          <t>Dữ liệu mẫu</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Sắp theo thiếu hụt, chọn đúng chương mất điểm</t>
+          <t>Khớp tính tay</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
@@ -3088,11 +3109,11 @@
         </is>
       </c>
       <c r="G58" s="4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>test_engine::test_learning_path_priorities</t>
+          <t>test_engine::test_p_and_di_kelley</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr"/>
@@ -3108,17 +3129,17 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Dữ liệu rỗng</t>
+          <t>Bỏ trống tính là sai</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Bài không có lượt làm</t>
+          <t>Câu bỏ trống</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Không lỗi, trả rỗng</t>
+          <t>is_correct = 0</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
@@ -3127,11 +3148,11 @@
         </is>
       </c>
       <c r="G59" s="4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>test_engine::test_empty_inputs</t>
+          <t>test_engine::test_blank_counts_as_wrong</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr"/>
@@ -3147,17 +3168,17 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Độ tin cậy KR-20</t>
+          <t>Lộ trình ôn tập cá nhân</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Ma trận đúng/sai mẫu</t>
+          <t>SV chưa đạt nhiều CLO</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Khớp công thức (1.3)</t>
+          <t>Sắp theo thiếu hụt, chọn đúng chương mất điểm</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
@@ -3170,7 +3191,7 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>test_engine::test_kr20_reliability</t>
+          <t>test_engine::test_learning_path_priorities</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr"/>
@@ -3186,17 +3207,17 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Đổi ngưỡng đạt → phân tích lại</t>
+          <t>Dữ liệu rỗng</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Sửa kế hoạch CLO (BM6a)</t>
+          <t>Bài không có lượt làm</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Kết quả CLO tính lại ngay</t>
+          <t>Không lỗi, trả rỗng</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
@@ -3205,11 +3226,11 @@
         </is>
       </c>
       <c r="G61" s="4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>test_hardening::test_clo_plan_change_reanalyzes</t>
+          <t>test_engine::test_empty_inputs</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr"/>
@@ -3220,22 +3241,22 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>7. Báo cáo biểu mẫu BM2, BM3, BM6, phân công</t>
+          <t>6. Analysis Engine (p, DI, KR-20, CLO, BM6)</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Nhận xét, cải tiến CLO</t>
+          <t>Độ tin cậy KR-20</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Lưu nhận xét BM6a</t>
+          <t>Ma trận đúng/sai mẫu</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Lưu và đọc lại đúng</t>
+          <t>Khớp công thức (1.3)</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
@@ -3248,7 +3269,7 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_clo_narrative</t>
+          <t>test_engine::test_kr20_reliability</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr"/>
@@ -3259,22 +3280,22 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>7. Báo cáo biểu mẫu BM2, BM3, BM6, phân công</t>
+          <t>6. Analysis Engine (p, DI, KR-20, CLO, BM6)</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Tổng hợp PLO = cộng dồn PI (BM3c)</t>
+          <t>Đổi ngưỡng đạt → phân tích lại</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Tổng hợp PLO năm học 2024–2025</t>
+          <t>Sửa kế hoạch CLO (BM6a)</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Số đạt/đánh giá PLO = Σ PI</t>
+          <t>Kết quả CLO tính lại ngay</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
@@ -3283,11 +3304,11 @@
         </is>
       </c>
       <c r="G63" s="4" t="n">
-        <v>0.03</v>
+        <v>1.88</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_plo_summary_is_sum_of_pi</t>
+          <t>test_hardening::test_clo_plan_change_reanalyzes</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr"/>
@@ -3303,17 +3324,17 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Xuất bộ Biểu mẫu 6 (.xlsx)</t>
+          <t>Nhận xét, cải tiến CLO</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Tải BM6 của lớp HP</t>
+          <t>Lưu nhận xét BM6a</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Mục lục, BM6a, BM6b, minh chứng; công thức COUNTIF</t>
+          <t>Lưu và đọc lại đúng</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
@@ -3322,11 +3343,11 @@
         </is>
       </c>
       <c r="G64" s="4" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_bm6_workbook</t>
+          <t>test_api::test_clo_narrative</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr"/>
@@ -3342,17 +3363,17 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Minh chứng theo kế hoạch BM6a</t>
+          <t>Tổng hợp PLO = cộng dồn PI (BM3c)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Trang minh chứng từng CLO</t>
+          <t>Tổng hợp PLO năm học 2024–2025</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Chỉ lấy bài đúng loại minh chứng; tổng khớp BM6b</t>
+          <t>Số đạt/đánh giá PLO = Σ PI</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
@@ -3361,11 +3382,11 @@
         </is>
       </c>
       <c r="G65" s="4" t="n">
-        <v>0.14</v>
+        <v>0.03</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_bm6_evidence_follows_plan_and_matches_bm6b</t>
+          <t>test_api::test_plo_summary_is_sum_of_pi</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr"/>
@@ -3381,17 +3402,17 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>BM6c riêng từng bài KT</t>
+          <t>Xuất bộ Biểu mẫu 6 (.xlsx)</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Xuất BM6c bài quá trình, cuối kỳ; GV khác; bài chưa phân tích</t>
+          <t>Tải BM6 của lớp HP</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Đúng; 403; 409</t>
+          <t>Mục lục, BM6a, BM6b, minh chứng; công thức COUNTIF</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
@@ -3400,11 +3421,11 @@
         </is>
       </c>
       <c r="G66" s="4" t="n">
-        <v>0.26</v>
+        <v>0.14</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_bm6c_per_exam</t>
+          <t>test_api::test_bm6_workbook</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr"/>
@@ -3420,17 +3441,17 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Xuất BM2/BM3 (.xlsx)</t>
+          <t>Minh chứng theo kế hoạch BM6a</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Tải tệp tổng hợp CTĐT</t>
+          <t>Trang minh chứng từng CLO</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Có BM2a, BM2b, BM3b, BM3c; GV bị 403</t>
+          <t>Chỉ lấy bài đúng loại minh chứng; tổng khớp BM6b</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
@@ -3443,7 +3464,7 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_bm3_workbook</t>
+          <t>test_api::test_bm6_evidence_follows_plan_and_matches_bm6b</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr"/>
@@ -3459,17 +3480,17 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Xuất BM2 dạng Word</t>
+          <t>BM6c riêng từng bài KT</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Tải BM2 .docx</t>
+          <t>Xuất BM6c bài quá trình, cuối kỳ; GV khác; bài chưa phân tích</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Có KẾ HOẠCH và BÁO CÁO TỔNG KẾT</t>
+          <t>Đúng; 403; 409</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
@@ -3478,11 +3499,11 @@
         </is>
       </c>
       <c r="G68" s="4" t="n">
-        <v>1.1</v>
+        <v>0.23</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_bm2_docx</t>
+          <t>test_api::test_bm6c_per_exam</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr"/>
@@ -3498,17 +3519,17 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Bảng phân công đánh giá PIs</t>
+          <t>Xuất BM2/BM3 (.xlsx)</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Xuất bảng phân công học kỳ</t>
+          <t>Tải tệp tổng hợp CTĐT</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Đúng cột như bảng gốc; 404 học kỳ không tồn tại</t>
+          <t>Có BM2a, BM2b, BM3b, BM3c; GV bị 403</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
@@ -3517,11 +3538,11 @@
         </is>
       </c>
       <c r="G69" s="4" t="n">
-        <v>0.04</v>
+        <v>0.24</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_assignments_xlsx</t>
+          <t>test_api::test_bm3_workbook</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr"/>
@@ -3537,17 +3558,17 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Nhận xét PLO (BM3b)</t>
+          <t>Xuất BM2 dạng Word</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Lưu 4 mục nhận xét PLO</t>
+          <t>Tải BM2 .docx</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Lưu đúng; GV bị 403</t>
+          <t>Có KẾ HOẠCH và BÁO CÁO TỔNG KẾT</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
@@ -3556,11 +3577,11 @@
         </is>
       </c>
       <c r="G70" s="4" t="n">
-        <v>0.01</v>
+        <v>0.91</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_plo_narrative</t>
+          <t>test_api::test_bm2_docx</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr"/>
@@ -3571,22 +3592,22 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>8. Nhập điểm, gộp bài, phụ đạo</t>
+          <t>7. Báo cáo biểu mẫu BM2, BM3, BM6, phân công</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Bài nhập điểm: bảng điểm, Excel, phân tích</t>
+          <t>Bảng phân công đánh giá PIs</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Tạo bài 2 câu/ý gắn CLO, nhập điểm, tải mẫu Excel, nhập lại, phân tích</t>
+          <t>Xuất bảng phân công học kỳ</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra giới hạn điểm; p, DI, alpha, CLO đúng</t>
+          <t>Đúng cột như bảng gốc; 404 học kỳ không tồn tại</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
@@ -3595,11 +3616,11 @@
         </is>
       </c>
       <c r="G71" s="4" t="n">
-        <v>0.76</v>
+        <v>0.05</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>test_grading::test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_api::test_assignments_xlsx</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr"/>
@@ -3610,22 +3631,22 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>8. Nhập điểm, gộp bài, phụ đạo</t>
+          <t>7. Báo cáo biểu mẫu BM2, BM3, BM6, phân công</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Tạo bài từ tệp Excel bất kỳ</t>
+          <t>Nhận xét PLO (BM3b)</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Tệp Excel tự soạn có cột MSSV và cột điểm</t>
+          <t>Lưu 4 mục nhận xét PLO</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Tạo bài, ghi điểm; SV lạ được ghi danh khi chọn</t>
+          <t>Lưu đúng; GV bị 403</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
@@ -3634,11 +3655,11 @@
         </is>
       </c>
       <c r="G72" s="4" t="n">
-        <v>0.27</v>
+        <v>0.02</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>test_grading::test_create_exam_from_any_excel</t>
+          <t>test_api::test_plo_narrative</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr"/>
@@ -3654,17 +3675,17 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Gộp 2–3 bài đánh giá CLO/PLO</t>
+          <t>Đề nhập điểm của môn giao cho lớp</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Gộp bài 2 lớp theo 2 cách; bật/tắt minh chứng BM6</t>
+          <t>Khai báo câu/ý gắn CLO ở cấp môn, giao cho lớp 02 rồi nhập điểm</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Số liệu khớp; PLO theo từng CTĐT; BM6b đổi tương ứng</t>
+          <t>Bảng điểm đủ 35 SV của lớp; nhập điểm ở đề chưa giao bị chặn (409)</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
@@ -3673,11 +3694,11 @@
         </is>
       </c>
       <c r="G73" s="4" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>test_grading::test_combine_exams_and_evidence_flag</t>
+          <t>test_de_cua_mon::test_course_manual_exam_deploy_and_grade</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr"/>
@@ -3693,17 +3714,17 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Phụ đạo theo câu sai</t>
+          <t>Bài nhập điểm: bảng điểm, Excel, phân tích</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Đếm câu sai từng SV, xem câu sai, tạo bài phụ đạo</t>
+          <t>Tạo bài 2 câu/ý gắn CLO, nhập điểm, tải mẫu Excel, nhập lại, phân tích</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Số câu sai đúng; bài phụ đạo có câu sai + câu tương tự, không gộp minh chứng</t>
+          <t>Kiểm tra giới hạn điểm; p, DI, alpha, CLO đúng</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
@@ -3712,11 +3733,11 @@
         </is>
       </c>
       <c r="G74" s="4" t="n">
-        <v>0.21</v>
+        <v>1.01</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>test_grading::test_remedial_flow</t>
+          <t>test_grading::test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr"/>
@@ -3727,22 +3748,22 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>9. Đề giấy &amp; chấm phiếu trên hệ thống (OMR)</t>
+          <t>8. Nhập điểm, gộp bài, phụ đạo</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Đề giấy trên hệ thống từ đầu đến cuối</t>
+          <t>Tạo bài từ tệp Excel bất kỳ</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Sinh 3 mã đề, xuất PDF 1/2 cột, Word, phiếu, đáp án, .zip; tô 6 phiếu (có ảnh nghiêng), chấm, sửa, lưu</t>
+          <t>Tệp Excel tự soạn có cột MSSV và cột điểm</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Đọc đúng MSSV, mã đề, điểm; 34 SV vắng; phân tích xong</t>
+          <t>Tạo bài, ghi điểm; SV lạ được ghi danh khi chọn</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
@@ -3751,11 +3772,11 @@
         </is>
       </c>
       <c r="G75" s="4" t="n">
-        <v>2.48</v>
+        <v>0.34</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>test_paper::test_system_paper_exam_end_to_end</t>
+          <t>test_grading::test_create_exam_from_any_excel</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr"/>
@@ -3766,22 +3787,22 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>9. Đề giấy &amp; chấm phiếu trên hệ thống (OMR)</t>
+          <t>8. Nhập điểm, gộp bài, phụ đạo</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Chấm phiếu: gạch chéo, tô 2 ô, nét bút đè ô định vị</t>
+          <t>Gộp 2–3 bài đánh giá CLO/PLO</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Phiếu tô theo nhiều kiểu</t>
+          <t>Gộp bài 2 lớp theo 2 cách; bật/tắt minh chứng BM6</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Lấy ô tô kín; cảnh báo tô 2 ô; không lệch phiếu</t>
+          <t>Số liệu khớp; PLO theo từng CTĐT; BM6b đổi tương ứng</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
@@ -3790,11 +3811,11 @@
         </is>
       </c>
       <c r="G76" s="4" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>test_paper::test_omr_crossed_out_and_scribbles</t>
+          <t>test_grading::test_combine_exams_and_evidence_flag</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr"/>
@@ -3805,22 +3826,22 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>10. Tích hợp Moodle: Web Service, SSO, đồng bộ câu hỏi, liên kết lớp</t>
+          <t>8. Nhập điểm, gộp bài, phụ đạo</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Dữ liệu kết quả gửi sang Moodle</t>
+          <t>Phụ đạo theo câu sai</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Xem trước kết quả từng SV</t>
+          <t>Đếm câu sai từng SV, xem câu sai, tạo bài phụ đạo</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Radar CLO, nhận định, lộ trình; SV vắng 'chưa đủ bằng chứng'</t>
+          <t>Số câu sai đúng; bài phụ đạo có câu sai + câu tương tự, không gộp minh chứng</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
@@ -3829,11 +3850,11 @@
         </is>
       </c>
       <c r="G77" s="4" t="n">
-        <v>0.02</v>
+        <v>0.29</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_results_for_moodle</t>
+          <t>test_grading::test_remedial_flow</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr"/>
@@ -3844,22 +3865,22 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>10. Tích hợp Moodle: Web Service, SSO, đồng bộ câu hỏi, liên kết lớp</t>
+          <t>9. Đề giấy &amp; chấm phiếu trên hệ thống (OMR)</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Gửi kết quả khi chưa cấu hình Web Service</t>
+          <t>Đề giấy trên hệ thống từ đầu đến cuối</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Gửi kết quả khi thiếu token Moodle</t>
+          <t>Sinh 3 mã đề, xuất PDF 1/2 cột, Word, phiếu, đáp án, .zip; tô 6 phiếu (có ảnh nghiêng), chấm, sửa, lưu</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>502 kèm thông báo</t>
+          <t>Đọc đúng MSSV, mã đề, điểm; 34 SV vắng; phân tích xong</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
@@ -3868,11 +3889,11 @@
         </is>
       </c>
       <c r="G78" s="4" t="n">
-        <v>0.02</v>
+        <v>2.76</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_push_requires_moodle_config</t>
+          <t>test_paper::test_system_paper_exam_end_to_end</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr"/>
@@ -3883,22 +3904,22 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>10. Tích hợp Moodle: Web Service, SSO, đồng bộ câu hỏi, liên kết lớp</t>
+          <t>9. Đề giấy &amp; chấm phiếu trên hệ thống (OMR)</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Chỉ công bố bài đã phân tích</t>
+          <t>Chấm phiếu: gạch chéo, tô 2 ô, nét bút đè ô định vị</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Công bố bài chưa phân tích</t>
+          <t>Phiếu tô theo nhiều kiểu</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>Lấy ô tô kín; cảnh báo tô 2 ô; không lệch phiếu</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -3907,11 +3928,11 @@
         </is>
       </c>
       <c r="G79" s="4" t="n">
-        <v>0.04</v>
+        <v>0.23</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_publish_requires_analyzed</t>
+          <t>test_paper::test_omr_crossed_out_and_scribbles</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr"/>
@@ -3927,17 +3948,17 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Đưa khóa học Moodle mới vào hệ thống</t>
+          <t>Dữ liệu kết quả gửi sang Moodle</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Khóa học GV là giảng viên trên Moodle</t>
+          <t>Xem trước kết quả từng SV</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Tạo lớp HP, gắn khóa, lấy danh sách SV</t>
+          <t>Radar CLO, nhận định, lộ trình; SV vắng 'chưa đủ bằng chứng'</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
@@ -3946,11 +3967,11 @@
         </is>
       </c>
       <c r="G80" s="4" t="n">
-        <v>0.17</v>
+        <v>0.03</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>test_courses::test_import_moodle_course</t>
+          <t>test_api::test_results_for_moodle</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr"/>
@@ -3966,17 +3987,17 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Chỉ liên kết Quiz của khóa mình dạy</t>
+          <t>Gửi kết quả khi chưa cấu hình Web Service</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Liên kết Quiz của khóa học khác</t>
+          <t>Gửi kết quả khi thiếu token Moodle</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>403/409</t>
+          <t>502 kèm thông báo</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
@@ -3985,11 +4006,11 @@
         </is>
       </c>
       <c r="G81" s="4" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>test_hardening::test_link_quiz_must_belong_to_teacher_course</t>
+          <t>test_api::test_push_requires_moodle_config</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr"/>
@@ -4005,17 +4026,17 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Đăng nhập một lần từ Moodle</t>
+          <t>Chỉ công bố bài đã phân tích</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Vé SSO hợp lệ; dùng lại vé</t>
+          <t>Công bố bài chưa phân tích</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Vào thẳng lớp HP; vé dùng lại bị từ chối</t>
+          <t>409</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
@@ -4024,11 +4045,11 @@
         </is>
       </c>
       <c r="G82" s="4" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>test_sso::test_teacher_sso_and_replay</t>
+          <t>test_api::test_publish_requires_analyzed</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr"/>
@@ -4044,17 +4065,17 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Từ chối vé SSO sai</t>
+          <t>Đưa khóa học Moodle mới vào hệ thống</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Sai chữ ký, hết hạn, sai nơi phát hành</t>
+          <t>Khóa học GV là giảng viên trên Moodle</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>Tạo lớp HP, gắn khóa, lấy danh sách SV</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
@@ -4063,11 +4084,11 @@
         </is>
       </c>
       <c r="G83" s="4" t="n">
-        <v>0.01</v>
+        <v>0.25</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>test_sso::test_sso_rejects_bad_tickets</t>
+          <t>test_courses::test_import_moodle_course</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr"/>
@@ -4083,17 +4104,17 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>SSO không nâng quyền</t>
+          <t>Chỉ liên kết Quiz của khóa mình dạy</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Vé ghi role admin cho tài khoản GV</t>
+          <t>Liên kết Quiz của khóa học khác</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Giữ quyền GV</t>
+          <t>403/409</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
@@ -4102,11 +4123,11 @@
         </is>
       </c>
       <c r="G84" s="4" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>test_sso::test_sso_never_escalates</t>
+          <t>test_hardening::test_link_quiz_must_belong_to_teacher_course</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr"/>
@@ -4122,17 +4143,17 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>SSO tạo tài khoản GV đã khai báo</t>
+          <t>Đăng nhập một lần từ Moodle</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>GV có hồ sơ nhưng chưa có tài khoản</t>
+          <t>Vé SSO hợp lệ; dùng lại vé</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Tạo tài khoản, gắn hồ sơ</t>
+          <t>Vào thẳng lớp HP; vé dùng lại bị từ chối</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
@@ -4141,11 +4162,11 @@
         </is>
       </c>
       <c r="G85" s="4" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>test_sso::test_sso_provisions_declared_lecturer</t>
+          <t>test_sso::test_teacher_sso_and_replay</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr"/>
@@ -4161,17 +4182,17 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Liên kết mã lớp ⇄ khóa học Moodle</t>
+          <t>Từ chối vé SSO sai</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Tự nối theo shortname, nối cả môn, gắn thủ công</t>
+          <t>Sai chữ ký, hết hạn, sai nơi phát hành</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Chỉ nối khi GV là giảng viên khóa; chặn trùng</t>
+          <t>401</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
@@ -4180,11 +4201,11 @@
         </is>
       </c>
       <c r="G86" s="4" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>test_z_toan_bo_chuc_nang::test_link_section_with_moodle_both_ways</t>
+          <t>test_sso::test_sso_rejects_bad_tickets</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr"/>
@@ -4200,17 +4221,17 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Web Service: Quiz, Offline Quiz, công bố</t>
+          <t>SSO không nâng quyền</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Tạo Quiz, tạo đề giấy, trạng thái, xử lý phiếu, tải tệp/.zip, công bố, gửi kết quả, trạng thái WS</t>
+          <t>Vé ghi role admin cho tài khoản GV</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Đúng tham số gửi Moodle; không lộ token; 40 kết quả</t>
+          <t>Giữ quyền GV</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
@@ -4219,11 +4240,11 @@
         </is>
       </c>
       <c r="G87" s="4" t="n">
-        <v>0.32</v>
+        <v>0.02</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>test_z_toan_bo_chuc_nang::test_moodle_web_service_flows</t>
+          <t>test_sso::test_sso_never_escalates</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr"/>
@@ -4239,17 +4260,17 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ ngân hàng câu hỏi hai chiều</t>
+          <t>SSO tạo tài khoản GV đã khai báo</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Đẩy câu mới, nhập câu soạn trên Moodle, Moodle sửa (phiên bản 2) → kéo về</t>
+          <t>GV có hồ sơ nhưng chưa có tài khoản</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Trạng thái đúng từng bước; câu có kết quả không bị ghi đè</t>
+          <t>Tạo tài khoản, gắn hồ sơ</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
@@ -4258,11 +4279,11 @@
         </is>
       </c>
       <c r="G88" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>test_z_toan_bo_chuc_nang::test_question_bank_two_way_sync</t>
+          <t>test_sso::test_sso_provisions_declared_lecturer</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr"/>
@@ -4273,22 +4294,22 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>11. Thống kê lớp, hồ sơ sinh viên</t>
+          <t>10. Tích hợp Moodle: Web Service, SSO, đồng bộ câu hỏi, liên kết lớp</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Thống kê lớp học phần</t>
+          <t>Liên kết mã lớp ⇄ khóa học Moodle</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Chỉ số tổng quan, CLO, Bloom, chương cần ôn, bản đồ nhiệt</t>
+          <t>Tự nối theo shortname, nối cả môn, gắn thủ công</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Khớp BM6</t>
+          <t>Chỉ nối khi GV là giảng viên khóa; chặn trùng</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
@@ -4297,11 +4318,11 @@
         </is>
       </c>
       <c r="G89" s="4" t="n">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>test_insights::test_section_stats</t>
+          <t>test_z_toan_bo_chuc_nang::test_link_section_with_moodle_both_ways</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr"/>
@@ -4312,22 +4333,22 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>11. Thống kê lớp, hồ sơ sinh viên</t>
+          <t>10. Tích hợp Moodle: Web Service, SSO, đồng bộ câu hỏi, liên kết lớp</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Hồ sơ từng sinh viên</t>
+          <t>Web Service: Quiz, Offline Quiz, công bố</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Điểm, thứ hạng, CLO qua các bài, phần cần học lại</t>
+          <t>Tạo Quiz, tạo đề giấy, trạng thái, xử lý phiếu, tải tệp/.zip, công bố, gửi kết quả, trạng thái WS</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Đúng số liệu</t>
+          <t>Đúng tham số gửi Moodle; không lộ token; 40 kết quả</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
@@ -4336,11 +4357,11 @@
         </is>
       </c>
       <c r="G90" s="4" t="n">
-        <v>0.19</v>
+        <v>0.46</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>test_insights::test_student_profile</t>
+          <t>test_z_toan_bo_chuc_nang::test_moodle_web_service_flows</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr"/>
@@ -4351,22 +4372,22 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>11. Thống kê lớp, hồ sơ sinh viên</t>
+          <t>10. Tích hợp Moodle: Web Service, SSO, đồng bộ câu hỏi, liên kết lớp</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Phân quyền hồ sơ SV</t>
+          <t>Đồng bộ ngân hàng câu hỏi hai chiều</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>GV khác, token SV</t>
+          <t>Đẩy câu mới, nhập câu soạn trên Moodle, Moodle sửa (phiên bản 2) → kéo về</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>Trạng thái đúng từng bước; câu có kết quả không bị ghi đè</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
@@ -4375,11 +4396,11 @@
         </is>
       </c>
       <c r="G91" s="4" t="n">
-        <v>0.13</v>
+        <v>0.65</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>test_insights::test_profile_access</t>
+          <t>test_z_toan_bo_chuc_nang::test_question_bank_two_way_sync</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr"/>
@@ -4390,22 +4411,22 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>12. Nâng cấp CSDL, cầu nối</t>
+          <t>11. Thống kê lớp, hồ sơ sinh viên</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Cầu nối khi Moodle chưa cài Offline Quiz</t>
+          <t>Thống kê lớp học phần</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Cài cầu nối</t>
+          <t>Chỉ số tổng quan, CLO, Bloom, chương cần ôn, bản đồ nhiệt</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Vẫn chạy cho Quiz</t>
+          <t>Khớp BM6</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
@@ -4414,11 +4435,11 @@
         </is>
       </c>
       <c r="G92" s="4" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>test_upgrade::test_bridge_without_offlinequiz_plugin</t>
+          <t>test_insights::test_section_stats</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr"/>
@@ -4429,38 +4450,311 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
+          <t>11. Thống kê lớp, hồ sơ sinh viên</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Hồ sơ từng sinh viên</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Điểm, thứ hạng, CLO qua các bài, phần cần học lại</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>Đúng số liệu</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>test_insights::test_student_profile</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>11. Thống kê lớp, hồ sơ sinh viên</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Phân quyền hồ sơ SV</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>GV khác, token SV</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>test_insights::test_profile_access</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
           <t>12. Nâng cấp CSDL, cầu nối</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Cầu nối khi Moodle chưa cài Offline Quiz</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Cài cầu nối</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>Vẫn chạy cho Quiz</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>test_upgrade::test_bridge_without_offlinequiz_plugin</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>12. Nâng cấp CSDL, cầu nối</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>Nâng cấp CSDL phiên bản cũ</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="D96" s="4" t="inlineStr">
         <is>
           <t>CSDL thiếu cột mới, CHECK cũ</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="E96" s="4" t="inlineStr">
         <is>
           <t>Tự thêm cột, thay CHECK, nạp CTĐT 2026</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>ĐẠT</t>
-        </is>
-      </c>
-      <c r="G93" s="4" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="H93" s="4" t="inlineStr">
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
         <is>
           <t>test_upgrade::test_upgrade_old_database_adds_offlinequiz_column</t>
         </is>
       </c>
-      <c r="I93" s="4" t="inlineStr"/>
+      <c r="I96" s="4" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>Tính thời gian trả lời từng câu</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Dãy thời điểm chọn đáp án; nhiều câu cùng một trang (cùng thời điểm)</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Thời gian = khoảng cách tới lần chọn trước; câu cùng trang chia đều; báo độ phân giải theo trang</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>test_timing::test_response_time_split_and_page_resolution</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>Đồng bộ thời điểm chọn đáp án từ Moodle</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>Đồng bộ Quiz có giới hạn 45 phút, tự nộp khi hết giờ</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lần chọn đầu/cuối, số lần lưu từng câu; giới hạn thời gian; lượt hết giờ tự nộp</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>test_timing::test_sync_stores_answer_times</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Cảnh báo SV chọn đại / chọn xong để hết giờ</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Dữ liệu có 2 SV chọn ~20 câu trong 1 phút và 2 SV chọn xong không nộp chờ hết giờ</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Đúng 4 SV bị cảnh báo đúng loại; SV bình thường không bị gắn cờ; số cảnh báo hiện ở danh sách bài KT</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>test_timing::test_timing_report_flags_planted_students</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>Đổi ngưỡng, diễn biến từng SV, xuất Excel</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>Gửi ngưỡng tùy chỉnh / sai; xem diễn biến 1 SV; tải Excel; bài giấy</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>Kết quả theo ngưỡng; ngưỡng sai 422; SV không làm 404; Excel 2 sheet; bài giấy báo không áp dụng</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>test_timing::test_timing_thresholds_timeline_and_export</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4473,7 +4767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5393,7 +5687,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>test_new_course_setup_flow</t>
+          <t>test_course_manual_exam_deploy_and_grade, test_new_course_setup_flow</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5792,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>test_aiken_and_moodle_xml, test_bulk_import_then_tag, test_import_moodle_course, test_new_course_setup_flow, test_profile_access, test_section_stats</t>
+          <t>test_aiken_and_moodle_xml, test_bulk_import_then_tag, test_course_exam_create_and_blocked_actions, test_course_exam_deploy_to_sections, test_course_manual_exam_deploy_and_grade, test_import_moodle_course</t>
         </is>
       </c>
     </row>
@@ -6493,7 +6787,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/exams</t>
+          <t>/api/courses/{course_id}/exams</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -6503,7 +6797,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>list_exams</t>
+          <t>Đề của môn (tạo ở trang môn học, chưa gắn lớp) kèm các lớp đã giao; và các lớp HP của người dùng để giao đề.</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
@@ -6513,7 +6807,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>test_profile_access, test_section_stats, test_student_profile</t>
+          <t>test_course_exam_create_and_blocked_actions</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6822,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/exam-blueprint/pool</t>
+          <t>/api/class-sections/{cs_id}/exams</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -6538,7 +6832,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Số câu sẵn có theo từng ô ma trận (chương × mức Bloom) và theo CLO – để GV lập ma trận đề.</t>
+          <t>list_exams</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
@@ -6548,7 +6842,7 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>test_blueprint_api</t>
+          <t>test_profile_access, test_section_stats, test_student_profile, test_timing_report_flags_planted_students</t>
         </is>
       </c>
     </row>
@@ -6558,12 +6852,12 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/exam-blueprint</t>
+          <t>/api/class-sections/{cs_id}/exam-blueprint/pool</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -6573,7 +6867,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Sinh đề theo ma trận: trả về danh sách câu + điểm, ma trận mục tiêu/đạt được, độ phủ CLO, lỗi thiếu câu và cảnh báo.</t>
+          <t>Số câu sẵn có theo từng ô ma trận (chương × mức Bloom) và theo CLO – để GV lập ma trận đề.</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
@@ -6593,12 +6887,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>/api/exams</t>
+          <t>/api/courses/{course_id}/exam-blueprint/pool</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -6608,7 +6902,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>create_exam</t>
+          <t>Như trên, cho đề của môn (tạo ở trang môn học).</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
@@ -6618,7 +6912,7 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>test_blueprint_api, test_bm6c_per_exam, test_bulk_import_then_tag, test_copy_exam_manual_items_and_paper_versions, test_exam_online_xml, test_link_quiz_must_belong_to_teacher_course</t>
+          <t>test_course_exam_create_and_blocked_actions</t>
         </is>
       </c>
     </row>
@@ -6628,12 +6922,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}</t>
+          <t>/api/class-sections/{cs_id}/exam-blueprint</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -6643,7 +6937,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>get_exam</t>
+          <t>Sinh đề theo ma trận: trả về danh sách câu + điểm, ma trận mục tiêu/đạt được, độ phủ CLO, lỗi thiếu câu và cảnh báo.</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
@@ -6653,7 +6947,7 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>test_exam_online_xml, test_manual_exam_grid_excel_and_analysis, test_moodle_web_service_flows, test_remedial_flow, test_system_paper_exam_end_to_end</t>
+          <t>test_blueprint_api</t>
         </is>
       </c>
     </row>
@@ -6663,12 +6957,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}</t>
+          <t>/api/courses/{course_id}/exam-blueprint</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -6678,7 +6972,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>delete_exam</t>
+          <t>Như trên, cho đề của môn (tạo ở trang môn học).</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
@@ -6688,7 +6982,7 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>test_blueprint_api, test_bulk_import_then_tag, test_exam_online_xml, test_link_quiz_must_belong_to_teacher_course, test_paper_sync_requires_offlinequiz, test_publish_requires_analyzed</t>
+          <t>test_course_exam_create_and_blocked_actions</t>
         </is>
       </c>
     </row>
@@ -6698,12 +6992,12 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle-xml</t>
+          <t>/api/exams</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -6713,7 +7007,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>moodle_xml</t>
+          <t>Bài KT của một lớp HP, hoặc đề của môn (course_id) – giao cho các lớp HP khi xuất (POST /exams/{id}/copy).</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
@@ -6723,7 +7017,7 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>test_exam_online_xml</t>
+          <t>test_blueprint_api, test_bm6c_per_exam, test_bulk_import_then_tag, test_copy_exam_manual_items_and_paper_versions, test_course_exam_create_and_blocked_actions, test_course_exam_deploy_to_sections</t>
         </is>
       </c>
     </row>
@@ -6733,12 +7027,12 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/link-quiz</t>
+          <t>/api/exams/{exam_id}</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -6748,7 +7042,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>link_quiz</t>
+          <t>get_exam</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
@@ -6758,7 +7052,7 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>test_link_quiz_must_belong_to_teacher_course</t>
+          <t>test_course_exam_create_and_blocked_actions, test_course_exam_deploy_to_sections, test_course_manual_exam_deploy_and_grade, test_exam_online_xml, test_manual_exam_grid_excel_and_analysis, test_moodle_web_service_flows</t>
         </is>
       </c>
     </row>
@@ -6768,12 +7062,12 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/publish</t>
+          <t>/api/exams/{exam_id}</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -6783,7 +7077,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>publish</t>
+          <t>Xóa bài KT chưa có kết quả. Xóa đề của môn không ảnh hưởng các bài đã giao cho lớp.</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
@@ -6793,7 +7087,7 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>test_moodle_web_service_flows</t>
+          <t>test_blueprint_api, test_bulk_import_then_tag, test_course_exam_deploy_to_sections, test_course_manual_exam_deploy_and_grade, test_exam_online_xml, test_link_quiz_must_belong_to_teacher_course</t>
         </is>
       </c>
     </row>
@@ -6803,12 +7097,12 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/copy</t>
+          <t>/api/exams/{exam_id}/moodle-xml</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -6818,7 +7112,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>GV dạy nhiều lớp của cùng một môn: sao đề (câu hỏi, điểm, cấu hình, câu/ý nhập điểm) sang các lớp khác và –</t>
+          <t>moodle_xml</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
@@ -6828,7 +7122,7 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>test_copy_exam_manual_items_and_paper_versions</t>
+          <t>test_course_exam_create_and_blocked_actions, test_exam_online_xml</t>
         </is>
       </c>
     </row>
@@ -6838,22 +7132,22 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/manual-exams</t>
+          <t>/api/exams/{exam_id}/link-quiz</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Nhập điểm thủ công &amp; gộp bài KT</t>
+          <t>UC-02 Đề thi</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>create_manual_exam</t>
+          <t>link_quiz</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
@@ -6863,7 +7157,7 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>test_copy_exam_manual_items_and_paper_versions, test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_link_quiz_must_belong_to_teacher_course</t>
         </is>
       </c>
     </row>
@@ -6873,22 +7167,22 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/manual-items</t>
+          <t>/api/exams/{exam_id}/publish</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Nhập điểm thủ công &amp; gộp bài KT</t>
+          <t>UC-02 Đề thi</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>replace_items</t>
+          <t>publish</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
@@ -6898,7 +7192,7 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>test_copy_exam_manual_items_and_paper_versions</t>
+          <t>test_moodle_web_service_flows</t>
         </is>
       </c>
     </row>
@@ -6908,22 +7202,22 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/grades</t>
+          <t>/api/exams/{exam_id}/copy</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Nhập điểm thủ công &amp; gộp bài KT</t>
+          <t>UC-02 Đề thi</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>get_grades</t>
+          <t>Giao đề cho lớp HP: đề của môn (tạo ở trang môn học) được giao khi xuất cho các lớp GV chọn; bài của một lớp được</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
@@ -6933,7 +7227,7 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>test_copy_exam_manual_items_and_paper_versions, test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_copy_exam_manual_items_and_paper_versions, test_course_exam_deploy_to_sections, test_course_manual_exam_deploy_and_grade</t>
         </is>
       </c>
     </row>
@@ -6943,12 +7237,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/grades</t>
+          <t>/api/class-sections/{cs_id}/manual-exams</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -6958,7 +7252,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>put_grades</t>
+          <t>create_manual_exam</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
@@ -6968,7 +7262,7 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_copy_exam_manual_items_and_paper_versions, test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
     </row>
@@ -6978,12 +7272,12 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/grades.xlsx</t>
+          <t>/api/courses/{course_id}/manual-exams</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -6993,7 +7287,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>grades_template</t>
+          <t>Đề nhập điểm của môn (tạo ở trang môn học): khai báo câu/ý gắn CLO một lần, giao cho các lớp HP để nhập điểm.</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
@@ -7003,7 +7297,7 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_course_manual_exam_deploy_and_grade</t>
         </is>
       </c>
     </row>
@@ -7013,12 +7307,12 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/grades/import</t>
+          <t>/api/exams/{exam_id}/manual-items</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -7028,7 +7322,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Nhập điểm từ Excel vào bài đã có: khớp cột theo mã câu (bảng điểm mẫu), theo tên câu/ý, hoặc theo thứ tự cột.</t>
+          <t>replace_items</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
@@ -7038,7 +7332,7 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_copy_exam_manual_items_and_paper_versions</t>
         </is>
       </c>
     </row>
@@ -7048,12 +7342,12 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/manual-exams/import</t>
+          <t>/api/exams/{exam_id}/grades</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -7063,7 +7357,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Tạo bài nhập điểm từ một file Excel bất kỳ (bài làm ngoài hệ thống) và nhập luôn điểm.</t>
+          <t>get_grades</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
@@ -7073,7 +7367,7 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>test_create_exam_from_any_excel</t>
+          <t>test_copy_exam_manual_items_and_paper_versions, test_course_manual_exam_deploy_and_grade, test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
     </row>
@@ -7083,12 +7377,12 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/evidence</t>
+          <t>/api/exams/{exam_id}/grades</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -7098,7 +7392,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Bài có được gộp vào kết quả CLO của lớp (BM6, PI, PLO) hay không.</t>
+          <t>put_grades</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
@@ -7108,7 +7402,7 @@
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>test_combine_exams_and_evidence_flag</t>
+          <t>test_course_manual_exam_deploy_and_grade, test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
     </row>
@@ -7123,7 +7417,7 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{course_id}/analyzed-exams</t>
+          <t>/api/exams/{exam_id}/grades.xlsx</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -7133,7 +7427,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Các bài đã phân tích của môn trong các lớp HP người dùng phụ trách – để chọn bài gộp.</t>
+          <t>grades_template</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
@@ -7143,7 +7437,7 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>test_combine_exams_and_evidence_flag</t>
+          <t>test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7452,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>/api/combined-analysis</t>
+          <t>/api/exams/{exam_id}/grades/import</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -7168,7 +7462,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>Nhập điểm từ Excel vào bài đã có: khớp cột theo mã câu (bảng điểm mẫu), theo tên câu/ý, hoặc theo thứ tự cột.</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
@@ -7178,7 +7472,7 @@
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>test_combine_exams_and_evidence_flag</t>
+          <t>test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
     </row>
@@ -7188,12 +7482,12 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>/api/combined-analysis.xlsx</t>
+          <t>/api/class-sections/{cs_id}/manual-exams/import</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -7203,7 +7497,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>combined_xlsx</t>
+          <t>Tạo bài nhập điểm từ một file Excel bất kỳ (bài làm ngoài hệ thống) và nhập luôn điểm.</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
@@ -7213,7 +7507,7 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>test_combine_exams_and_evidence_flag</t>
+          <t>test_create_exam_from_any_excel</t>
         </is>
       </c>
     </row>
@@ -7223,22 +7517,22 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/remedial</t>
+          <t>/api/exams/{exam_id}/evidence</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Phụ đạo theo câu trả lời sai</t>
+          <t>Nhập điểm thủ công &amp; gộp bài KT</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Bảng tổng hợp: mỗi SV sai bao nhiêu câu (trên các bài chọn), CLO chưa đạt; mỗi câu bao nhiêu SV sai.</t>
+          <t>Bài có được gộp vào kết quả CLO của lớp (BM6, PI, PLO) hay không.</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -7248,7 +7542,7 @@
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>test_remedial_flow</t>
+          <t>test_combine_exams_and_evidence_flag</t>
         </is>
       </c>
     </row>
@@ -7263,17 +7557,17 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/remedial/students/{student_id}</t>
+          <t>/api/courses/{course_id}/analyzed-exams</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Phụ đạo theo câu trả lời sai</t>
+          <t>Nhập điểm thủ công &amp; gộp bài KT</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Danh sách câu SV trả lời sai/bỏ trống (kèm phương án đã chọn, đáp án đúng, CLO, chương).</t>
+          <t>Các bài đã phân tích của môn trong các lớp HP người dùng phụ trách – để chọn bài gộp.</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
@@ -7283,7 +7577,7 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>test_remedial_flow</t>
+          <t>test_combine_exams_and_evidence_flag</t>
         </is>
       </c>
     </row>
@@ -7298,17 +7592,17 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/remedial-exams</t>
+          <t>/api/combined-analysis</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Phụ đạo theo câu trả lời sai</t>
+          <t>Nhập điểm thủ công &amp; gộp bài KT</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Tạo bài KT phụ đạo: câu trắc nghiệm các SV đã chọn làm sai (+ câu tương tự cùng CLO/chương chưa gặp).</t>
+          <t>combined</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
@@ -7318,7 +7612,7 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>test_remedial_flow</t>
+          <t>test_combine_exams_and_evidence_flag</t>
         </is>
       </c>
     </row>
@@ -7333,17 +7627,17 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper</t>
+          <t>/api/combined-analysis.xlsx</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Đề thi giấy &amp; chấm phiếu trên hệ thống</t>
+          <t>Nhập điểm thủ công &amp; gộp bài KT</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Trạng thái đề giấy: chế độ (hệ thống tự in &amp; chấm / Moodle Offline Quiz), các mã đề với đầy đủ câu, đáp án; tùy chọn in.</t>
+          <t>combined_xlsx</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
@@ -7353,7 +7647,7 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>test_copy_exam_manual_items_and_paper_versions, test_paper_exam_two_modes, test_system_paper_exam_end_to_end</t>
+          <t>test_combine_exams_and_evidence_flag</t>
         </is>
       </c>
     </row>
@@ -7363,22 +7657,22 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper/versions</t>
+          <t>/api/class-sections/{cs_id}/remedial</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Đề thi giấy &amp; chấm phiếu trên hệ thống</t>
+          <t>Phụ đạo theo câu trả lời sai</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>make_versions</t>
+          <t>Bảng tổng hợp: mỗi SV sai bao nhiêu câu (trên các bài chọn), CLO chưa đạt; mỗi câu bao nhiêu SV sai.</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
@@ -7388,7 +7682,7 @@
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>test_copy_exam_manual_items_and_paper_versions, test_system_paper_exam_end_to_end</t>
+          <t>test_remedial_flow</t>
         </is>
       </c>
     </row>
@@ -7398,22 +7692,22 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper/versions</t>
+          <t>/api/class-sections/{cs_id}/remedial/students/{student_id}</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Đề thi giấy &amp; chấm phiếu trên hệ thống</t>
+          <t>Phụ đạo theo câu trả lời sai</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Bỏ các mã đề hệ thống đã sinh (khi chưa chấm phiếu) – để sinh lại hoặc chuyển sang Moodle Offline Quiz.</t>
+          <t>Danh sách câu SV trả lời sai/bỏ trống (kèm phương án đã chọn, đáp án đúng, CLO, chương).</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
@@ -7423,7 +7717,7 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>test_copy_exam_manual_items_and_paper_versions</t>
+          <t>test_remedial_flow</t>
         </is>
       </c>
     </row>
@@ -7433,22 +7727,22 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper/settings</t>
+          <t>/api/class-sections/{cs_id}/remedial-exams</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Đề thi giấy &amp; chấm phiếu trên hệ thống</t>
+          <t>Phụ đạo theo câu trả lời sai</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>save_settings</t>
+          <t>Tạo bài KT phụ đạo: câu trắc nghiệm các SV đã chọn làm sai (+ câu tương tự cùng CLO/chương chưa gặp).</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
@@ -7458,7 +7752,7 @@
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>test_system_paper_exam_end_to_end</t>
+          <t>test_remedial_flow</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7767,7 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper/exam.{fmt}</t>
+          <t>/api/exams/{exam_id}/paper</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -7483,7 +7777,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>exam_file</t>
+          <t>Trạng thái đề giấy: chế độ (hệ thống tự in &amp; chấm / Moodle Offline Quiz), các mã đề với đầy đủ câu, đáp án; tùy chọn in.</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
@@ -7493,7 +7787,7 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>test_system_paper_exam_end_to_end</t>
+          <t>test_copy_exam_manual_items_and_paper_versions, test_paper_exam_two_modes, test_system_paper_exam_end_to_end</t>
         </is>
       </c>
     </row>
@@ -7503,12 +7797,12 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper/answer-sheet.{fmt}</t>
+          <t>/api/exams/{exam_id}/paper/versions</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -7518,7 +7812,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Phiếu trả lời: png = ảnh xem trước (theo tham số đang chỉnh); pdf = tệp in (theo cài đặt đã lưu).</t>
+          <t>make_versions</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
@@ -7528,7 +7822,7 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>test_system_paper_exam_end_to_end</t>
+          <t>test_copy_exam_manual_items_and_paper_versions, test_course_exam_deploy_to_sections, test_system_paper_exam_end_to_end</t>
         </is>
       </c>
     </row>
@@ -7538,12 +7832,12 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper/answer-key.pdf</t>
+          <t>/api/exams/{exam_id}/paper/versions</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -7553,7 +7847,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>answer_key</t>
+          <t>Bỏ các mã đề hệ thống đã sinh (khi chưa chấm phiếu) – để sinh lại hoặc chuyển sang Moodle Offline Quiz.</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
@@ -7563,7 +7857,7 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>test_system_paper_exam_end_to_end</t>
+          <t>test_copy_exam_manual_items_and_paper_versions, test_course_exam_deploy_to_sections</t>
         </is>
       </c>
     </row>
@@ -7573,12 +7867,12 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper/package.zip</t>
+          <t>/api/exams/{exam_id}/paper/settings</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -7588,7 +7882,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Trọn bộ để in: đề từng mã đề (PDF + Word), phiếu trả lời, đáp án.</t>
+          <t>save_settings</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
@@ -7608,12 +7902,12 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/scan</t>
+          <t>/api/exams/{exam_id}/paper/exam.{fmt}</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -7623,7 +7917,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Nhận diện phiếu từ ảnh quét / ảnh chụp (JPG, PNG) hoặc PDF nhiều trang. Chưa ghi CSDL – GV soát rồi lưu (scan/commit).</t>
+          <t>exam_file</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
@@ -7643,12 +7937,12 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/scan/commit</t>
+          <t>/api/exams/{exam_id}/paper/answer-sheet.{fmt}</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -7658,7 +7952,7 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Lưu kết quả phiếu đã soát: Reverse Shuffle nhãn in trên mã đề -&gt; phương án gốc, chấm và phân tích.</t>
+          <t>Phiếu trả lời: png = ảnh xem trước (theo tham số đang chỉnh); pdf = tệp in (theo cài đặt đã lưu).</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
@@ -7683,17 +7977,17 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{course_id}/moodle-sync/targets</t>
+          <t>/api/exams/{exam_id}/paper/answer-key.pdf</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ ngân hàng câu hỏi với Moodle</t>
+          <t>Đề thi giấy &amp; chấm phiếu trên hệ thống</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>targets</t>
+          <t>answer_key</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
@@ -7703,7 +7997,7 @@
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>test_question_bank_two_way_sync</t>
+          <t>test_system_paper_exam_end_to_end</t>
         </is>
       </c>
     </row>
@@ -7718,17 +8012,17 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{course_id}/moodle-sync</t>
+          <t>/api/exams/{exam_id}/paper/package.zip</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ ngân hàng câu hỏi với Moodle</t>
+          <t>Đề thi giấy &amp; chấm phiếu trên hệ thống</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>compare</t>
+          <t>Trọn bộ để in: đề từng mã đề (PDF + Word), phiếu trả lời, đáp án.</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
@@ -7738,7 +8032,7 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>test_question_bank_two_way_sync</t>
+          <t>test_system_paper_exam_end_to_end</t>
         </is>
       </c>
     </row>
@@ -7753,17 +8047,17 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{course_id}/moodle-sync</t>
+          <t>/api/exams/{exam_id}/scan</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ ngân hàng câu hỏi với Moodle</t>
+          <t>Đề thi giấy &amp; chấm phiếu trên hệ thống</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>apply</t>
+          <t>Nhận diện phiếu từ ảnh quét / ảnh chụp (JPG, PNG) hoặc PDF nhiều trang. Chưa ghi CSDL – GV soát rồi lưu (scan/commit).</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
@@ -7773,7 +8067,7 @@
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>test_question_bank_two_way_sync</t>
+          <t>test_system_paper_exam_end_to_end</t>
         </is>
       </c>
     </row>
@@ -7788,17 +8082,17 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/sync</t>
+          <t>/api/exams/{exam_id}/scan/commit</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>UC-03 Đồng bộ &amp; phân tích</t>
+          <t>Đề thi giấy &amp; chấm phiếu trên hệ thống</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>sync_moodle</t>
+          <t>Lưu kết quả phiếu đã soát: Reverse Shuffle nhãn in trên mã đề -&gt; phương án gốc, chấm và phân tích.</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
@@ -7808,7 +8102,7 @@
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>test_paper_resync_is_idempotent, test_resync_is_idempotent, test_sync_stops_when_question_edited_on_moodle, test_sync_warns_average_grade_method</t>
+          <t>test_system_paper_exam_end_to_end</t>
         </is>
       </c>
     </row>
@@ -7818,22 +8112,22 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/analyze</t>
+          <t>/api/courses/{course_id}/moodle-sync/targets</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>UC-03 Đồng bộ &amp; phân tích</t>
+          <t>Đồng bộ ngân hàng câu hỏi với Moodle</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>analyze</t>
+          <t>targets</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
@@ -7843,7 +8137,7 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>test_sync_analyze_runs_and_bridge</t>
+          <t>test_question_bank_two_way_sync</t>
         </is>
       </c>
     </row>
@@ -7858,17 +8152,17 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/sync-runs</t>
+          <t>/api/courses/{course_id}/moodle-sync</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>UC-03 Đồng bộ &amp; phân tích</t>
+          <t>Đồng bộ ngân hàng câu hỏi với Moodle</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>sync_runs</t>
+          <t>compare</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
@@ -7878,7 +8172,7 @@
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>test_sync_analyze_runs_and_bridge</t>
+          <t>test_question_bank_two_way_sync</t>
         </is>
       </c>
     </row>
@@ -7888,22 +8182,22 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>/api/system/moodle-status</t>
+          <t>/api/courses/{course_id}/moodle-sync</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>UC-03 Đồng bộ &amp; phân tích</t>
+          <t>Đồng bộ ngân hàng câu hỏi với Moodle</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>moodle_status</t>
+          <t>apply</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -7913,7 +8207,7 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>test_sync_analyze_runs_and_bridge</t>
+          <t>test_question_bank_two_way_sync</t>
         </is>
       </c>
     </row>
@@ -7928,7 +8222,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>/api/system/install-bridge</t>
+          <t>/api/exams/{exam_id}/sync</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -7938,7 +8232,7 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>install_bridge</t>
+          <t>sync_moodle</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
@@ -7948,7 +8242,7 @@
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>test_sync_analyze_runs_and_bridge</t>
+          <t>test_paper_resync_is_idempotent, test_resync_is_idempotent, test_sync_stops_when_question_edited_on_moodle, test_sync_warns_average_grade_method</t>
         </is>
       </c>
     </row>
@@ -7958,22 +8252,22 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/moodle-course</t>
+          <t>/api/exams/{exam_id}/analyze</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Tích hợp Moodle (Web Service)</t>
+          <t>UC-03 Đồng bộ &amp; phân tích</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>set_moodle_course</t>
+          <t>analyze</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
@@ -7983,7 +8277,7 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>test_link_section_with_moodle_both_ways</t>
+          <t>test_sync_analyze_runs_and_bridge</t>
         </is>
       </c>
     </row>
@@ -7993,22 +8287,22 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/create-quiz</t>
+          <t>/api/exams/{exam_id}/sync-runs</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Tích hợp Moodle (Web Service)</t>
+          <t>UC-03 Đồng bộ &amp; phân tích</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>create_quiz</t>
+          <t>sync_runs</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
@@ -8018,7 +8312,7 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>test_moodle_web_service_flows</t>
+          <t>test_sync_analyze_runs_and_bridge</t>
         </is>
       </c>
     </row>
@@ -8028,22 +8322,22 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/create-offlinequiz</t>
+          <t>/api/system/moodle-status</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Tích hợp Moodle (Web Service)</t>
+          <t>UC-03 Đồng bộ &amp; phân tích</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>create_offlinequiz</t>
+          <t>moodle_status</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
@@ -8053,7 +8347,7 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>test_moodle_web_service_flows</t>
+          <t>test_sync_analyze_runs_and_bridge</t>
         </is>
       </c>
     </row>
@@ -8063,22 +8357,22 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/offlinequiz</t>
+          <t>/api/system/install-bridge</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Tích hợp Moodle (Web Service)</t>
+          <t>UC-03 Đồng bộ &amp; phân tích</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>offlinequiz_status</t>
+          <t>install_bridge</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
@@ -8088,7 +8382,7 @@
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>test_moodle_web_service_flows</t>
+          <t>test_sync_analyze_runs_and_bridge</t>
         </is>
       </c>
     </row>
@@ -8098,12 +8392,12 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/process-scans</t>
+          <t>/api/class-sections/{cs_id}/moodle-course</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -8113,7 +8407,7 @@
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>process_scans</t>
+          <t>set_moodle_course</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
@@ -8123,7 +8417,7 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>test_moodle_web_service_flows</t>
+          <t>test_link_section_with_moodle_both_ways</t>
         </is>
       </c>
     </row>
@@ -8133,12 +8427,12 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/offlinequiz/files/{filename}</t>
+          <t>/api/exams/{exam_id}/moodle/create-quiz</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -8148,7 +8442,7 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>offlinequiz_file</t>
+          <t>create_quiz</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
@@ -8168,12 +8462,12 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/offlinequiz/files.zip</t>
+          <t>/api/exams/{exam_id}/moodle/create-offlinequiz</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -8183,7 +8477,7 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>offlinequiz_zip</t>
+          <t>create_offlinequiz</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
@@ -8208,7 +8502,7 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/results-preview</t>
+          <t>/api/exams/{exam_id}/moodle/offlinequiz</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -8218,7 +8512,7 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>results_preview</t>
+          <t>offlinequiz_status</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
@@ -8228,7 +8522,7 @@
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>test_results_for_moodle</t>
+          <t>test_moodle_web_service_flows</t>
         </is>
       </c>
     </row>
@@ -8243,7 +8537,7 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/push-results</t>
+          <t>/api/exams/{exam_id}/moodle/process-scans</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -8253,7 +8547,7 @@
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>push_results</t>
+          <t>process_scans</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
@@ -8278,7 +8572,7 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>/api/system/lms-status</t>
+          <t>/api/exams/{exam_id}/moodle/offlinequiz/files/{filename}</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -8288,7 +8582,7 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>lms_status</t>
+          <t>offlinequiz_file</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
@@ -8313,17 +8607,17 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/overview</t>
+          <t>/api/exams/{exam_id}/moodle/offlinequiz/files.zip</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>UC-04 Thống kê lớp học</t>
+          <t>Tích hợp Moodle (Web Service)</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>overview</t>
+          <t>offlinequiz_zip</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
@@ -8333,7 +8627,7 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_moodle_web_service_flows</t>
         </is>
       </c>
     </row>
@@ -8348,17 +8642,17 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/item-stats</t>
+          <t>/api/exams/{exam_id}/moodle/results-preview</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>UC-04 Thống kê lớp học</t>
+          <t>Tích hợp Moodle (Web Service)</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>item_stats</t>
+          <t>results_preview</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
@@ -8368,7 +8662,7 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>test_item_stats_flags_trap_question, test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_results_for_moodle</t>
         </is>
       </c>
     </row>
@@ -8378,22 +8672,22 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/students</t>
+          <t>/api/exams/{exam_id}/moodle/push-results</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>UC-04 Thống kê lớp học</t>
+          <t>Tích hợp Moodle (Web Service)</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>exam_students</t>
+          <t>push_results</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
@@ -8403,7 +8697,7 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_moodle_web_service_flows</t>
         </is>
       </c>
     </row>
@@ -8418,17 +8712,17 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/clo-results</t>
+          <t>/api/system/lms-status</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>UC-04 Thống kê lớp học</t>
+          <t>Tích hợp Moodle (Web Service)</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>BM6b – kết quả tổng hợp của từng CĐR môn học (E1: rỗng nếu chưa phân tích).</t>
+          <t>lms_status</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
@@ -8438,7 +8732,7 @@
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>test_clo_results_bm6b</t>
+          <t>test_moodle_web_service_flows</t>
         </is>
       </c>
     </row>
@@ -8453,7 +8747,7 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/clo-results/{clo_id}/evidence</t>
+          <t>/api/exams/{exam_id}/overview</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -8463,7 +8757,7 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>BM6c/6d – bảng minh chứng: điểm từng SV trên các câu thuộc CLO, theo từng bài KT; câu hỏi có DI thấp.</t>
+          <t>overview</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
@@ -8473,7 +8767,7 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>test_sync_analyze_runs_and_bridge</t>
+          <t>test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
     </row>
@@ -8483,12 +8777,12 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/clo-results/{clo_id}</t>
+          <t>/api/exams/{exam_id}/item-stats</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -8498,7 +8792,7 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>clo_narrative</t>
+          <t>item_stats</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
@@ -8508,7 +8802,7 @@
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>test_clo_narrative</t>
+          <t>test_item_stats_flags_trap_question, test_manual_exam_grid_excel_and_analysis, test_timing_thresholds_timeline_and_export</t>
         </is>
       </c>
     </row>
@@ -8523,17 +8817,17 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/students/{student_id}/profile</t>
+          <t>/api/exams/{exam_id}/students</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>UC-04 Hồ sơ SV &amp; thống kê lớp</t>
+          <t>UC-04 Thống kê lớp học</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>student_profile</t>
+          <t>exam_students</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
@@ -8543,7 +8837,7 @@
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>test_student_profile</t>
+          <t>test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
     </row>
@@ -8558,17 +8852,17 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/stats</t>
+          <t>/api/class-sections/{cs_id}/clo-results</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>UC-04 Hồ sơ SV &amp; thống kê lớp</t>
+          <t>UC-04 Thống kê lớp học</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>section_stats</t>
+          <t>BM6b – kết quả tổng hợp của từng CĐR môn học (E1: rỗng nếu chưa phân tích).</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
@@ -8578,7 +8872,7 @@
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>test_section_stats, test_student_profile</t>
+          <t>test_clo_results_bm6b</t>
         </is>
       </c>
     </row>
@@ -8593,17 +8887,17 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/class-sections/{cs_id}/bm6.xlsx</t>
+          <t>/api/class-sections/{cs_id}/clo-results/{clo_id}/evidence</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>UC-07 Báo cáo đo lường CĐR</t>
+          <t>UC-04 Thống kê lớp học</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>bm6</t>
+          <t>BM6c/6d – bảng minh chứng: điểm từng SV trên các câu thuộc CLO, theo từng bài KT; câu hỏi có DI thấp.</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
@@ -8613,7 +8907,7 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>test_bm6_evidence_follows_plan_and_matches_bm6b, test_bm6_workbook, test_http_errors_and_inputs</t>
+          <t>test_sync_analyze_runs_and_bridge</t>
         </is>
       </c>
     </row>
@@ -8623,22 +8917,22 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/exams/{exam_id}/bm6c.xlsx</t>
+          <t>/api/class-sections/{cs_id}/clo-results/{clo_id}</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>UC-07 Báo cáo đo lường CĐR</t>
+          <t>UC-04 Thống kê lớp học</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>BM6c riêng cho một bài kiểm tra – minh chứng từng CLO bài KT đo (kèm MSSV, họ tên).</t>
+          <t>clo_narrative</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
@@ -8648,7 +8942,7 @@
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>test_bm6c_per_exam</t>
+          <t>test_clo_narrative</t>
         </is>
       </c>
     </row>
@@ -8663,17 +8957,17 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/programs/{pid}/bm3.xlsx</t>
+          <t>/api/exams/{exam_id}/timing</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>UC-07 Báo cáo đo lường CĐR</t>
+          <t>UC-04 Thống kê lớp học</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>bm3</t>
+          <t>Thời gian làm bài của từng SV và các dấu hiệu bất thường (làm quá nhanh/chọn đại, bỏ dở, treo máy chờ hết giờ…).</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
@@ -8683,7 +8977,7 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>test_bm3_workbook</t>
+          <t>test_timing_report_flags_planted_students, test_timing_thresholds_timeline_and_export</t>
         </is>
       </c>
     </row>
@@ -8698,17 +8992,17 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/programs/{pid}/bm2.docx</t>
+          <t>/api/exams/{exam_id}/timing/students/{student_id}</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>UC-07 Báo cáo đo lường CĐR</t>
+          <t>UC-04 Thống kê lớp học</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>BM2 dạng Word như biểu mẫu gốc: BM2a (kế hoạch) + BM2b (báo cáo tổng kết).</t>
+          <t>Diễn biến làm bài của một SV: thời điểm chọn, thời gian trả lời, số lần đổi đáp án từng câu.</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
@@ -8718,7 +9012,7 @@
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>test_bm2_docx</t>
+          <t>test_timing_thresholds_timeline_and_export</t>
         </is>
       </c>
     </row>
@@ -8733,17 +9027,17 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/semesters/{sem_id}/assignments.xlsx</t>
+          <t>/api/exams/{exam_id}/timing.xlsx</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>UC-07 Báo cáo đo lường CĐR</t>
+          <t>UC-04 Thống kê lớp học</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>Bảng "Phân công đánh giá PIs" của một học kỳ.</t>
+          <t>Xuất Excel danh sách cảnh báo và thời gian trả lời từng câu.</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
@@ -8753,7 +9047,7 @@
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>test_assignments_xlsx</t>
+          <t>test_timing_thresholds_timeline_and_export</t>
         </is>
       </c>
     </row>
@@ -8768,17 +9062,17 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/programs/{pid}/plo-summary</t>
+          <t>/api/class-sections/{cs_id}/students/{student_id}/profile</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>UC-07 Báo cáo đo lường CĐR</t>
+          <t>UC-04 Hồ sơ SV &amp; thống kê lớp</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>plo_summary</t>
+          <t>student_profile</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
@@ -8788,7 +9082,7 @@
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>test_plo_summary_is_sum_of_pi</t>
+          <t>test_student_profile, test_timing_thresholds_timeline_and_export</t>
         </is>
       </c>
     </row>
@@ -8798,22 +9092,22 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/programs/{pid}/recompute</t>
+          <t>/api/class-sections/{cs_id}/stats</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>UC-07 Báo cáo đo lường CĐR</t>
+          <t>UC-04 Hồ sơ SV &amp; thống kê lớp</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>recompute</t>
+          <t>section_stats</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
@@ -8823,7 +9117,7 @@
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>test_programs_plo_and_pi_plans</t>
+          <t>test_section_stats, test_student_profile</t>
         </is>
       </c>
     </row>
@@ -8833,12 +9127,12 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/plo-results/{plo_id}/{academic_year}</t>
+          <t>/api/reports/class-sections/{cs_id}/bm6.xlsx</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -8848,7 +9142,7 @@
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>plo_narrative</t>
+          <t>bm6</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
@@ -8858,7 +9152,7 @@
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>test_plo_narrative</t>
+          <t>test_bm6_evidence_follows_plan_and_matches_bm6b, test_bm6_workbook, test_http_errors_and_inputs</t>
         </is>
       </c>
     </row>
@@ -8873,17 +9167,17 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>/api/health</t>
+          <t>/api/reports/exams/{exam_id}/bm6c.xlsx</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống</t>
+          <t>UC-07 Báo cáo đo lường CĐR</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra dịch vụ</t>
+          <t>BM6c riêng cho một bài kiểm tra – minh chứng từng CLO bài KT đo (kèm MSSV, họ tên).</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
@@ -8893,7 +9187,7 @@
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>test_auth_me_and_catalogs</t>
+          <t>test_bm6c_per_exam</t>
         </is>
       </c>
     </row>
@@ -8908,25 +9202,270 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
+          <t>/api/reports/programs/{pid}/bm3.xlsx</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>UC-07 Báo cáo đo lường CĐR</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>bm3</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>test_bm3_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>/api/reports/programs/{pid}/bm2.docx</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>UC-07 Báo cáo đo lường CĐR</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>BM2 dạng Word như biểu mẫu gốc: BM2a (kế hoạch) + BM2b (báo cáo tổng kết).</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>test_bm2_docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>/api/reports/semesters/{sem_id}/assignments.xlsx</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>UC-07 Báo cáo đo lường CĐR</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>Bảng "Phân công đánh giá PIs" của một học kỳ.</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>test_assignments_xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>/api/reports/programs/{pid}/plo-summary</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>UC-07 Báo cáo đo lường CĐR</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>plo_summary</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>test_plo_summary_is_sum_of_pi</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>/api/reports/programs/{pid}/recompute</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>UC-07 Báo cáo đo lường CĐR</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>recompute</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>test_programs_plo_and_pi_plans</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>/api/reports/plo-results/{plo_id}/{academic_year}</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>UC-07 Báo cáo đo lường CĐR</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>plo_narrative</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>test_plo_narrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>/api/health</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>Hệ thống</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>Kiểm tra dịch vụ</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>test_auth_me_and_catalogs</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
           <t>/api/public-config</t>
         </is>
       </c>
-      <c r="D127" s="4" t="inlineStr">
+      <c r="D134" s="4" t="inlineStr">
         <is>
           <t>Hệ thống</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
+      <c r="E134" s="4" t="inlineStr">
         <is>
           <t>Cấu hình công khai cho giao diện</t>
         </is>
       </c>
-      <c r="F127" s="5" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="G127" s="4" t="inlineStr">
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
         <is>
           <t>test_auth_me_and_catalogs</t>
         </is>
@@ -8943,7 +9482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10035,6 +10574,64 @@
       </c>
       <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>GD-37</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>GV</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Tạo bài KT ở trang môn học, giao lớp khi xuất</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Môn học của tôi → '+ Tạo bài KT' ở môn DBMS330284 → chọn hình thức (3 thẻ) → soạn đề → Lưu đề của môn → 'Giao cho lớp HP / Xuất' → chọn lớp 02</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Hộp chọn hình thức hiển thị đủ chữ, không cuộn ngang; đề nằm ở thẻ Đề kiểm tra của môn; lớp 02 có bài mới 'giao từ đề #…'; giao lại lớp đã có bị bỏ qua</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>GD-38</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>GV</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Thời gian làm bài &amp; cảnh báo</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Bài Thi cuối kỳ (Moodle) &gt; thẻ 'Thời gian làm bài'; bấm 'Diễn biến' của SV 22130017; đổi ngưỡng giây/câu rồi Áp dụng; Xuất Excel</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>4 SV bị cảnh báo (2 làm quá nhanh, 2 để hết giờ tự nộp); biểu đồ từng câu; danh sách đổi theo ngưỡng; tải được Excel</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10051,8 +10648,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -10061,32 +10658,32 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Điều kiện / kiểu tô</t>
+          <t>Điều kiện ảnh / kiểu tô</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>Cột 2</t>
+          <t>MSSV đúng (ảnh) · Câu đọc đúng (kiểu tô)</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Cột 3</t>
+          <t>Mã đề đúng (ảnh) · Số câu bị cảnh báo (kiểu tô)</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Cột 4</t>
+          <t>Câu đọc đúng</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Cột 5</t>
+          <t>Phiếu lỗi định vị</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Cột 6</t>
+          <t>Thời gian/phiếu</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10715,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>115ms</t>
+          <t>117ms</t>
         </is>
       </c>
     </row>
@@ -10150,7 +10747,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>127ms</t>
+          <t>115ms</t>
         </is>
       </c>
     </row>
@@ -10182,7 +10779,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>228ms</t>
+          <t>227ms</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10811,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>114ms</t>
+          <t>107ms</t>
         </is>
       </c>
     </row>
@@ -10246,7 +10843,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>130ms</t>
+          <t>125ms</t>
         </is>
       </c>
     </row>

--- a/docs/kiem_thu/KET_QUA_KIEM_THU.xlsx
+++ b/docs/kiem_thu/KET_QUA_KIEM_THU.xlsx
@@ -11,7 +11,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ca kiem thu tu dong" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Do phu API" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kiem thu giao dien" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cham phieu OMR" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -42,7 +41,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +56,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -86,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -97,6 +101,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -484,14 +491,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Thời điểm chạy: 17/10/2026 11:03 · Python 3.11.15 · CSDL: kiểm thử dựng lại assessment_db</t>
+          <t>Thời điểm chạy: 24/10/2026 10:06 · Python 3.13.17 · CSDL: kiểm thử dựng lại assessment_db</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Ca kiểm thử tự động: 99/99 đạt · Độ phủ API: 133/133 endpoint được gọi thành công</t>
+          <t>Ca kiểm thử tự động: 112/112 đạt · Độ phủ API: 137/138 endpoint được gọi thành công</t>
         </is>
       </c>
     </row>
@@ -550,10 +557,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>0</v>
@@ -676,10 +683,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0</v>
@@ -781,10 +788,10 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>0</v>
@@ -802,10 +809,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0</v>
@@ -834,7 +841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -925,7 +932,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>33.01</v>
+        <v>15.76</v>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
@@ -964,7 +971,7 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
@@ -1003,7 +1010,7 @@
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
@@ -1081,7 +1088,7 @@
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -1120,7 +1127,7 @@
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -1159,7 +1166,7 @@
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -1393,7 +1400,7 @@
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.52</v>
+        <v>0.39</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
@@ -1432,7 +1439,7 @@
         </is>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -1452,17 +1459,17 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Phân công 'Tất cả thầy/cô có hướng dẫn'</t>
+          <t>In đề cương chi tiết dạng PDF theo mẫu ký</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Môn TLCN/KLTN</t>
+          <t>GET /courses/{id}/syllabus.pdf</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Mọi GV hướng dẫn được truy cập</t>
+          <t>PDF có quốc hiệu, tiêu đề, các mục đánh số, ô ký Trưởng khoa/Trưởng bộ môn/Giảng viên; không có token thì 401</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -1471,11 +1478,11 @@
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1</v>
+        <v>0.41</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>test_hardening::test_assignment_all_supervisors</t>
+          <t>test_courses::test_syllabus_pdf_mau_in</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr"/>
@@ -1491,17 +1498,17 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Quản lý CTĐT, PLO, kế hoạch đo PI</t>
+          <t>Phân công 'Tất cả thầy/cô có hướng dẫn'</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Thêm CTĐT, thêm/bỏ học phần, sửa chỉ tiêu PLO, thêm/sửa/xóa kế hoạch PI, tính lại</t>
+          <t>Môn TLCN/KLTN</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Đúng; GV 403; trùng mã 409; 404</t>
+          <t>Mọi GV hướng dẫn được truy cập</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1510,11 +1517,11 @@
         </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.32</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>test_z_toan_bo_chuc_nang::test_programs_plo_and_pi_plans</t>
+          <t>test_hardening::test_assignment_all_supervisors</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr"/>
@@ -1530,17 +1537,17 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Thêm/xóa CLO, Hủy câu hỏi, tệp mẫu</t>
+          <t>Quản lý CTĐT, PLO, kế hoạch đo PI</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Bộ môn thêm/xóa CLO; GV Hủy câu có lý do; tải tệp mẫu</t>
+          <t>Thêm CTĐT, thêm/bỏ học phần, sửa chỉ tiêu PLO, thêm/sửa/xóa kế hoạch PI, tính lại</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>GV không sửa CLO (403); CLO đã dùng 409</t>
+          <t>Đúng; GV 403; trùng mã 409; 404</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -1549,11 +1556,11 @@
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.14</v>
+        <v>0.27</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>test_z_toan_bo_chuc_nang::test_clo_lifecycle_cancel_question_and_template</t>
+          <t>test_z_toan_bo_chuc_nang::test_programs_plo_and_pi_plans</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr"/>
@@ -1564,22 +1571,22 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>3. Ngân hàng câu hỏi, nhập từ tệp, gán CLO</t>
+          <t>2. CTĐT, PLO/PI, học phần, đề cương, CLO</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra dữ liệu câu hỏi</t>
+          <t>Thêm/xóa CLO, Hủy câu hỏi, tệp mẫu</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Câu không có/ nhiều đáp án đúng, &lt; 2 phương án, tổng trọng số CLO ≠ 1</t>
+          <t>Bộ môn thêm/xóa CLO; GV Hủy câu có lý do; tải tệp mẫu</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>422 kèm thông báo tiếng Việt</t>
+          <t>GV không sửa CLO (403); CLO đã dùng 409</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -1588,11 +1595,11 @@
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_question_validation</t>
+          <t>test_z_toan_bo_chuc_nang::test_clo_lifecycle_cancel_question_and_template</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr"/>
@@ -1608,17 +1615,17 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Thêm, sửa, xóa câu hỏi</t>
+          <t>Kiểm tra dữ liệu câu hỏi</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Tạo câu hỏi 4 phương án gắn CLO, sửa, xóa câu chưa dùng</t>
+          <t>Câu không có/ nhiều đáp án đúng, &lt; 2 phương án, tổng trọng số CLO ≠ 1</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>201/200; dữ liệu ghi đúng</t>
+          <t>422 kèm thông báo tiếng Việt</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -1627,11 +1634,11 @@
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_question_crud</t>
+          <t>test_api::test_question_validation</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr"/>
@@ -1647,17 +1654,17 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Khóa câu hỏi đã có kết quả thi</t>
+          <t>Thêm, sửa, xóa câu hỏi</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Sửa/xóa câu đã có bài làm</t>
+          <t>Tạo câu hỏi 4 phương án gắn CLO, sửa, xóa câu chưa dùng</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>409; chỉ được Hủy</t>
+          <t>201/200; dữ liệu ghi đúng</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -1666,11 +1673,11 @@
         </is>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_question_with_results_is_locked</t>
+          <t>test_api::test_question_crud</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr"/>
@@ -1686,17 +1693,17 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Quy tắc sửa câu hỏi</t>
+          <t>Khóa câu hỏi đã có kết quả thi</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Sửa câu đã dùng trong đề nhưng chưa có kết quả</t>
+          <t>Sửa/xóa câu đã có bài làm</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Cho phép/khóa đúng quy tắc</t>
+          <t>409; chỉ được Hủy</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -1705,11 +1712,11 @@
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>test_hardening::test_question_edit_rules</t>
+          <t>test_api::test_question_with_results_is_locked</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr"/>
@@ -1725,17 +1732,17 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Trường hợp biên khi đọc tệp</t>
+          <t>Quy tắc sửa câu hỏi</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Dòng trống, BOM, khoảng trắng</t>
+          <t>Sửa câu đã dùng trong đề nhưng chưa có kết quả</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Đọc đúng, báo lỗi từng dòng</t>
+          <t>Cho phép/khóa đúng quy tắc</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -1744,11 +1751,11 @@
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>test_hardening::test_import_parsers_edge_cases</t>
+          <t>test_hardening::test_question_edit_rules</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr"/>
@@ -1764,17 +1771,17 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Đọc tệp Excel/CSV câu hỏi</t>
+          <t>Trường hợp biên khi đọc tệp</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Tệp mẫu</t>
+          <t>Dòng trống, BOM, khoảng trắng</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Đúng nội dung, phương án, đáp án</t>
+          <t>Đọc đúng, báo lỗi từng dòng</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -1787,7 +1794,7 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>test_question_import::test_parsers</t>
+          <t>test_hardening::test_import_parsers_edge_cases</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr"/>
@@ -1803,17 +1810,17 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Nhập hàng loạt rồi gán CLO từ tệp</t>
+          <t>Đọc tệp Excel/CSV câu hỏi</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Xem trước → ghi → tệp gán CLO</t>
+          <t>Tệp mẫu</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Câu 'Chưa gán' → đã gán; phát hiện trùng</t>
+          <t>Đúng nội dung, phương án, đáp án</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -1822,11 +1829,11 @@
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.59</v>
+        <v>0</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>test_question_import::test_bulk_import_then_tag</t>
+          <t>test_question_import::test_parsers</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr"/>
@@ -1842,17 +1849,17 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Không gán lại CLO câu đã có kết quả</t>
+          <t>Nhập hàng loạt rồi gán CLO từ tệp</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Tệp gán CLO cho câu đã dùng</t>
+          <t>Xem trước → ghi → tệp gán CLO</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Bị bỏ qua kèm lý do</t>
+          <t>Câu 'Chưa gán' → đã gán; phát hiện trùng</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -1861,11 +1868,11 @@
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.17</v>
+        <v>0.44</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>test_question_import::test_tagging_locks_used_questions</t>
+          <t>test_question_import::test_bulk_import_then_tag</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr"/>
@@ -1881,17 +1888,17 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Nhập Aiken và Moodle XML</t>
+          <t>Không gán lại CLO câu đã có kết quả</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Tệp .txt Aiken, .xml Moodle</t>
+          <t>Tệp gán CLO cho câu đã dùng</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Đọc đúng</t>
+          <t>Bị bỏ qua kèm lý do</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -1900,11 +1907,11 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>test_question_import::test_aiken_and_moodle_xml</t>
+          <t>test_question_import::test_tagging_locks_used_questions</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr"/>
@@ -1915,22 +1922,22 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>4. Đề thi: ma trận đề, Moodle XML, đề giấy</t>
+          <t>3. Ngân hàng câu hỏi, nhập từ tệp, gán CLO</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Tạo bài KT trực tuyến, xuất Moodle XML</t>
+          <t>Nhập Aiken và Moodle XML</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Tạo bài 20 câu, tải Moodle XML</t>
+          <t>Tệp .txt Aiken, .xml Moodle</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>XML hợp lệ, idnumber QB-n, đáp án đúng fraction 100</t>
+          <t>Đọc đúng</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -1939,11 +1946,11 @@
         </is>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_exam_online_xml</t>
+          <t>test_question_import::test_aiken_and_moodle_xml</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr"/>
@@ -1959,17 +1966,17 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Chặn câu hỏi môn khác/chưa gán CLO</t>
+          <t>Tạo bài KT trực tuyến, xuất Moodle XML</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Tạo bài KT có câu của môn khác hoặc chưa gán CLO</t>
+          <t>Tạo bài 20 câu, tải Moodle XML</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>XML hợp lệ, idnumber QB-n, đáp án đúng fraction 100</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -1978,11 +1985,11 @@
         </is>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_exam_rejects_foreign_question</t>
+          <t>test_api::test_exam_online_xml</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr"/>
@@ -1998,17 +2005,17 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Bài giấy: hai cách (hệ thống / Moodle Offline Quiz)</t>
+          <t>Chặn câu hỏi môn khác/chưa gán CLO</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Sinh mã đề trên hệ thống rồi tạo Offline Quiz và ngược lại</t>
+          <t>Tạo bài KT có câu của môn khác hoặc chưa gán CLO</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Loại trừ nhau (409)</t>
+          <t>422</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2017,11 +2024,11 @@
         </is>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_paper_exam_two_modes</t>
+          <t>test_api::test_exam_rejects_foreign_question</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr"/>
@@ -2037,17 +2044,17 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Sinh đề tự động theo ma trận</t>
+          <t>Bài giấy: hai cách (hệ thống / Moodle Offline Quiz)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Nhập 20 câu, phân bố Bloom cân bằng</t>
+          <t>Sinh mã đề trên hệ thống rồi tạo Offline Quiz và ngược lại</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Phủ đủ chương, CLO; không vượt số câu sẵn có</t>
+          <t>Loại trừ nhau (409)</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2056,11 +2063,11 @@
         </is>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>test_blueprint::test_auto_matrix_covers_chapters_clos_and_respects_bank</t>
+          <t>test_api::test_paper_exam_two_modes</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr"/>
@@ -2076,17 +2083,17 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Báo thiếu câu theo ô ma trận</t>
+          <t>Sinh đề tự động theo ma trận</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Ma trận yêu cầu nhiều hơn ngân hàng</t>
+          <t>Nhập 20 câu, phân bố Bloom cân bằng</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Lỗi rõ ô thiếu, vẫn trả phần chọn được</t>
+          <t>Phủ đủ chương, CLO; không vượt số câu sẵn có</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -2099,7 +2106,7 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>test_blueprint::test_shortage_and_matrix_errors</t>
+          <t>test_blueprint::test_auto_matrix_covers_chapters_clos_and_respects_bank</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr"/>
@@ -2115,17 +2122,17 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra theo chương</t>
+          <t>Báo thiếu câu theo ô ma trận</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Chọn chương 1–2</t>
+          <t>Ma trận yêu cầu nhiều hơn ngân hàng</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Chỉ câu thuộc chương; CLO ngoài phạm vi 'không đo'</t>
+          <t>Lỗi rõ ô thiếu, vẫn trả phần chọn được</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -2138,7 +2145,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>test_blueprint::test_chapter_test_and_fixed_questions</t>
+          <t>test_blueprint::test_shortage_and_matrix_errors</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr"/>
@@ -2154,17 +2161,17 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Chia số câu theo tỷ lệ Bloom</t>
+          <t>Kiểm tra theo chương</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Phần dư lớn nhất có trần</t>
+          <t>Chọn chương 1–2</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Tổng đúng n, không ô nào vượt trần</t>
+          <t>Chỉ câu thuộc chương; CLO ngoài phạm vi 'không đo'</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -2177,7 +2184,7 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>test_blueprint::test_largest_remainder_caps</t>
+          <t>test_blueprint::test_chapter_test_and_fixed_questions</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr"/>
@@ -2193,17 +2200,17 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>API sinh đề theo ma trận</t>
+          <t>Chia số câu theo tỷ lệ Bloom</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Gọi pool và generate qua API</t>
+          <t>Phần dư lớn nhất có trần</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Kết quả, cảnh báo đúng; phân quyền</t>
+          <t>Tổng đúng n, không ô nào vượt trần</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -2212,11 +2219,11 @@
         </is>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>test_blueprint::test_blueprint_api</t>
+          <t>test_blueprint::test_largest_remainder_caps</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr"/>
@@ -2232,17 +2239,17 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Tạo bài kiểm tra ở trang môn học (đề của môn)</t>
+          <t>API sinh đề theo ma trận</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Sinh đề theo ma trận cấp môn rồi lưu đề chưa gắn lớp; gọi tạo Quiz, đồng bộ, thống kê; GV khác; gửi cả lớp và môn</t>
+          <t>Gọi pool và generate qua API</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Đề lưu ở môn; thao tác cần lớp 409 kèm hướng dẫn chọn lớp; Moodle XML được; GV khác 403; 422</t>
+          <t>Kết quả, cảnh báo đúng; phân quyền</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -2251,11 +2258,11 @@
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>test_de_cua_mon::test_course_exam_create_and_blocked_actions</t>
+          <t>test_blueprint::test_blueprint_api</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr"/>
@@ -2271,17 +2278,17 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Giao đề của môn cho lớp HP khi xuất</t>
+          <t>Tạo bài kiểm tra ở trang môn học (đề của môn)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Giao đề giấy cho 2 lớp, sinh mã đề ở bài của lớp, giao lại lớp đã có, xóa đề của môn</t>
+          <t>Sinh đề theo ma trận cấp môn rồi lưu đề chưa gắn lớp; gọi tạo Quiz, đồng bộ, thống kê; GV khác; gửi cả lớp và môn</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Mỗi lớp một bài cùng câu hỏi; không tạo trùng; xóa đề gốc không mất bài của lớp</t>
+          <t>Đề lưu ở môn; thao tác cần lớp 409 kèm hướng dẫn chọn lớp; Moodle XML được; GV khác 403; 422</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -2290,11 +2297,11 @@
         </is>
       </c>
       <c r="G37" s="4" t="n">
-        <v>0.43</v>
+        <v>0.29</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>test_de_cua_mon::test_course_exam_deploy_to_sections</t>
+          <t>test_de_cua_mon::test_course_exam_create_and_blocked_actions</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr"/>
@@ -2310,17 +2317,17 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Dùng đề cho lớp khác, sửa câu/ý, sinh lại mã đề</t>
+          <t>Giao đề của môn cho lớp HP khi xuất</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Sao chép đề sang lớp 02; sửa câu/ý bài nhập điểm; xóa mã đề chưa chấm</t>
+          <t>Giao đề giấy cho 2 lớp, sinh mã đề ở bài của lớp, giao lại lớp đã có, xóa đề của môn</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Đủ câu; GV khác 403; cấu trúc mới đúng</t>
+          <t>Mỗi lớp một bài cùng câu hỏi; không tạo trùng; xóa đề gốc không mất bài của lớp</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -2329,11 +2336,11 @@
         </is>
       </c>
       <c r="G38" s="4" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>test_z_toan_bo_chuc_nang::test_copy_exam_manual_items_and_paper_versions</t>
+          <t>test_de_cua_mon::test_course_exam_deploy_to_sections</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr"/>
@@ -2344,22 +2351,22 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>5. Đồng bộ Moodle, giải xáo trộn, phân tích</t>
+          <t>4. Đề thi: ma trận đề, Moodle XML, đề giấy</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ bài làm khớp điểm Moodle</t>
+          <t>Dùng đề cho lớp khác, sửa câu/ý, sinh lại mã đề</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ Quiz từ CSDL Moodle mô phỏng</t>
+          <t>Sao chép đề sang lớp 02; sửa câu/ý bài nhập điểm; xóa mã đề chưa chấm</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Tổng điểm từng SV = sumgrades của Moodle</t>
+          <t>Đủ câu; GV khác 403; cấu trúc mới đúng</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -2368,11 +2375,11 @@
         </is>
       </c>
       <c r="G39" s="4" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_moodle_sync_matches_moodle_grades</t>
+          <t>test_z_toan_bo_chuc_nang::test_copy_exam_manual_items_and_paper_versions</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr"/>
@@ -2388,17 +2395,17 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Chọn lượt theo cách tính điểm của Quiz</t>
+          <t>Đồng bộ bài làm khớp điểm Moodle</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Quiz cho nhiều lượt: lượt cuối / lượt đầu / điểm cao nhất; lượt xem trước của GV</t>
+          <t>Đồng bộ Quiz từ CSDL Moodle mô phỏng</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Đúng lượt Moodle dùng tính điểm; bỏ lượt xem trước</t>
+          <t>Tổng điểm từng SV = sumgrades của Moodle</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -2411,7 +2418,7 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_moodle_sync_follows_grade_method_and_skips_preview</t>
+          <t>test_api::test_moodle_sync_matches_moodle_grades</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr"/>
@@ -2427,17 +2434,17 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Ghi nhận SV vắng thi</t>
+          <t>Chọn lượt theo cách tính điểm của Quiz</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>SV ghi danh nhưng không làm bài</t>
+          <t>Quiz cho nhiều lượt: lượt cuối / lượt đầu / điểm cao nhất; lượt xem trước của GV</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Lượt absent, không tính vào p/DI</t>
+          <t>Đúng lượt Moodle dùng tính điểm; bỏ lượt xem trước</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -2450,7 +2457,7 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_absent_students_recorded</t>
+          <t>test_api::test_moodle_sync_follows_grade_method_and_skips_preview</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr"/>
@@ -2466,17 +2473,17 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ lại không trùng lặp</t>
+          <t>Ghi nhận SV vắng thi</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ 2 lần liên tiếp</t>
+          <t>SV ghi danh nhưng không làm bài</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Số lượt, kết quả không đổi</t>
+          <t>Lượt absent, không tính vào p/DI</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -2485,11 +2492,11 @@
         </is>
       </c>
       <c r="G42" s="4" t="n">
-        <v>14.15</v>
+        <v>0</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_resync_is_idempotent</t>
+          <t>test_api::test_absent_students_recorded</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr"/>
@@ -2505,17 +2512,17 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Cảnh báo cách tính 'trung bình các lượt'</t>
+          <t>Đồng bộ lại không trùng lặp</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Quiz đặt grademethod = trung bình</t>
+          <t>Đồng bộ 2 lần liên tiếp</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ lượt cuối kèm cảnh báo</t>
+          <t>Số lượt, kết quả không đổi</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -2524,11 +2531,11 @@
         </is>
       </c>
       <c r="G43" s="4" t="n">
-        <v>30.51</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_sync_warns_average_grade_method</t>
+          <t>test_api::test_resync_is_idempotent</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr"/>
@@ -2544,17 +2551,17 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Phát hiện câu bị sửa trên Moodle</t>
+          <t>Cảnh báo cách tính 'trung bình các lượt'</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Đổi số phương án/đáp án trên Moodle rồi đồng bộ</t>
+          <t>Quiz đặt grademethod = trung bình</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>409, không ghi kết quả sai</t>
+          <t>Đồng bộ lượt cuối kèm cảnh báo</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -2563,11 +2570,11 @@
         </is>
       </c>
       <c r="G44" s="4" t="n">
-        <v>23.1</v>
+        <v>16.82</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_sync_stops_when_question_edited_on_moodle</t>
+          <t>test_api::test_sync_warns_average_grade_method</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr"/>
@@ -2583,17 +2590,17 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ bài giấy từ Offline Quiz</t>
+          <t>Phát hiện câu bị sửa trên Moodle</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Kéo kết quả phiếu Moodle đã chấm</t>
+          <t>Đổi số phương án/đáp án trên Moodle rồi đồng bộ</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Đủ bài làm, đúng điểm</t>
+          <t>409, không ghi kết quả sai</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -2602,11 +2609,11 @@
         </is>
       </c>
       <c r="G45" s="4" t="n">
-        <v>0.01</v>
+        <v>8.56</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_paper_sync_reads_moodle_offlinequiz</t>
+          <t>test_api::test_sync_stops_when_question_edited_on_moodle</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr"/>
@@ -2622,17 +2629,17 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Ánh xạ nhóm đề A/B sang mã đề</t>
+          <t>Đồng bộ bài giấy từ Offline Quiz</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ bài giấy 2 nhóm đề</t>
+          <t>Kéo kết quả phiếu Moodle đã chấm</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Mỗi lượt gắn đúng nhóm đề</t>
+          <t>Đủ bài làm, đúng điểm</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -2645,7 +2652,7 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_paper_sync_maps_groups_to_versions</t>
+          <t>test_api::test_paper_sync_reads_moodle_offlinequiz</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr"/>
@@ -2661,17 +2668,17 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Giải xáo trộn theo từng nhóm đề</t>
+          <t>Ánh xạ nhóm đề A/B sang mã đề</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Phương án bị xáo khác nhau giữa nhóm A, B</t>
+          <t>Đồng bộ bài giấy 2 nhóm đề</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Lựa chọn quy về đúng phương án gốc</t>
+          <t>Mỗi lượt gắn đúng nhóm đề</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -2684,7 +2691,7 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_paper_reverse_shuffle_per_group</t>
+          <t>test_api::test_paper_sync_maps_groups_to_versions</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr"/>
@@ -2700,17 +2707,17 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Bài giấy chưa có Offline Quiz</t>
+          <t>Giải xáo trộn theo từng nhóm đề</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ bài giấy chưa liên kết</t>
+          <t>Phương án bị xáo khác nhau giữa nhóm A, B</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>422/409 kèm hướng dẫn</t>
+          <t>Lựa chọn quy về đúng phương án gốc</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -2719,11 +2726,11 @@
         </is>
       </c>
       <c r="G48" s="4" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_paper_sync_requires_offlinequiz</t>
+          <t>test_api::test_paper_reverse_shuffle_per_group</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr"/>
@@ -2739,17 +2746,17 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ lại bài giấy</t>
+          <t>Bài giấy chưa có Offline Quiz</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ bài giấy 2 lần</t>
+          <t>Đồng bộ bài giấy chưa liên kết</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Không trùng lặp</t>
+          <t>422/409 kèm hướng dẫn</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -2758,11 +2765,11 @@
         </is>
       </c>
       <c r="G49" s="4" t="n">
-        <v>7.85</v>
+        <v>0.04</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_paper_resync_is_idempotent</t>
+          <t>test_api::test_paper_sync_requires_offlinequiz</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr"/>
@@ -2778,17 +2785,17 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Phân tích lại, nhật ký, trạng thái và cài cầu nối</t>
+          <t>Đồng bộ lại bài giấy</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Phân tích lại bài, xem nhật ký, trạng thái CSDL Moodle, cài lại cầu nối, minh chứng CLO</t>
+          <t>Đồng bộ bài giấy 2 lần</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Đúng; GV không cài cầu nối</t>
+          <t>Không trùng lặp</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -2797,11 +2804,11 @@
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>0.48</v>
+        <v>4.54</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>test_z_toan_bo_chuc_nang::test_sync_analyze_runs_and_bridge</t>
+          <t>test_api::test_paper_resync_is_idempotent</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr"/>
@@ -2812,22 +2819,22 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>6. Analysis Engine (p, DI, KR-20, CLO, BM6)</t>
+          <t>5. Đồng bộ Moodle, giải xáo trộn, phân tích</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Phát hiện câu hỏi lỗi (DI âm)</t>
+          <t>Phân tích lại, nhật ký, trạng thái và cài cầu nối</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Phân tích bài có câu bẫy</t>
+          <t>Phân tích lại bài, xem nhật ký, trạng thái CSDL Moodle, cài lại cầu nối, minh chứng CLO</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Câu 24 DI âm, phân loại 'Loại bỏ/xem lại'</t>
+          <t>Đúng; GV không cài cầu nối</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
@@ -2836,11 +2843,11 @@
         </is>
       </c>
       <c r="G51" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_item_stats_flags_trap_question</t>
+          <t>test_z_toan_bo_chuc_nang::test_sync_analyze_runs_and_bridge</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr"/>
@@ -2856,17 +2863,17 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Kết quả CLO lớp HP (BM6b)</t>
+          <t>Phát hiện câu hỏi lỗi (DI âm)</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Tính số SV đạt/đánh giá từng CLO</t>
+          <t>Phân tích bài có câu bẫy</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Khớp số liệu tính tay; kết luận Đạt/Không đạt</t>
+          <t>Câu 24 DI âm, phân loại 'Loại bỏ/xem lại'</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -2879,7 +2886,7 @@
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_clo_results_bm6b</t>
+          <t>test_api::test_item_stats_flags_trap_question</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr"/>
@@ -2895,17 +2902,17 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Mức đạt CLO một bài (BM6c)</t>
+          <t>Kết quả CLO lớp HP (BM6b)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Số liệu mẫu của biểu mẫu</t>
+          <t>Tính số SV đạt/đánh giá từng CLO</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Khớp BM6c mẫu</t>
+          <t>Khớp số liệu tính tay; kết luận Đạt/Không đạt</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
@@ -2918,7 +2925,7 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>test_engine::test_bm6c_single_test</t>
+          <t>test_api::test_clo_results_bm6b</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr"/>
@@ -2934,17 +2941,17 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>SV 0 điểm vẫn tính vào mẫu số</t>
+          <t>Mức đạt CLO một bài (BM6c)</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>SV làm bài được 0 điểm</t>
+          <t>Số liệu mẫu của biểu mẫu</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Có trong số SV đánh giá</t>
+          <t>Khớp BM6c mẫu</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -2957,7 +2964,7 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>test_engine::test_bm6d_zero_score_stays_in_denominator</t>
+          <t>test_engine::test_bm6c_single_test</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr"/>
@@ -2973,17 +2980,17 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Cộng dồn nhiều bài (BM6d)</t>
+          <t>SV 0 điểm vẫn tính vào mẫu số</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>CLO đo bởi 2 bài</t>
+          <t>SV làm bài được 0 điểm</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Cộng dồn lượt đánh giá đúng biểu mẫu</t>
+          <t>Có trong số SV đánh giá</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
@@ -2992,11 +2999,11 @@
         </is>
       </c>
       <c r="G55" s="4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>test_engine::test_bm6d_multi_test_aggregation</t>
+          <t>test_engine::test_bm6d_zero_score_stays_in_denominator</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr"/>
@@ -3012,17 +3019,17 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Ngưỡng đạt so sánh ≥</t>
+          <t>Cộng dồn nhiều bài (BM6d)</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Điểm đúng bằng ngưỡng</t>
+          <t>CLO đo bởi 2 bài</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Tính là Đạt</t>
+          <t>Cộng dồn lượt đánh giá đúng biểu mẫu</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
@@ -3031,11 +3038,11 @@
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>test_engine::test_threshold_boundary_is_inclusive</t>
+          <t>test_engine::test_bm6d_multi_test_aggregation</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr"/>
@@ -3051,17 +3058,17 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Điểm CLO có trọng số</t>
+          <t>Ngưỡng đạt so sánh ≥</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Câu đo 2 CLO trọng số 0,5</t>
+          <t>Điểm đúng bằng ngưỡng</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Công thức (3.1) đúng</t>
+          <t>Tính là Đạt</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -3074,7 +3081,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>test_engine::test_weighted_clo_score</t>
+          <t>test_engine::test_threshold_boundary_is_inclusive</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr"/>
@@ -3090,17 +3097,17 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Độ khó p và độ phân biệt DI (27%)</t>
+          <t>Điểm CLO có trọng số</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Dữ liệu mẫu</t>
+          <t>Câu đo 2 CLO trọng số 0,5</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Khớp tính tay</t>
+          <t>Công thức (3.1) đúng</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
@@ -3113,7 +3120,7 @@
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>test_engine::test_p_and_di_kelley</t>
+          <t>test_engine::test_weighted_clo_score</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr"/>
@@ -3129,17 +3136,17 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Bỏ trống tính là sai</t>
+          <t>Độ khó p và độ phân biệt DI (27%)</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Câu bỏ trống</t>
+          <t>Dữ liệu mẫu</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>is_correct = 0</t>
+          <t>Khớp tính tay</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
@@ -3152,7 +3159,7 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>test_engine::test_blank_counts_as_wrong</t>
+          <t>test_engine::test_p_and_di_kelley</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr"/>
@@ -3168,17 +3175,17 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Lộ trình ôn tập cá nhân</t>
+          <t>Bỏ trống tính là sai</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>SV chưa đạt nhiều CLO</t>
+          <t>Câu bỏ trống</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Sắp theo thiếu hụt, chọn đúng chương mất điểm</t>
+          <t>is_correct = 0</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
@@ -3191,7 +3198,7 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>test_engine::test_learning_path_priorities</t>
+          <t>test_engine::test_blank_counts_as_wrong</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr"/>
@@ -3207,17 +3214,17 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Dữ liệu rỗng</t>
+          <t>Lộ trình ôn tập cá nhân</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Bài không có lượt làm</t>
+          <t>SV chưa đạt nhiều CLO</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Không lỗi, trả rỗng</t>
+          <t>Sắp theo thiếu hụt, chọn đúng chương mất điểm</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
@@ -3230,7 +3237,7 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>test_engine::test_empty_inputs</t>
+          <t>test_engine::test_learning_path_priorities</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr"/>
@@ -3246,17 +3253,17 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Độ tin cậy KR-20</t>
+          <t>Dữ liệu rỗng</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Ma trận đúng/sai mẫu</t>
+          <t>Bài không có lượt làm</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Khớp công thức (1.3)</t>
+          <t>Không lỗi, trả rỗng</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
@@ -3265,11 +3272,11 @@
         </is>
       </c>
       <c r="G62" s="4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>test_engine::test_kr20_reliability</t>
+          <t>test_engine::test_empty_inputs</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr"/>
@@ -3285,17 +3292,17 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Đổi ngưỡng đạt → phân tích lại</t>
+          <t>Độ tin cậy KR-20</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Sửa kế hoạch CLO (BM6a)</t>
+          <t>Ma trận đúng/sai mẫu</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Kết quả CLO tính lại ngay</t>
+          <t>Khớp công thức (1.3)</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
@@ -3304,11 +3311,11 @@
         </is>
       </c>
       <c r="G63" s="4" t="n">
-        <v>1.88</v>
+        <v>0.01</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>test_hardening::test_clo_plan_change_reanalyzes</t>
+          <t>test_engine::test_kr20_reliability</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr"/>
@@ -3319,22 +3326,22 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>7. Báo cáo biểu mẫu BM2, BM3, BM6, phân công</t>
+          <t>6. Analysis Engine (p, DI, KR-20, CLO, BM6)</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Nhận xét, cải tiến CLO</t>
+          <t>Đổi ngưỡng đạt → phân tích lại</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Lưu nhận xét BM6a</t>
+          <t>Sửa kế hoạch CLO (BM6a)</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Lưu và đọc lại đúng</t>
+          <t>Kết quả CLO tính lại ngay</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
@@ -3343,11 +3350,11 @@
         </is>
       </c>
       <c r="G64" s="4" t="n">
-        <v>0.01</v>
+        <v>1.19</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_clo_narrative</t>
+          <t>test_hardening::test_clo_plan_change_reanalyzes</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr"/>
@@ -3363,17 +3370,17 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Tổng hợp PLO = cộng dồn PI (BM3c)</t>
+          <t>Nhận xét, cải tiến CLO</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Tổng hợp PLO năm học 2024–2025</t>
+          <t>Lưu nhận xét BM6a</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Số đạt/đánh giá PLO = Σ PI</t>
+          <t>Lưu và đọc lại đúng</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
@@ -3382,11 +3389,11 @@
         </is>
       </c>
       <c r="G65" s="4" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_plo_summary_is_sum_of_pi</t>
+          <t>test_api::test_clo_narrative</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr"/>
@@ -3402,17 +3409,17 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Xuất bộ Biểu mẫu 6 (.xlsx)</t>
+          <t>Tổng hợp PLO = cộng dồn PI (BM3c)</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Tải BM6 của lớp HP</t>
+          <t>Tổng hợp PLO năm học 2024–2025</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Mục lục, BM6a, BM6b, minh chứng; công thức COUNTIF</t>
+          <t>Số đạt/đánh giá PLO = Σ PI</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
@@ -3421,11 +3428,11 @@
         </is>
       </c>
       <c r="G66" s="4" t="n">
-        <v>0.14</v>
+        <v>0.02</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_bm6_workbook</t>
+          <t>test_api::test_plo_summary_is_sum_of_pi</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr"/>
@@ -3441,17 +3448,17 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Minh chứng theo kế hoạch BM6a</t>
+          <t>Xuất bộ Biểu mẫu 6 (.xlsx)</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Trang minh chứng từng CLO</t>
+          <t>Tải BM6 của lớp HP</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Chỉ lấy bài đúng loại minh chứng; tổng khớp BM6b</t>
+          <t>Mục lục, BM6a, BM6b, minh chứng; công thức COUNTIF</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
@@ -3460,11 +3467,11 @@
         </is>
       </c>
       <c r="G67" s="4" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_bm6_evidence_follows_plan_and_matches_bm6b</t>
+          <t>test_api::test_bm6_workbook</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr"/>
@@ -3480,17 +3487,17 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>BM6c riêng từng bài KT</t>
+          <t>Minh chứng theo kế hoạch BM6a</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Xuất BM6c bài quá trình, cuối kỳ; GV khác; bài chưa phân tích</t>
+          <t>Trang minh chứng từng CLO</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Đúng; 403; 409</t>
+          <t>Chỉ lấy bài đúng loại minh chứng; tổng khớp BM6b</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
@@ -3499,11 +3506,11 @@
         </is>
       </c>
       <c r="G68" s="4" t="n">
-        <v>0.23</v>
+        <v>0.14</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_bm6c_per_exam</t>
+          <t>test_api::test_bm6_evidence_follows_plan_and_matches_bm6b</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr"/>
@@ -3519,17 +3526,17 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Xuất BM2/BM3 (.xlsx)</t>
+          <t>BM6c riêng từng bài KT</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Tải tệp tổng hợp CTĐT</t>
+          <t>Xuất BM6c bài quá trình, cuối kỳ; GV khác; bài chưa phân tích</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Có BM2a, BM2b, BM3b, BM3c; GV bị 403</t>
+          <t>Đúng; 403; 409</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
@@ -3538,11 +3545,11 @@
         </is>
       </c>
       <c r="G69" s="4" t="n">
-        <v>0.24</v>
+        <v>0.45</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_bm3_workbook</t>
+          <t>test_api::test_bm6c_per_exam</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr"/>
@@ -3558,17 +3565,17 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Xuất BM2 dạng Word</t>
+          <t>Xuất BM2/BM3 (.xlsx)</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Tải BM2 .docx</t>
+          <t>Tải tệp tổng hợp CTĐT</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Có KẾ HOẠCH và BÁO CÁO TỔNG KẾT</t>
+          <t>Có BM2a, BM2b, BM3b, BM3c; GV bị 403</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
@@ -3577,11 +3584,11 @@
         </is>
       </c>
       <c r="G70" s="4" t="n">
-        <v>0.91</v>
+        <v>0.14</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_bm2_docx</t>
+          <t>test_api::test_bm3_workbook</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr"/>
@@ -3597,17 +3604,17 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Bảng phân công đánh giá PIs</t>
+          <t>Xuất BM2 dạng Word</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Xuất bảng phân công học kỳ</t>
+          <t>Tải BM2 .docx</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Đúng cột như bảng gốc; 404 học kỳ không tồn tại</t>
+          <t>Có KẾ HOẠCH và BÁO CÁO TỔNG KẾT</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
@@ -3616,11 +3623,11 @@
         </is>
       </c>
       <c r="G71" s="4" t="n">
-        <v>0.05</v>
+        <v>1.1</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_assignments_xlsx</t>
+          <t>test_api::test_bm2_docx</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr"/>
@@ -3636,17 +3643,17 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Nhận xét PLO (BM3b)</t>
+          <t>Bảng phân công đánh giá PIs</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Lưu 4 mục nhận xét PLO</t>
+          <t>Xuất bảng phân công học kỳ</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Lưu đúng; GV bị 403</t>
+          <t>Đúng cột như bảng gốc; 404 học kỳ không tồn tại</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
@@ -3655,11 +3662,11 @@
         </is>
       </c>
       <c r="G72" s="4" t="n">
-        <v>0.02</v>
+        <v>0.13</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_plo_narrative</t>
+          <t>test_api::test_assignments_xlsx</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr"/>
@@ -3670,22 +3677,22 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>8. Nhập điểm, gộp bài, phụ đạo</t>
+          <t>7. Báo cáo biểu mẫu BM2, BM3, BM6, phân công</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Đề nhập điểm của môn giao cho lớp</t>
+          <t>Nhận xét PLO (BM3b)</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Khai báo câu/ý gắn CLO ở cấp môn, giao cho lớp 02 rồi nhập điểm</t>
+          <t>Lưu 4 mục nhận xét PLO</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Bảng điểm đủ 35 SV của lớp; nhập điểm ở đề chưa giao bị chặn (409)</t>
+          <t>Lưu đúng; GV bị 403</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
@@ -3694,11 +3701,11 @@
         </is>
       </c>
       <c r="G73" s="4" t="n">
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>test_de_cua_mon::test_course_manual_exam_deploy_and_grade</t>
+          <t>test_api::test_plo_narrative</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr"/>
@@ -3714,17 +3721,17 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Bài nhập điểm: bảng điểm, Excel, phân tích</t>
+          <t>Đề nhập điểm của môn giao cho lớp</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Tạo bài 2 câu/ý gắn CLO, nhập điểm, tải mẫu Excel, nhập lại, phân tích</t>
+          <t>Khai báo câu/ý gắn CLO ở cấp môn, giao cho lớp 02 rồi nhập điểm</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra giới hạn điểm; p, DI, alpha, CLO đúng</t>
+          <t>Bảng điểm đủ 35 SV của lớp; nhập điểm ở đề chưa giao bị chặn (409)</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
@@ -3733,11 +3740,11 @@
         </is>
       </c>
       <c r="G74" s="4" t="n">
-        <v>1.01</v>
+        <v>0.12</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>test_grading::test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_de_cua_mon::test_course_manual_exam_deploy_and_grade</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr"/>
@@ -3753,17 +3760,17 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Tạo bài từ tệp Excel bất kỳ</t>
+          <t>Bài nhập điểm: bảng điểm, Excel, phân tích</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Tệp Excel tự soạn có cột MSSV và cột điểm</t>
+          <t>Tạo bài 2 câu/ý gắn CLO, nhập điểm, tải mẫu Excel, nhập lại, phân tích</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Tạo bài, ghi điểm; SV lạ được ghi danh khi chọn</t>
+          <t>Kiểm tra giới hạn điểm; p, DI, alpha, CLO đúng</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
@@ -3772,11 +3779,11 @@
         </is>
       </c>
       <c r="G75" s="4" t="n">
-        <v>0.34</v>
+        <v>0.74</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>test_grading::test_create_exam_from_any_excel</t>
+          <t>test_grading::test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr"/>
@@ -3792,17 +3799,17 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Gộp 2–3 bài đánh giá CLO/PLO</t>
+          <t>Tạo bài từ tệp Excel bất kỳ</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Gộp bài 2 lớp theo 2 cách; bật/tắt minh chứng BM6</t>
+          <t>Tệp Excel tự soạn có cột MSSV và cột điểm</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Số liệu khớp; PLO theo từng CTĐT; BM6b đổi tương ứng</t>
+          <t>Tạo bài, ghi điểm; SV lạ được ghi danh khi chọn</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
@@ -3811,11 +3818,11 @@
         </is>
       </c>
       <c r="G76" s="4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>test_grading::test_combine_exams_and_evidence_flag</t>
+          <t>test_grading::test_create_exam_from_any_excel</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr"/>
@@ -3831,17 +3838,17 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Phụ đạo theo câu sai</t>
+          <t>Gộp 2–3 bài đánh giá CLO/PLO</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Đếm câu sai từng SV, xem câu sai, tạo bài phụ đạo</t>
+          <t>Gộp bài 2 lớp theo 2 cách; bật/tắt minh chứng BM6</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Số câu sai đúng; bài phụ đạo có câu sai + câu tương tự, không gộp minh chứng</t>
+          <t>Số liệu khớp; PLO theo từng CTĐT; BM6b đổi tương ứng</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
@@ -3850,11 +3857,11 @@
         </is>
       </c>
       <c r="G77" s="4" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>test_grading::test_remedial_flow</t>
+          <t>test_grading::test_combine_exams_and_evidence_flag</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr"/>
@@ -3865,22 +3872,22 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>9. Đề giấy &amp; chấm phiếu trên hệ thống (OMR)</t>
+          <t>8. Nhập điểm, gộp bài, phụ đạo</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Đề giấy trên hệ thống từ đầu đến cuối</t>
+          <t>Phụ đạo theo câu sai</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Sinh 3 mã đề, xuất PDF 1/2 cột, Word, phiếu, đáp án, .zip; tô 6 phiếu (có ảnh nghiêng), chấm, sửa, lưu</t>
+          <t>Đếm câu sai từng SV, xem câu sai, tạo bài phụ đạo</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Đọc đúng MSSV, mã đề, điểm; 34 SV vắng; phân tích xong</t>
+          <t>Số câu sai đúng; bài phụ đạo có câu sai + câu tương tự, không gộp minh chứng</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
@@ -3889,11 +3896,11 @@
         </is>
       </c>
       <c r="G78" s="4" t="n">
-        <v>2.76</v>
+        <v>0.22</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>test_paper::test_system_paper_exam_end_to_end</t>
+          <t>test_grading::test_remedial_flow</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr"/>
@@ -3904,22 +3911,22 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>9. Đề giấy &amp; chấm phiếu trên hệ thống (OMR)</t>
+          <t>8. Nhập điểm, gộp bài, phụ đạo</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Chấm phiếu: gạch chéo, tô 2 ô, nét bút đè ô định vị</t>
+          <t>Theo dõi tiến bộ – trước khi làm bài ôn</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Phiếu tô theo nhiều kiểu</t>
+          <t>Xem bài ôn vừa giao cho 1 SV</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Lấy ô tô kín; cảnh báo tô 2 ô; không lệch phiếu</t>
+          <t>1 SV được giao, chưa làm; có điểm trước, chưa có điểm sau</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -3928,11 +3935,11 @@
         </is>
       </c>
       <c r="G79" s="4" t="n">
-        <v>0.23</v>
+        <v>0.04</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>test_paper::test_omr_crossed_out_and_scribbles</t>
+          <t>test_remedial_progress::test_progress_before_attempt</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr"/>
@@ -3943,22 +3950,22 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>10. Tích hợp Moodle: Web Service, SSO, đồng bộ câu hỏi, liên kết lớp</t>
+          <t>8. Nhập điểm, gộp bài, phụ đạo</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Dữ liệu kết quả gửi sang Moodle</t>
+          <t>Theo dõi tiến bộ – sau khi làm bài ôn</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Xem trước kết quả từng SV</t>
+          <t>SV làm bài ôn, hệ thống tính mức cải thiện</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Radar CLO, nhận định, lộ trình; SV vắng 'chưa đủ bằng chứng'</t>
+          <t>Có điểm sau và mức tăng</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
@@ -3967,11 +3974,11 @@
         </is>
       </c>
       <c r="G80" s="4" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_results_for_moodle</t>
+          <t>test_remedial_progress::test_progress_after_attempt</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr"/>
@@ -3982,22 +3989,22 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>10. Tích hợp Moodle: Web Service, SSO, đồng bộ câu hỏi, liên kết lớp</t>
+          <t>8. Nhập điểm, gộp bài, phụ đạo</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Gửi kết quả khi chưa cấu hình Web Service</t>
+          <t>Giới hạn bài ôn cho đúng SV trên Moodle</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Gửi kết quả khi thiếu token Moodle</t>
+          <t>Danh sách SV được giao chuyển thành tài khoản Moodle</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>502 kèm thông báo</t>
+          <t>Thiếu tài khoản Moodle thì báo lỗi rõ ràng</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
@@ -4006,11 +4013,11 @@
         </is>
       </c>
       <c r="G81" s="4" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_push_requires_moodle_config</t>
+          <t>test_remedial_progress::test_restrict_requires_moodle_accounts</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr"/>
@@ -4021,22 +4028,22 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>10. Tích hợp Moodle: Web Service, SSO, đồng bộ câu hỏi, liên kết lớp</t>
+          <t>8. Nhập điểm, gộp bài, phụ đạo</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Chỉ công bố bài đã phân tích</t>
+          <t>Ôn tập theo nhóm sinh viên yếu từng chương</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Công bố bài chưa phân tích</t>
+          <t>Xem danh sách chương có SV yếu, chọn chương rồi tạo bài kiểm tra lại cho nhóm đó</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>Có danh sách chương + SV; không còn CLO riêng từng SV; bài ôn chỉ gồm câu của chương đã chọn</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
@@ -4049,7 +4056,7 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>test_api::test_publish_requires_analyzed</t>
+          <t>test_remedial_progress::test_overview_theo_chuong_va_loc_chuong</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr"/>
@@ -4060,22 +4067,22 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>10. Tích hợp Moodle: Web Service, SSO, đồng bộ câu hỏi, liên kết lớp</t>
+          <t>9. Đề giấy &amp; chấm phiếu trên hệ thống (OMR)</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Đưa khóa học Moodle mới vào hệ thống</t>
+          <t>Đề giấy trên hệ thống từ đầu đến cuối</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Khóa học GV là giảng viên trên Moodle</t>
+          <t>Sinh 3 mã đề, xuất PDF 1/2 cột, Word, phiếu, đáp án, .zip; tô 6 phiếu (có ảnh nghiêng), chấm, sửa, lưu</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Tạo lớp HP, gắn khóa, lấy danh sách SV</t>
+          <t>Đọc đúng MSSV, mã đề, điểm; 34 SV vắng; phân tích xong</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
@@ -4084,11 +4091,11 @@
         </is>
       </c>
       <c r="G83" s="4" t="n">
-        <v>0.25</v>
+        <v>1.93</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>test_courses::test_import_moodle_course</t>
+          <t>test_paper::test_system_paper_exam_end_to_end</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr"/>
@@ -4099,22 +4106,22 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>10. Tích hợp Moodle: Web Service, SSO, đồng bộ câu hỏi, liên kết lớp</t>
+          <t>9. Đề giấy &amp; chấm phiếu trên hệ thống (OMR)</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Chỉ liên kết Quiz của khóa mình dạy</t>
+          <t>Chấm phiếu: gạch chéo, tô 2 ô, nét bút đè ô định vị</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Liên kết Quiz của khóa học khác</t>
+          <t>Phiếu tô theo nhiều kiểu</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>403/409</t>
+          <t>Lấy ô tô kín; cảnh báo tô 2 ô; không lệch phiếu</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
@@ -4123,11 +4130,11 @@
         </is>
       </c>
       <c r="G84" s="4" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>test_hardening::test_link_quiz_must_belong_to_teacher_course</t>
+          <t>test_paper::test_omr_crossed_out_and_scribbles</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr"/>
@@ -4143,17 +4150,17 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Đăng nhập một lần từ Moodle</t>
+          <t>Dữ liệu kết quả gửi sang Moodle</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Vé SSO hợp lệ; dùng lại vé</t>
+          <t>Xem trước kết quả từng SV</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Vào thẳng lớp HP; vé dùng lại bị từ chối</t>
+          <t>Radar CLO, nhận định, lộ trình; SV vắng 'chưa đủ bằng chứng'</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
@@ -4162,11 +4169,11 @@
         </is>
       </c>
       <c r="G85" s="4" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>test_sso::test_teacher_sso_and_replay</t>
+          <t>test_api::test_results_for_moodle</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr"/>
@@ -4182,17 +4189,17 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Từ chối vé SSO sai</t>
+          <t>Gửi kết quả khi chưa cấu hình Web Service</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Sai chữ ký, hết hạn, sai nơi phát hành</t>
+          <t>Gửi kết quả khi thiếu token Moodle</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>502 kèm thông báo</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
@@ -4201,11 +4208,11 @@
         </is>
       </c>
       <c r="G86" s="4" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>test_sso::test_sso_rejects_bad_tickets</t>
+          <t>test_api::test_push_requires_moodle_config</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr"/>
@@ -4221,17 +4228,17 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>SSO không nâng quyền</t>
+          <t>Chỉ công bố bài đã phân tích</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Vé ghi role admin cho tài khoản GV</t>
+          <t>Công bố bài chưa phân tích</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Giữ quyền GV</t>
+          <t>409</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
@@ -4240,11 +4247,11 @@
         </is>
       </c>
       <c r="G87" s="4" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>test_sso::test_sso_never_escalates</t>
+          <t>test_api::test_publish_requires_analyzed</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr"/>
@@ -4260,17 +4267,17 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>SSO tạo tài khoản GV đã khai báo</t>
+          <t>Đưa khóa học Moodle mới vào hệ thống</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>GV có hồ sơ nhưng chưa có tài khoản</t>
+          <t>Khóa học GV là giảng viên trên Moodle</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Tạo tài khoản, gắn hồ sơ</t>
+          <t>Tạo lớp HP, gắn khóa, lấy danh sách SV</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
@@ -4279,11 +4286,11 @@
         </is>
       </c>
       <c r="G88" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>test_sso::test_sso_provisions_declared_lecturer</t>
+          <t>test_courses::test_import_moodle_course</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr"/>
@@ -4299,17 +4306,17 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Liên kết mã lớp ⇄ khóa học Moodle</t>
+          <t>Chỉ liên kết Quiz của khóa mình dạy</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Tự nối theo shortname, nối cả môn, gắn thủ công</t>
+          <t>Liên kết Quiz của khóa học khác</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Chỉ nối khi GV là giảng viên khóa; chặn trùng</t>
+          <t>403/409</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
@@ -4318,11 +4325,11 @@
         </is>
       </c>
       <c r="G89" s="4" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>test_z_toan_bo_chuc_nang::test_link_section_with_moodle_both_ways</t>
+          <t>test_hardening::test_link_quiz_must_belong_to_teacher_course</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr"/>
@@ -4338,17 +4345,17 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Web Service: Quiz, Offline Quiz, công bố</t>
+          <t>Đăng nhập một lần từ Moodle</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Tạo Quiz, tạo đề giấy, trạng thái, xử lý phiếu, tải tệp/.zip, công bố, gửi kết quả, trạng thái WS</t>
+          <t>Vé SSO hợp lệ; dùng lại vé</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Đúng tham số gửi Moodle; không lộ token; 40 kết quả</t>
+          <t>Vào thẳng lớp HP; vé dùng lại bị từ chối</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
@@ -4357,11 +4364,11 @@
         </is>
       </c>
       <c r="G90" s="4" t="n">
-        <v>0.46</v>
+        <v>0.01</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>test_z_toan_bo_chuc_nang::test_moodle_web_service_flows</t>
+          <t>test_sso::test_teacher_sso_and_replay</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr"/>
@@ -4377,17 +4384,17 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ ngân hàng câu hỏi hai chiều</t>
+          <t>Từ chối vé SSO sai</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Đẩy câu mới, nhập câu soạn trên Moodle, Moodle sửa (phiên bản 2) → kéo về</t>
+          <t>Sai chữ ký, hết hạn, sai nơi phát hành</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Trạng thái đúng từng bước; câu có kết quả không bị ghi đè</t>
+          <t>401</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
@@ -4396,11 +4403,11 @@
         </is>
       </c>
       <c r="G91" s="4" t="n">
-        <v>0.65</v>
+        <v>0.01</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>test_z_toan_bo_chuc_nang::test_question_bank_two_way_sync</t>
+          <t>test_sso::test_sso_rejects_bad_tickets</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr"/>
@@ -4411,22 +4418,22 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>11. Thống kê lớp, hồ sơ sinh viên</t>
+          <t>10. Tích hợp Moodle: Web Service, SSO, đồng bộ câu hỏi, liên kết lớp</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Thống kê lớp học phần</t>
+          <t>SSO không nâng quyền</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Chỉ số tổng quan, CLO, Bloom, chương cần ôn, bản đồ nhiệt</t>
+          <t>Vé ghi role admin cho tài khoản GV</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Khớp BM6</t>
+          <t>Giữ quyền GV</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
@@ -4435,11 +4442,11 @@
         </is>
       </c>
       <c r="G92" s="4" t="n">
-        <v>0.24</v>
+        <v>0.02</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>test_insights::test_section_stats</t>
+          <t>test_sso::test_sso_never_escalates</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr"/>
@@ -4450,22 +4457,22 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>11. Thống kê lớp, hồ sơ sinh viên</t>
+          <t>10. Tích hợp Moodle: Web Service, SSO, đồng bộ câu hỏi, liên kết lớp</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Hồ sơ từng sinh viên</t>
+          <t>SSO tạo tài khoản GV đã khai báo</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Điểm, thứ hạng, CLO qua các bài, phần cần học lại</t>
+          <t>GV có hồ sơ nhưng chưa có tài khoản</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Đúng số liệu</t>
+          <t>Tạo tài khoản, gắn hồ sơ</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
@@ -4474,11 +4481,11 @@
         </is>
       </c>
       <c r="G93" s="4" t="n">
-        <v>0.22</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>test_insights::test_student_profile</t>
+          <t>test_sso::test_sso_provisions_declared_lecturer</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr"/>
@@ -4489,22 +4496,22 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>11. Thống kê lớp, hồ sơ sinh viên</t>
+          <t>10. Tích hợp Moodle: Web Service, SSO, đồng bộ câu hỏi, liên kết lớp</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Phân quyền hồ sơ SV</t>
+          <t>Liên kết mã lớp ⇄ khóa học Moodle</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>GV khác, token SV</t>
+          <t>Tự nối theo shortname, nối cả môn, gắn thủ công</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>Chỉ nối khi GV là giảng viên khóa; chặn trùng</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
@@ -4513,11 +4520,11 @@
         </is>
       </c>
       <c r="G94" s="4" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>test_insights::test_profile_access</t>
+          <t>test_z_toan_bo_chuc_nang::test_link_section_with_moodle_both_ways</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr"/>
@@ -4528,22 +4535,22 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>12. Nâng cấp CSDL, cầu nối</t>
+          <t>10. Tích hợp Moodle: Web Service, SSO, đồng bộ câu hỏi, liên kết lớp</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Cầu nối khi Moodle chưa cài Offline Quiz</t>
+          <t>Web Service: Quiz, Offline Quiz, công bố</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Cài cầu nối</t>
+          <t>Tạo Quiz, tạo đề giấy, trạng thái, xử lý phiếu, tải tệp/.zip, công bố, gửi kết quả, trạng thái WS</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Vẫn chạy cho Quiz</t>
+          <t>Đúng tham số gửi Moodle; không lộ token; 40 kết quả</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
@@ -4552,11 +4559,11 @@
         </is>
       </c>
       <c r="G95" s="4" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>test_upgrade::test_bridge_without_offlinequiz_plugin</t>
+          <t>test_z_toan_bo_chuc_nang::test_moodle_web_service_flows</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr"/>
@@ -4567,22 +4574,22 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>12. Nâng cấp CSDL, cầu nối</t>
+          <t>10. Tích hợp Moodle: Web Service, SSO, đồng bộ câu hỏi, liên kết lớp</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Nâng cấp CSDL phiên bản cũ</t>
+          <t>Đồng bộ ngân hàng câu hỏi hai chiều</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>CSDL thiếu cột mới, CHECK cũ</t>
+          <t>Đẩy câu mới, nhập câu soạn trên Moodle, Moodle sửa (phiên bản 2) → kéo về</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Tự thêm cột, thay CHECK, nạp CTĐT 2026</t>
+          <t>Trạng thái đúng từng bước; câu có kết quả không bị ghi đè</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
@@ -4591,11 +4598,11 @@
         </is>
       </c>
       <c r="G96" s="4" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>test_upgrade::test_upgrade_old_database_adds_offlinequiz_column</t>
+          <t>test_z_toan_bo_chuc_nang::test_question_bank_two_way_sync</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr"/>
@@ -4606,22 +4613,22 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+          <t>11. Thống kê lớp, hồ sơ sinh viên</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Tính thời gian trả lời từng câu</t>
+          <t>Thống kê lớp học phần</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Dãy thời điểm chọn đáp án; nhiều câu cùng một trang (cùng thời điểm)</t>
+          <t>Chỉ số tổng quan, CLO, Bloom, chương cần ôn, bản đồ nhiệt</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Thời gian = khoảng cách tới lần chọn trước; câu cùng trang chia đều; báo độ phân giải theo trang</t>
+          <t>Khớp BM6</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
@@ -4630,11 +4637,11 @@
         </is>
       </c>
       <c r="G97" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>test_timing::test_response_time_split_and_page_resolution</t>
+          <t>test_insights::test_section_stats</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr"/>
@@ -4645,22 +4652,22 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+          <t>11. Thống kê lớp, hồ sơ sinh viên</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ thời điểm chọn đáp án từ Moodle</t>
+          <t>Hồ sơ từng sinh viên</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ Quiz có giới hạn 45 phút, tự nộp khi hết giờ</t>
+          <t>Điểm, thứ hạng, CLO qua các bài, phần cần học lại</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Lưu lần chọn đầu/cuối, số lần lưu từng câu; giới hạn thời gian; lượt hết giờ tự nộp</t>
+          <t>Đúng số liệu</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -4669,11 +4676,11 @@
         </is>
       </c>
       <c r="G98" s="4" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>test_timing::test_sync_stores_answer_times</t>
+          <t>test_insights::test_student_profile</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr"/>
@@ -4684,22 +4691,22 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+          <t>11. Thống kê lớp, hồ sơ sinh viên</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Cảnh báo SV chọn đại / chọn xong để hết giờ</t>
+          <t>Phân quyền hồ sơ SV</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Dữ liệu có 2 SV chọn ~20 câu trong 1 phút và 2 SV chọn xong không nộp chờ hết giờ</t>
+          <t>GV khác, token SV</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Đúng 4 SV bị cảnh báo đúng loại; SV bình thường không bị gắn cờ; số cảnh báo hiện ở danh sách bài KT</t>
+          <t>403</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
@@ -4708,11 +4715,11 @@
         </is>
       </c>
       <c r="G99" s="4" t="n">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>test_timing::test_timing_report_flags_planted_students</t>
+          <t>test_insights::test_profile_access</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr"/>
@@ -4723,38 +4730,481 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
+          <t>12. Nâng cấp CSDL, cầu nối</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>Cầu nối khi Moodle chưa cài Offline Quiz</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>Cài cầu nối</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>Vẫn chạy cho Quiz</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>test_upgrade::test_bridge_without_offlinequiz_plugin</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>12. Nâng cấp CSDL, cầu nối</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>Nâng cấp CSDL phiên bản cũ</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>CSDL thiếu cột mới, CHECK cũ</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>Tự thêm cột, thay CHECK, nạp CTĐT 2026</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>test_upgrade::test_upgrade_old_database_adds_offlinequiz_column</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
           <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>test_seed_backfilled_clo_pi</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr"/>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>test_clo_pi::test_seed_backfilled_clo_pi</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>test_clo_pi_mapping_derives_plo</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr"/>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>test_clo_pi::test_clo_pi_mapping_derives_plo</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>test_backfill_from_legacy_plo</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr"/>
+      <c r="E104" s="4" t="inlineStr"/>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>test_clo_pi::test_backfill_from_legacy_plo</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>test_question_outcome_tree</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr"/>
+      <c r="E105" s="4" t="inlineStr"/>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>test_clo_pi::test_question_outcome_tree</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>test_demo_syllabus_approved</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr"/>
+      <c r="E106" s="4" t="inlineStr"/>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>test_syllabus_versions::test_demo_syllabus_approved</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>test_syllabus_version_flow</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr"/>
+      <c r="E107" s="4" t="inlineStr"/>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>test_syllabus_versions::test_syllabus_version_flow</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>test_outline_detail</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr"/>
+      <c r="E108" s="4" t="inlineStr"/>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>test_syllabus_versions::test_outline_detail</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>test_new_course_without_syllabus</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr"/>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>test_syllabus_versions::test_new_course_without_syllabus</t>
+        </is>
+      </c>
+      <c r="I109" s="4" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>Tính thời gian trả lời từng câu</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Dãy thời điểm chọn đáp án; nhiều câu cùng một trang (cùng thời điểm)</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>Thời gian = khoảng cách tới lần chọn trước; câu cùng trang chia đều; báo độ phân giải theo trang</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>test_timing::test_response_time_split_and_page_resolution</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Đồng bộ thời điểm chọn đáp án từ Moodle</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Đồng bộ Quiz có giới hạn 45 phút, tự nộp khi hết giờ</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lần chọn đầu/cuối, số lần lưu từng câu; giới hạn thời gian; lượt hết giờ tự nộp</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>test_timing::test_sync_stores_answer_times</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>Cảnh báo SV chọn đại / chọn xong để hết giờ</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>Dữ liệu có 2 SV chọn ~20 câu trong 1 phút và 2 SV chọn xong không nộp chờ hết giờ</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>Đúng 4 SV bị cảnh báo đúng loại; SV bình thường không bị gắn cờ; số cảnh báo hiện ở danh sách bài KT</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>test_timing::test_timing_report_flags_planted_students</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
         <is>
           <t>Đổi ngưỡng, diễn biến từng SV, xuất Excel</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr">
+      <c r="D113" s="4" t="inlineStr">
         <is>
           <t>Gửi ngưỡng tùy chỉnh / sai; xem diễn biến 1 SV; tải Excel; bài giấy</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
+      <c r="E113" s="4" t="inlineStr">
         <is>
           <t>Kết quả theo ngưỡng; ngưỡng sai 422; SV không làm 404; Excel 2 sheet; bài giấy báo không áp dụng</t>
         </is>
       </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>ĐẠT</t>
-        </is>
-      </c>
-      <c r="G100" s="4" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H100" s="4" t="inlineStr">
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
         <is>
           <t>test_timing::test_timing_thresholds_timeline_and_export</t>
         </is>
       </c>
-      <c r="I100" s="4" t="inlineStr"/>
+      <c r="I113" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4767,7 +5217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5232,7 +5682,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>test_new_course_setup_flow, test_programs_ctdt_2026</t>
+          <t>test_demo_syllabus_approved, test_new_course_setup_flow, test_new_course_without_syllabus, test_outline_detail, test_programs_ctdt_2026, test_syllabus_version_flow</t>
         </is>
       </c>
     </row>
@@ -5247,17 +5697,17 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>/api/semesters</t>
+          <t>/api/courses/{cid}/syllabus.pdf</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Danh mục &amp; kế hoạch đo lường</t>
+          <t>Chương trình đào tạo &amp; đề cương học phần</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>semesters</t>
+          <t>Đề cương chi tiết dạng PDF theo bố cục biểu mẫu in để ký (quốc hiệu, các mục đánh số, chỗ ký tên).</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -5267,7 +5717,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>test_auth_me_and_catalogs</t>
+          <t>test_syllabus_pdf_mau_in</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5732,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>/api/bloom-levels</t>
+          <t>/api/semesters</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -5292,7 +5742,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>bloom</t>
+          <t>semesters</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -5317,7 +5767,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>/api/lecturers</t>
+          <t>/api/bloom-levels</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -5327,7 +5777,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>lecturers</t>
+          <t>bloom</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -5347,12 +5797,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>/api/plos/{plo_id}</t>
+          <t>/api/lecturers</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -5362,7 +5812,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>update_plo</t>
+          <t>lecturers</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -5372,7 +5822,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>test_programs_plo_and_pi_plans</t>
+          <t>test_auth_me_and_catalogs</t>
         </is>
       </c>
     </row>
@@ -5382,12 +5832,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>/api/pi-plans</t>
+          <t>/api/plos/{plo_id}</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -5397,7 +5847,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>pi_plans</t>
+          <t>update_plo</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -5407,7 +5857,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>test_program_structure, test_programs_plo_and_pi_plans</t>
+          <t>test_programs_plo_and_pi_plans</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5867,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -5432,7 +5882,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>create_pi_plan</t>
+          <t>pi_plans</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -5442,7 +5892,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>test_programs_plo_and_pi_plans</t>
+          <t>test_program_structure, test_programs_plo_and_pi_plans</t>
         </is>
       </c>
     </row>
@@ -5452,12 +5902,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>/api/pi-plans/{plan_id}</t>
+          <t>/api/pi-plans</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -5467,7 +5917,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>update_pi_plan</t>
+          <t>create_pi_plan</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -5487,7 +5937,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -5502,7 +5952,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>delete_pi_plan</t>
+          <t>update_pi_plan</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -5522,12 +5972,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>/api/assignments</t>
+          <t>/api/pi-plans/{plan_id}</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -5537,7 +5987,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>assignments</t>
+          <t>delete_pi_plan</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -5547,7 +5997,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>test_assignment_all_supervisors</t>
+          <t>test_programs_plo_and_pi_plans</t>
         </is>
       </c>
     </row>
@@ -5557,7 +6007,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -5572,7 +6022,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Phân công đánh giá PI: chọn một GV, hoặc all_supervisors = true cho môn không có GV phụ trách riêng (TLCN, KLTN).</t>
+          <t>assignments</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -5592,12 +6042,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>/api/assignments/{aid}</t>
+          <t>/api/assignments</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -5607,7 +6057,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>delete_assignment</t>
+          <t>Phân công đánh giá PI: chọn một GV, hoặc all_supervisors = true cho môn không có GV phụ trách riêng (TLCN, KLTN).</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -5627,12 +6077,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>/api/courses</t>
+          <t>/api/assignments/{aid}</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -5642,7 +6092,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>courses</t>
+          <t>delete_assignment</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -5652,7 +6102,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>test_auth_me_and_catalogs</t>
+          <t>test_assignment_all_supervisors</t>
         </is>
       </c>
     </row>
@@ -5667,7 +6117,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{cid}</t>
+          <t>/api/courses</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -5677,7 +6127,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Đề cương môn (CLO, ma trận CLO–PLO, kế hoạch đo) là thông tin công khai trong trường – mọi tài khoản đều xem được.</t>
+          <t>courses</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -5687,7 +6137,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>test_course_manual_exam_deploy_and_grade, test_new_course_setup_flow</t>
+          <t>test_auth_me_and_catalogs, test_syllabus_pdf_mau_in</t>
         </is>
       </c>
     </row>
@@ -5697,12 +6147,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>/api/clos</t>
+          <t>/api/courses/{cid}</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -5712,7 +6162,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>CLO do Bộ môn quản lý theo CTĐT – giảng viên chỉ xem (góp ý 15/10).</t>
+          <t>Đề cương môn (CLO, ma trận CLO–PLO, kế hoạch đo) là thông tin công khai trong trường – mọi tài khoản đều xem được.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -5722,7 +6172,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>test_clo_lifecycle_cancel_question_and_template, test_new_course_setup_flow</t>
+          <t>test_clo_pi_mapping_derives_plo, test_course_manual_exam_deploy_and_grade, test_new_course_setup_flow, test_outline_detail</t>
         </is>
       </c>
     </row>
@@ -5732,12 +6182,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>/api/clo-plans</t>
+          <t>/api/clos</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -5747,7 +6197,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>upsert_clo_plan</t>
+          <t>CLO do Bộ môn quản lý theo CTĐT – giảng viên chỉ xem (góp ý 15/10).</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -5757,7 +6207,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>test_clo_plan_change_reanalyzes</t>
+          <t>test_backfill_from_legacy_plo, test_clo_lifecycle_cancel_question_and_template, test_clo_pi_mapping_derives_plo, test_new_course_setup_flow</t>
         </is>
       </c>
     </row>
@@ -5767,12 +6217,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections</t>
+          <t>/api/clo-plans</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -5782,7 +6232,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>class_sections</t>
+          <t>upsert_clo_plan</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -5792,7 +6242,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>test_aiken_and_moodle_xml, test_bulk_import_then_tag, test_course_exam_create_and_blocked_actions, test_course_exam_deploy_to_sections, test_course_manual_exam_deploy_and_grade, test_import_moodle_course</t>
+          <t>test_clo_plan_change_reanalyzes</t>
         </is>
       </c>
     </row>
@@ -5807,7 +6257,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/students</t>
+          <t>/api/class-sections</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -5817,7 +6267,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>section_students</t>
+          <t>class_sections</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -5827,7 +6277,7 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>test_profile_access</t>
+          <t>test_aiken_and_moodle_xml, test_bulk_import_then_tag, test_course_exam_create_and_blocked_actions, test_course_exam_deploy_to_sections, test_course_manual_exam_deploy_and_grade, test_import_moodle_course</t>
         </is>
       </c>
     </row>
@@ -5837,12 +6287,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/students/import</t>
+          <t>/api/class-sections/{cs_id}/students</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -5852,7 +6302,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Nhập danh sách lớp HP từ CSV: student_code, full_name, class_name (UTF-8/UTF-8 BOM/Windows-1258; dấu , hoặc ;).</t>
+          <t>section_students</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -5862,7 +6312,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>test_import_students_csv_semicolon</t>
+          <t>test_profile_access</t>
         </is>
       </c>
     </row>
@@ -5877,17 +6327,17 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>/api/courses</t>
+          <t>/api/class-sections/{cs_id}/students/import</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>UC-12 Học phần, chương, CLO, lớp học phần</t>
+          <t>Danh mục &amp; kế hoạch đo lường</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>create_course</t>
+          <t>Nhập danh sách lớp HP từ CSV: student_code, full_name, class_name (UTF-8/UTF-8 BOM/Windows-1258; dấu , hoặc ;).</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -5897,7 +6347,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>test_new_course_setup_flow</t>
+          <t>test_import_students_csv_semicolon</t>
         </is>
       </c>
     </row>
@@ -5907,12 +6357,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{cid}</t>
+          <t>/api/courses</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -5922,7 +6372,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Thông tin học phần (đề cương) do Bộ môn quản lý – giảng viên chỉ xem.</t>
+          <t>create_course</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -5932,7 +6382,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>test_new_course_setup_flow</t>
+          <t>test_backfill_from_legacy_plo, test_clo_pi_mapping_derives_plo, test_new_course_setup_flow, test_new_course_without_syllabus</t>
         </is>
       </c>
     </row>
@@ -5942,12 +6392,12 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{cid}/setup</t>
+          <t>/api/courses/{cid}</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -5957,7 +6407,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Tình trạng khai báo của học phần: những bước đã xong / còn thiếu trước khi ra đề và đo CĐR.</t>
+          <t>Thông tin học phần (đề cương) do Bộ môn quản lý – giảng viên chỉ xem.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -5977,12 +6427,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{cid}/outlines</t>
+          <t>/api/courses/{cid}/setup</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -5992,7 +6442,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>create_outline</t>
+          <t>Tình trạng khai báo của học phần: những bước đã xong / còn thiếu trước khi ra đề và đo CĐR.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -6002,7 +6452,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>test_new_course_setup_flow</t>
+          <t>test_demo_syllabus_approved, test_new_course_setup_flow</t>
         </is>
       </c>
     </row>
@@ -6012,12 +6462,12 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>/api/outlines/{oid}</t>
+          <t>/api/courses/{cid}/outlines</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -6027,7 +6477,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>update_outline</t>
+          <t>create_outline</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -6047,7 +6497,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -6062,7 +6512,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>delete_outline</t>
+          <t>update_outline</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -6072,7 +6522,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>test_new_course_setup_flow</t>
+          <t>test_new_course_setup_flow, test_outline_detail</t>
         </is>
       </c>
     </row>
@@ -6082,12 +6532,12 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>/api/clos/{clo_id}</t>
+          <t>/api/outlines/{oid}</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -6097,7 +6547,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>update_clo</t>
+          <t>delete_outline</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -6117,7 +6567,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -6132,7 +6582,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>delete_clo</t>
+          <t>update_clo</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -6142,7 +6592,7 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>test_clo_lifecycle_cancel_question_and_template</t>
+          <t>test_clo_pi_mapping_derives_plo, test_new_course_setup_flow</t>
         </is>
       </c>
     </row>
@@ -6152,12 +6602,12 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections</t>
+          <t>/api/clos/{clo_id}</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -6167,7 +6617,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>create_section</t>
+          <t>delete_clo</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -6177,7 +6627,7 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>test_new_course_setup_flow</t>
+          <t>test_clo_lifecycle_cancel_question_and_template</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6637,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}</t>
+          <t>/api/class-sections</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -6202,7 +6652,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>update_section</t>
+          <t>create_section</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -6222,7 +6672,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -6237,7 +6687,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>delete_section</t>
+          <t>update_section</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -6247,7 +6697,7 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>test_import_moodle_course, test_new_course_setup_flow</t>
+          <t>test_new_course_setup_flow</t>
         </is>
       </c>
     </row>
@@ -6257,12 +6707,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>/api/moodle/my-courses</t>
+          <t>/api/class-sections/{cs_id}</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -6272,7 +6722,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Khóa học trên Moodle của GV (Bộ môn: mọi khóa học) kèm lớp HP đã gắn, hoặc gợi ý môn học / học kỳ / GV để đưa vào hệ thống.</t>
+          <t>delete_section</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -6282,7 +6732,7 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>test_import_moodle_course</t>
+          <t>test_import_moodle_course, test_new_course_setup_flow</t>
         </is>
       </c>
     </row>
@@ -6292,12 +6742,12 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>/api/moodle/courses/{mid}/import</t>
+          <t>/api/moodle/my-courses</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -6307,7 +6757,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Tạo lớp HP từ một khóa học Moodle và lấy danh sách SV đang ghi danh. GV chỉ đưa vào khóa học mình là giảng viên</t>
+          <t>Khóa học trên Moodle của GV (Bộ môn: mọi khóa học) kèm lớp HP đã gắn, hoặc gợi ý môn học / học kỳ / GV để đưa vào hệ thống.</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -6332,7 +6782,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/moodle-roster</t>
+          <t>/api/moodle/courses/{mid}/import</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -6342,7 +6792,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Cập nhật danh sách SV của lớp HP theo ghi danh hiện tại của khóa học Moodle đã gắn (chỉ thêm, không xóa).</t>
+          <t>Tạo lớp HP từ một khóa học Moodle và lấy danh sách SV đang ghi danh. GV chỉ đưa vào khóa học mình là giảng viên</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -6367,7 +6817,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/moodle-autolink</t>
+          <t>/api/class-sections/{cs_id}/moodle-roster</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -6377,7 +6827,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>moodle_autolink</t>
+          <t>Cập nhật danh sách SV của lớp HP theo ghi danh hiện tại của khóa học Moodle đã gắn (chỉ thêm, không xóa).</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -6387,7 +6837,7 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>test_link_section_with_moodle_both_ways</t>
+          <t>test_import_moodle_course</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6852,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{cid}/moodle-sync-sections</t>
+          <t>/api/class-sections/{cs_id}/moodle-autolink</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -6412,7 +6862,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Một lần bấm cho cả môn: gắn các lớp HP (của GV) với khóa học Moodle trùng mã lớp và cập nhật danh sách SV từ Moodle.</t>
+          <t>moodle_autolink</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -6432,22 +6882,22 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>/api/questions/import-template</t>
+          <t>/api/courses/{cid}/moodle-sync-sections</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>UC-01 Nhập câu hỏi &amp; gán CLO từ file</t>
+          <t>UC-12 Học phần, chương, CLO, lớp học phần</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>import_template</t>
+          <t>Một lần bấm cho cả môn: gắn các lớp HP (của GV) với khóa học Moodle trùng mã lớp và cập nhật danh sách SV từ Moodle.</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -6457,7 +6907,7 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>test_clo_lifecycle_cancel_question_and_template</t>
+          <t>test_link_section_with_moodle_both_ways</t>
         </is>
       </c>
     </row>
@@ -6467,12 +6917,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>/api/questions/import</t>
+          <t>/api/questions/import-template</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -6482,7 +6932,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>import_questions</t>
+          <t>import_template</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -6492,7 +6942,7 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>test_aiken_and_moodle_xml, test_bulk_import_then_tag</t>
+          <t>test_clo_lifecycle_cancel_question_and_template</t>
         </is>
       </c>
     </row>
@@ -6502,12 +6952,12 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>/api/questions/tagging-template</t>
+          <t>/api/questions/import</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -6517,7 +6967,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>tagging_template</t>
+          <t>import_questions</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -6527,7 +6977,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>test_bulk_import_then_tag</t>
+          <t>test_aiken_and_moodle_xml, test_bulk_import_then_tag</t>
         </is>
       </c>
     </row>
@@ -6537,12 +6987,12 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>/api/questions/tagging-import</t>
+          <t>/api/questions/tagging-template</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -6552,7 +7002,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>tagging_import</t>
+          <t>tagging_template</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
@@ -6562,7 +7012,7 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>test_bulk_import_then_tag, test_tagging_locks_used_questions</t>
+          <t>test_bulk_import_then_tag</t>
         </is>
       </c>
     </row>
@@ -6572,22 +7022,22 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>/api/questions</t>
+          <t>/api/questions/tagging-import</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>UC-01 Ngân hàng câu hỏi</t>
+          <t>UC-01 Nhập câu hỏi &amp; gán CLO từ file</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>list_questions</t>
+          <t>tagging_import</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -6597,7 +7047,7 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>test_assignment_all_supervisors, test_bulk_import_then_tag, test_copy_exam_manual_items_and_paper_versions, test_course_level_access, test_manual_exam_grid_excel_and_analysis, test_moodle_web_service_flows</t>
+          <t>test_bulk_import_then_tag, test_tagging_locks_used_questions</t>
         </is>
       </c>
     </row>
@@ -6612,7 +7062,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>/api/questions/{qid}</t>
+          <t>/api/questions</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -6622,7 +7072,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>get_question</t>
+          <t>list_questions</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
@@ -6632,7 +7082,7 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>test_bulk_import_then_tag, test_clo_lifecycle_cancel_question_and_template, test_question_bank_two_way_sync, test_question_edit_rules, test_tagging_locks_used_questions</t>
+          <t>test_assignment_all_supervisors, test_bulk_import_then_tag, test_copy_exam_manual_items_and_paper_versions, test_course_level_access, test_manual_exam_grid_excel_and_analysis, test_moodle_web_service_flows</t>
         </is>
       </c>
     </row>
@@ -6642,12 +7092,12 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>/api/questions</t>
+          <t>/api/questions/tree</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -6657,7 +7107,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>create_question</t>
+          <t>Cây CTĐT → PLO → PI → CLO của học phần với số câu hỏi đang dùng ở mỗi nút (góp ý F2a);</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -6667,7 +7117,7 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>test_clo_lifecycle_cancel_question_and_template, test_new_course_setup_flow, test_question_bank_two_way_sync, test_question_crud</t>
+          <t>test_question_outcome_tree</t>
         </is>
       </c>
     </row>
@@ -6677,7 +7127,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -6692,7 +7142,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>update_question</t>
+          <t>get_question</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
@@ -6702,7 +7152,7 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>test_question_crud</t>
+          <t>test_bulk_import_then_tag, test_clo_lifecycle_cancel_question_and_template, test_question_bank_two_way_sync, test_question_edit_rules, test_tagging_locks_used_questions</t>
         </is>
       </c>
     </row>
@@ -6712,12 +7162,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>/api/questions/{qid}/cancel</t>
+          <t>/api/questions</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -6727,7 +7177,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>cancel_question</t>
+          <t>create_question</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
@@ -6737,7 +7187,7 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>test_clo_lifecycle_cancel_question_and_template</t>
+          <t>test_clo_lifecycle_cancel_question_and_template, test_new_course_setup_flow, test_question_bank_two_way_sync, test_question_crud</t>
         </is>
       </c>
     </row>
@@ -6747,7 +7197,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -6762,7 +7212,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>delete_question</t>
+          <t>update_question</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -6772,7 +7222,7 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>test_bulk_import_then_tag, test_clo_lifecycle_cancel_question_and_template, test_question_crud</t>
+          <t>test_question_crud</t>
         </is>
       </c>
     </row>
@@ -6782,22 +7232,22 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{course_id}/exams</t>
+          <t>/api/questions/{qid}/cancel</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>UC-02 Đề thi</t>
+          <t>UC-01 Ngân hàng câu hỏi</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Đề của môn (tạo ở trang môn học, chưa gắn lớp) kèm các lớp đã giao; và các lớp HP của người dùng để giao đề.</t>
+          <t>cancel_question</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
@@ -6807,7 +7257,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>test_course_exam_create_and_blocked_actions</t>
+          <t>test_clo_lifecycle_cancel_question_and_template</t>
         </is>
       </c>
     </row>
@@ -6817,22 +7267,22 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/exams</t>
+          <t>/api/questions/{qid}</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>UC-02 Đề thi</t>
+          <t>UC-01 Ngân hàng câu hỏi</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>list_exams</t>
+          <t>delete_question</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
@@ -6842,7 +7292,7 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>test_profile_access, test_section_stats, test_student_profile, test_timing_report_flags_planted_students</t>
+          <t>test_bulk_import_then_tag, test_clo_lifecycle_cancel_question_and_template, test_question_crud</t>
         </is>
       </c>
     </row>
@@ -6857,7 +7307,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/exam-blueprint/pool</t>
+          <t>/api/courses/{course_id}/exams</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -6867,7 +7317,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Số câu sẵn có theo từng ô ma trận (chương × mức Bloom) và theo CLO – để GV lập ma trận đề.</t>
+          <t>Đề của môn (tạo ở trang môn học, chưa gắn lớp) kèm các lớp đã giao; và các lớp HP của người dùng để giao đề.</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
@@ -6877,7 +7327,7 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>test_blueprint_api</t>
+          <t>test_course_exam_create_and_blocked_actions</t>
         </is>
       </c>
     </row>
@@ -6892,7 +7342,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{course_id}/exam-blueprint/pool</t>
+          <t>/api/class-sections/{cs_id}/exams</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -6902,7 +7352,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Như trên, cho đề của môn (tạo ở trang môn học).</t>
+          <t>list_exams</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
@@ -6912,7 +7362,7 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>test_course_exam_create_and_blocked_actions</t>
+          <t>test_profile_access, test_section_stats, test_student_profile, test_timing_report_flags_planted_students</t>
         </is>
       </c>
     </row>
@@ -6922,12 +7372,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/exam-blueprint</t>
+          <t>/api/class-sections/{cs_id}/exam-blueprint/pool</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -6937,7 +7387,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Sinh đề theo ma trận: trả về danh sách câu + điểm, ma trận mục tiêu/đạt được, độ phủ CLO, lỗi thiếu câu và cảnh báo.</t>
+          <t>Số câu sẵn có theo từng ô ma trận (chương × mức Bloom) và theo CLO – để GV lập ma trận đề.</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
@@ -6957,12 +7407,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{course_id}/exam-blueprint</t>
+          <t>/api/courses/{course_id}/exam-blueprint/pool</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -6997,7 +7447,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>/api/exams</t>
+          <t>/api/class-sections/{cs_id}/exam-blueprint</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -7007,7 +7457,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Bài KT của một lớp HP, hoặc đề của môn (course_id) – giao cho các lớp HP khi xuất (POST /exams/{id}/copy).</t>
+          <t>Sinh đề theo ma trận: trả về danh sách câu + điểm, ma trận mục tiêu/đạt được, độ phủ CLO, lỗi thiếu câu và cảnh báo.</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
@@ -7017,7 +7467,7 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>test_blueprint_api, test_bm6c_per_exam, test_bulk_import_then_tag, test_copy_exam_manual_items_and_paper_versions, test_course_exam_create_and_blocked_actions, test_course_exam_deploy_to_sections</t>
+          <t>test_blueprint_api</t>
         </is>
       </c>
     </row>
@@ -7027,12 +7477,12 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}</t>
+          <t>/api/courses/{course_id}/exam-blueprint</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -7042,7 +7492,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>get_exam</t>
+          <t>Như trên, cho đề của môn (tạo ở trang môn học).</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
@@ -7052,7 +7502,7 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>test_course_exam_create_and_blocked_actions, test_course_exam_deploy_to_sections, test_course_manual_exam_deploy_and_grade, test_exam_online_xml, test_manual_exam_grid_excel_and_analysis, test_moodle_web_service_flows</t>
+          <t>test_course_exam_create_and_blocked_actions</t>
         </is>
       </c>
     </row>
@@ -7062,12 +7512,12 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}</t>
+          <t>/api/exams</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -7077,7 +7527,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Xóa bài KT chưa có kết quả. Xóa đề của môn không ảnh hưởng các bài đã giao cho lớp.</t>
+          <t>Bài KT của một lớp HP, hoặc đề của môn (course_id) – giao cho các lớp HP khi xuất (POST /exams/{id}/copy).</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
@@ -7087,7 +7537,7 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>test_blueprint_api, test_bulk_import_then_tag, test_course_exam_deploy_to_sections, test_course_manual_exam_deploy_and_grade, test_exam_online_xml, test_link_quiz_must_belong_to_teacher_course</t>
+          <t>test_blueprint_api, test_bm6c_per_exam, test_bulk_import_then_tag, test_copy_exam_manual_items_and_paper_versions, test_course_exam_create_and_blocked_actions, test_course_exam_deploy_to_sections</t>
         </is>
       </c>
     </row>
@@ -7102,7 +7552,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle-xml</t>
+          <t>/api/exams/{exam_id}</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -7112,7 +7562,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>moodle_xml</t>
+          <t>get_exam</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
@@ -7122,7 +7572,7 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>test_course_exam_create_and_blocked_actions, test_exam_online_xml</t>
+          <t>test_course_exam_create_and_blocked_actions, test_course_exam_deploy_to_sections, test_course_manual_exam_deploy_and_grade, test_exam_online_xml, test_manual_exam_grid_excel_and_analysis, test_moodle_web_service_flows</t>
         </is>
       </c>
     </row>
@@ -7132,12 +7582,12 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/link-quiz</t>
+          <t>/api/exams/{exam_id}</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -7147,7 +7597,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>link_quiz</t>
+          <t>Xóa bài KT chưa có kết quả. Xóa đề của môn không ảnh hưởng các bài đã giao cho lớp.</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
@@ -7157,7 +7607,7 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>test_link_quiz_must_belong_to_teacher_course</t>
+          <t>test_blueprint_api, test_bulk_import_then_tag, test_course_exam_deploy_to_sections, test_course_manual_exam_deploy_and_grade, test_exam_online_xml, test_link_quiz_must_belong_to_teacher_course</t>
         </is>
       </c>
     </row>
@@ -7167,12 +7617,12 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/publish</t>
+          <t>/api/exams/{exam_id}/moodle-xml</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -7182,7 +7632,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>publish</t>
+          <t>moodle_xml</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
@@ -7192,7 +7642,7 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>test_moodle_web_service_flows</t>
+          <t>test_course_exam_create_and_blocked_actions, test_exam_online_xml</t>
         </is>
       </c>
     </row>
@@ -7202,12 +7652,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/copy</t>
+          <t>/api/exams/{exam_id}/link-quiz</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -7217,7 +7667,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Giao đề cho lớp HP: đề của môn (tạo ở trang môn học) được giao khi xuất cho các lớp GV chọn; bài của một lớp được</t>
+          <t>link_quiz</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
@@ -7227,7 +7677,7 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>test_copy_exam_manual_items_and_paper_versions, test_course_exam_deploy_to_sections, test_course_manual_exam_deploy_and_grade</t>
+          <t>test_link_quiz_must_belong_to_teacher_course</t>
         </is>
       </c>
     </row>
@@ -7237,22 +7687,22 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/manual-exams</t>
+          <t>/api/exams/{exam_id}/publish</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Nhập điểm thủ công &amp; gộp bài KT</t>
+          <t>UC-02 Đề thi</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>create_manual_exam</t>
+          <t>publish</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
@@ -7262,7 +7712,7 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>test_copy_exam_manual_items_and_paper_versions, test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_moodle_web_service_flows</t>
         </is>
       </c>
     </row>
@@ -7277,17 +7727,17 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{course_id}/manual-exams</t>
+          <t>/api/exams/{exam_id}/copy</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Nhập điểm thủ công &amp; gộp bài KT</t>
+          <t>UC-02 Đề thi</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Đề nhập điểm của môn (tạo ở trang môn học): khai báo câu/ý gắn CLO một lần, giao cho các lớp HP để nhập điểm.</t>
+          <t>Giao đề cho lớp HP: đề của môn (tạo ở trang môn học) được giao khi xuất cho các lớp GV chọn; bài của một lớp được</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
@@ -7297,7 +7747,7 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>test_course_manual_exam_deploy_and_grade</t>
+          <t>test_copy_exam_manual_items_and_paper_versions, test_course_exam_deploy_to_sections, test_course_manual_exam_deploy_and_grade</t>
         </is>
       </c>
     </row>
@@ -7307,12 +7757,12 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/manual-items</t>
+          <t>/api/class-sections/{cs_id}/manual-exams</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -7322,7 +7772,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>replace_items</t>
+          <t>create_manual_exam</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
@@ -7332,7 +7782,7 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>test_copy_exam_manual_items_and_paper_versions</t>
+          <t>test_copy_exam_manual_items_and_paper_versions, test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
     </row>
@@ -7342,12 +7792,12 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/grades</t>
+          <t>/api/courses/{course_id}/manual-exams</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -7357,7 +7807,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>get_grades</t>
+          <t>Đề nhập điểm của môn (tạo ở trang môn học): khai báo câu/ý gắn CLO một lần, giao cho các lớp HP để nhập điểm.</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
@@ -7367,7 +7817,7 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>test_copy_exam_manual_items_and_paper_versions, test_course_manual_exam_deploy_and_grade, test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_course_manual_exam_deploy_and_grade</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7832,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/grades</t>
+          <t>/api/exams/{exam_id}/manual-items</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -7392,7 +7842,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>put_grades</t>
+          <t>replace_items</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
@@ -7402,7 +7852,7 @@
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>test_course_manual_exam_deploy_and_grade, test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_copy_exam_manual_items_and_paper_versions</t>
         </is>
       </c>
     </row>
@@ -7417,7 +7867,7 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/grades.xlsx</t>
+          <t>/api/exams/{exam_id}/grades</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -7427,7 +7877,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>grades_template</t>
+          <t>get_grades</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
@@ -7437,7 +7887,7 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_copy_exam_manual_items_and_paper_versions, test_course_manual_exam_deploy_and_grade, test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
     </row>
@@ -7447,12 +7897,12 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/grades/import</t>
+          <t>/api/exams/{exam_id}/grades</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -7462,7 +7912,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Nhập điểm từ Excel vào bài đã có: khớp cột theo mã câu (bảng điểm mẫu), theo tên câu/ý, hoặc theo thứ tự cột.</t>
+          <t>put_grades</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
@@ -7472,7 +7922,7 @@
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_course_manual_exam_deploy_and_grade, test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
     </row>
@@ -7482,12 +7932,12 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/manual-exams/import</t>
+          <t>/api/exams/{exam_id}/grades.xlsx</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -7497,7 +7947,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Tạo bài nhập điểm từ một file Excel bất kỳ (bài làm ngoài hệ thống) và nhập luôn điểm.</t>
+          <t>grades_template</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
@@ -7507,7 +7957,7 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>test_create_exam_from_any_excel</t>
+          <t>test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
     </row>
@@ -7517,12 +7967,12 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/evidence</t>
+          <t>/api/exams/{exam_id}/grades/import</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -7532,7 +7982,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Bài có được gộp vào kết quả CLO của lớp (BM6, PI, PLO) hay không.</t>
+          <t>Nhập điểm từ Excel vào bài đã có: khớp cột theo mã câu (bảng điểm mẫu), theo tên câu/ý, hoặc theo thứ tự cột.</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -7542,7 +7992,7 @@
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>test_combine_exams_and_evidence_flag</t>
+          <t>test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
     </row>
@@ -7552,12 +8002,12 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{course_id}/analyzed-exams</t>
+          <t>/api/class-sections/{cs_id}/manual-exams/import</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -7567,7 +8017,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Các bài đã phân tích của môn trong các lớp HP người dùng phụ trách – để chọn bài gộp.</t>
+          <t>Tạo bài nhập điểm từ một file Excel bất kỳ (bài làm ngoài hệ thống) và nhập luôn điểm.</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
@@ -7577,7 +8027,7 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>test_combine_exams_and_evidence_flag</t>
+          <t>test_create_exam_from_any_excel</t>
         </is>
       </c>
     </row>
@@ -7587,12 +8037,12 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>/api/combined-analysis</t>
+          <t>/api/exams/{exam_id}/evidence</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -7602,7 +8052,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>Bài có được gộp vào kết quả CLO của lớp (BM6, PI, PLO) hay không.</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
@@ -7627,7 +8077,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>/api/combined-analysis.xlsx</t>
+          <t>/api/courses/{course_id}/analyzed-exams</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -7637,7 +8087,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>combined_xlsx</t>
+          <t>Các bài đã phân tích của môn trong các lớp HP người dùng phụ trách – để chọn bài gộp.</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
@@ -7657,22 +8107,22 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/remedial</t>
+          <t>/api/combined-analysis</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Phụ đạo theo câu trả lời sai</t>
+          <t>Nhập điểm thủ công &amp; gộp bài KT</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Bảng tổng hợp: mỗi SV sai bao nhiêu câu (trên các bài chọn), CLO chưa đạt; mỗi câu bao nhiêu SV sai.</t>
+          <t>combined</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
@@ -7682,7 +8132,7 @@
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>test_remedial_flow</t>
+          <t>test_combine_exams_and_evidence_flag</t>
         </is>
       </c>
     </row>
@@ -7697,17 +8147,17 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/remedial/students/{student_id}</t>
+          <t>/api/combined-analysis.xlsx</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Phụ đạo theo câu trả lời sai</t>
+          <t>Nhập điểm thủ công &amp; gộp bài KT</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Danh sách câu SV trả lời sai/bỏ trống (kèm phương án đã chọn, đáp án đúng, CLO, chương).</t>
+          <t>combined_xlsx</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
@@ -7717,7 +8167,7 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>test_remedial_flow</t>
+          <t>test_combine_exams_and_evidence_flag</t>
         </is>
       </c>
     </row>
@@ -7727,22 +8177,22 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/remedial-exams</t>
+          <t>/api/class-sections/{cs_id}/remedial</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Phụ đạo theo câu trả lời sai</t>
+          <t>Ôn tập theo câu trả lời sai (phụ đạo)</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Tạo bài KT phụ đạo: câu trắc nghiệm các SV đã chọn làm sai (+ câu tương tự cùng CLO/chương chưa gặp).</t>
+          <t>Bảng tổng hợp: mỗi SV sai bao nhiêu câu (trên các bài chọn), CLO chưa đạt; mỗi câu bao nhiêu SV sai.</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
@@ -7752,7 +8202,7 @@
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>test_remedial_flow</t>
+          <t>test_overview_theo_chuong_va_loc_chuong, test_remedial_flow</t>
         </is>
       </c>
     </row>
@@ -7767,17 +8217,17 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper</t>
+          <t>/api/class-sections/{cs_id}/remedial-exams</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Đề thi giấy &amp; chấm phiếu trên hệ thống</t>
+          <t>Ôn tập theo câu trả lời sai (phụ đạo)</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Trạng thái đề giấy: chế độ (hệ thống tự in &amp; chấm / Moodle Offline Quiz), các mã đề với đầy đủ câu, đáp án; tùy chọn in.</t>
+          <t>Các bài phụ đạo của lớp và tiến bộ của từng SV được giao (góp ý F5):</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
@@ -7787,7 +8237,7 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>test_copy_exam_manual_items_and_paper_versions, test_paper_exam_two_modes, test_system_paper_exam_end_to_end</t>
+          <t>test_progress_after_attempt, test_progress_before_attempt</t>
         </is>
       </c>
     </row>
@@ -7797,22 +8247,22 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper/versions</t>
+          <t>/api/class-sections/{cs_id}/remedial/students/{student_id}</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Đề thi giấy &amp; chấm phiếu trên hệ thống</t>
+          <t>Ôn tập theo câu trả lời sai (phụ đạo)</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>make_versions</t>
+          <t>Danh sách câu SV trả lời sai/bỏ trống (kèm phương án đã chọn, đáp án đúng, chương).</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
@@ -7822,7 +8272,7 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>test_copy_exam_manual_items_and_paper_versions, test_course_exam_deploy_to_sections, test_system_paper_exam_end_to_end</t>
+          <t>test_remedial_flow</t>
         </is>
       </c>
     </row>
@@ -7832,22 +8282,22 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper/versions</t>
+          <t>/api/class-sections/{cs_id}/remedial-exams</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Đề thi giấy &amp; chấm phiếu trên hệ thống</t>
+          <t>Ôn tập theo câu trả lời sai (phụ đạo)</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Bỏ các mã đề hệ thống đã sinh (khi chưa chấm phiếu) – để sinh lại hoặc chuyển sang Moodle Offline Quiz.</t>
+          <t>Tạo bài KT phụ đạo: câu trắc nghiệm các SV đã chọn làm sai (+ câu tương tự cùng chương chưa gặp).</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
@@ -7857,7 +8307,7 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>test_copy_exam_manual_items_and_paper_versions, test_course_exam_deploy_to_sections</t>
+          <t>test_overview_theo_chuong_va_loc_chuong, test_progress_before_attempt, test_remedial_flow</t>
         </is>
       </c>
     </row>
@@ -7867,12 +8317,12 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper/settings</t>
+          <t>/api/exams/{exam_id}/paper</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -7882,7 +8332,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>save_settings</t>
+          <t>Trạng thái đề giấy: chế độ (hệ thống tự in &amp; chấm / Moodle Offline Quiz), các mã đề với đầy đủ câu, đáp án; tùy chọn in.</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
@@ -7892,7 +8342,7 @@
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>test_system_paper_exam_end_to_end</t>
+          <t>test_copy_exam_manual_items_and_paper_versions, test_paper_exam_two_modes, test_system_paper_exam_end_to_end</t>
         </is>
       </c>
     </row>
@@ -7902,12 +8352,12 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper/exam.{fmt}</t>
+          <t>/api/exams/{exam_id}/paper/versions</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -7917,7 +8367,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>exam_file</t>
+          <t>make_versions</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
@@ -7927,7 +8377,7 @@
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>test_system_paper_exam_end_to_end</t>
+          <t>test_copy_exam_manual_items_and_paper_versions, test_course_exam_deploy_to_sections, test_system_paper_exam_end_to_end</t>
         </is>
       </c>
     </row>
@@ -7937,12 +8387,12 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper/answer-sheet.{fmt}</t>
+          <t>/api/exams/{exam_id}/paper/versions</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -7952,7 +8402,7 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Phiếu trả lời: png = ảnh xem trước (theo tham số đang chỉnh); pdf = tệp in (theo cài đặt đã lưu).</t>
+          <t>Bỏ các mã đề hệ thống đã sinh (khi chưa chấm phiếu) – để sinh lại hoặc chuyển sang Moodle Offline Quiz.</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
@@ -7962,7 +8412,7 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>test_system_paper_exam_end_to_end</t>
+          <t>test_copy_exam_manual_items_and_paper_versions, test_course_exam_deploy_to_sections</t>
         </is>
       </c>
     </row>
@@ -7972,12 +8422,12 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper/answer-key.pdf</t>
+          <t>/api/exams/{exam_id}/paper/settings</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -7987,7 +8437,7 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>answer_key</t>
+          <t>save_settings</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
@@ -8012,7 +8462,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper/package.zip</t>
+          <t>/api/exams/{exam_id}/paper/exam.{fmt}</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -8022,7 +8472,7 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Trọn bộ để in: đề từng mã đề (PDF + Word), phiếu trả lời, đáp án.</t>
+          <t>exam_file</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
@@ -8042,12 +8492,12 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/scan</t>
+          <t>/api/exams/{exam_id}/paper/answer-sheet.{fmt}</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -8057,7 +8507,7 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Nhận diện phiếu từ ảnh quét / ảnh chụp (JPG, PNG) hoặc PDF nhiều trang. Chưa ghi CSDL – GV soát rồi lưu (scan/commit).</t>
+          <t>Phiếu trả lời: png = ảnh xem trước (theo tham số đang chỉnh); pdf = tệp in (theo cài đặt đã lưu).</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
@@ -8077,12 +8527,12 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/scan/commit</t>
+          <t>/api/exams/{exam_id}/paper/answer-key.pdf</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -8092,7 +8542,7 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Lưu kết quả phiếu đã soát: Reverse Shuffle nhãn in trên mã đề -&gt; phương án gốc, chấm và phân tích.</t>
+          <t>answer_key</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
@@ -8117,17 +8567,17 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{course_id}/moodle-sync/targets</t>
+          <t>/api/exams/{exam_id}/paper/package.zip</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ ngân hàng câu hỏi với Moodle</t>
+          <t>Đề thi giấy &amp; chấm phiếu trên hệ thống</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>targets</t>
+          <t>Trọn bộ để in: đề từng mã đề (PDF + Word), phiếu trả lời, đáp án.</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
@@ -8137,7 +8587,7 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>test_question_bank_two_way_sync</t>
+          <t>test_system_paper_exam_end_to_end</t>
         </is>
       </c>
     </row>
@@ -8147,22 +8597,22 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{course_id}/moodle-sync</t>
+          <t>/api/exams/{exam_id}/scan</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ ngân hàng câu hỏi với Moodle</t>
+          <t>Đề thi giấy &amp; chấm phiếu trên hệ thống</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>compare</t>
+          <t>Nhận diện phiếu từ ảnh quét / ảnh chụp (JPG, PNG) hoặc PDF nhiều trang. Chưa ghi CSDL – GV soát rồi lưu (scan/commit).</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
@@ -8172,7 +8622,7 @@
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>test_question_bank_two_way_sync</t>
+          <t>test_system_paper_exam_end_to_end</t>
         </is>
       </c>
     </row>
@@ -8187,17 +8637,17 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{course_id}/moodle-sync</t>
+          <t>/api/exams/{exam_id}/scan/commit</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ ngân hàng câu hỏi với Moodle</t>
+          <t>Đề thi giấy &amp; chấm phiếu trên hệ thống</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>apply</t>
+          <t>Lưu kết quả phiếu đã soát: Reverse Shuffle nhãn in trên mã đề -&gt; phương án gốc, chấm và phân tích.</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -8207,7 +8657,7 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>test_question_bank_two_way_sync</t>
+          <t>test_system_paper_exam_end_to_end</t>
         </is>
       </c>
     </row>
@@ -8217,22 +8667,22 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/sync</t>
+          <t>/api/courses/{course_id}/moodle-sync/targets</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>UC-03 Đồng bộ &amp; phân tích</t>
+          <t>Đồng bộ ngân hàng câu hỏi với Moodle</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>sync_moodle</t>
+          <t>targets</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
@@ -8242,7 +8692,7 @@
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>test_paper_resync_is_idempotent, test_resync_is_idempotent, test_sync_stops_when_question_edited_on_moodle, test_sync_warns_average_grade_method</t>
+          <t>test_question_bank_two_way_sync</t>
         </is>
       </c>
     </row>
@@ -8252,22 +8702,22 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/analyze</t>
+          <t>/api/courses/{course_id}/moodle-sync</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>UC-03 Đồng bộ &amp; phân tích</t>
+          <t>Đồng bộ ngân hàng câu hỏi với Moodle</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>analyze</t>
+          <t>compare</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
@@ -8277,7 +8727,7 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>test_sync_analyze_runs_and_bridge</t>
+          <t>test_question_bank_two_way_sync</t>
         </is>
       </c>
     </row>
@@ -8287,22 +8737,22 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/sync-runs</t>
+          <t>/api/courses/{course_id}/moodle-sync</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>UC-03 Đồng bộ &amp; phân tích</t>
+          <t>Đồng bộ ngân hàng câu hỏi với Moodle</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>sync_runs</t>
+          <t>apply</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
@@ -8312,7 +8762,7 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>test_sync_analyze_runs_and_bridge</t>
+          <t>test_question_bank_two_way_sync</t>
         </is>
       </c>
     </row>
@@ -8322,12 +8772,12 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>/api/system/moodle-status</t>
+          <t>/api/exams/{exam_id}/sync</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -8337,7 +8787,7 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>moodle_status</t>
+          <t>sync_moodle</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
@@ -8347,7 +8797,7 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>test_sync_analyze_runs_and_bridge</t>
+          <t>test_paper_resync_is_idempotent, test_resync_is_idempotent, test_sync_stops_when_question_edited_on_moodle, test_sync_warns_average_grade_method</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8812,7 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>/api/system/install-bridge</t>
+          <t>/api/exams/{exam_id}/analyze</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -8372,7 +8822,7 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>install_bridge</t>
+          <t>analyze</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
@@ -8392,22 +8842,22 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/moodle-course</t>
+          <t>/api/exams/{exam_id}/sync-runs</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Tích hợp Moodle (Web Service)</t>
+          <t>UC-03 Đồng bộ &amp; phân tích</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>set_moodle_course</t>
+          <t>sync_runs</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
@@ -8417,7 +8867,7 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>test_link_section_with_moodle_both_ways</t>
+          <t>test_sync_analyze_runs_and_bridge</t>
         </is>
       </c>
     </row>
@@ -8427,22 +8877,22 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/create-quiz</t>
+          <t>/api/system/moodle-status</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Tích hợp Moodle (Web Service)</t>
+          <t>UC-03 Đồng bộ &amp; phân tích</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>create_quiz</t>
+          <t>moodle_status</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
@@ -8452,7 +8902,7 @@
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>test_moodle_web_service_flows</t>
+          <t>test_sync_analyze_runs_and_bridge</t>
         </is>
       </c>
     </row>
@@ -8467,17 +8917,17 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/create-offlinequiz</t>
+          <t>/api/system/install-bridge</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Tích hợp Moodle (Web Service)</t>
+          <t>UC-03 Đồng bộ &amp; phân tích</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>create_offlinequiz</t>
+          <t>install_bridge</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
@@ -8487,7 +8937,7 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>test_moodle_web_service_flows</t>
+          <t>test_sync_analyze_runs_and_bridge</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8947,12 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/offlinequiz</t>
+          <t>/api/class-sections/{cs_id}/moodle-course</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -8512,7 +8962,7 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>offlinequiz_status</t>
+          <t>set_moodle_course</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
@@ -8522,7 +8972,7 @@
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>test_moodle_web_service_flows</t>
+          <t>test_link_section_with_moodle_both_ways</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8987,7 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/process-scans</t>
+          <t>/api/exams/{exam_id}/moodle/create-quiz</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -8547,7 +8997,7 @@
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>process_scans</t>
+          <t>create_quiz</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
@@ -8567,12 +9017,12 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/offlinequiz/files/{filename}</t>
+          <t>/api/exams/{exam_id}/moodle/restrict</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -8582,17 +9032,17 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>offlinequiz_file</t>
-        </is>
-      </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>Có</t>
+          <t>Bài phụ đạo đã có Quiz: (đồng bộ lại) nhóm Moodle gồm đúng các SV được giao và điều kiện truy cập của Quiz.</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>Chỉ lỗi</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>test_moodle_web_service_flows</t>
+          <t>test_restrict_requires_moodle_accounts</t>
         </is>
       </c>
     </row>
@@ -8602,12 +9052,12 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/offlinequiz/files.zip</t>
+          <t>/api/exams/{exam_id}/moodle/create-offlinequiz</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -8617,7 +9067,7 @@
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>offlinequiz_zip</t>
+          <t>create_offlinequiz</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
@@ -8642,7 +9092,7 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/results-preview</t>
+          <t>/api/exams/{exam_id}/moodle/offlinequiz</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -8652,7 +9102,7 @@
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>results_preview</t>
+          <t>offlinequiz_status</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
@@ -8662,7 +9112,7 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>test_results_for_moodle</t>
+          <t>test_moodle_web_service_flows</t>
         </is>
       </c>
     </row>
@@ -8677,7 +9127,7 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/push-results</t>
+          <t>/api/exams/{exam_id}/moodle/process-scans</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -8687,7 +9137,7 @@
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>push_results</t>
+          <t>process_scans</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
@@ -8712,7 +9162,7 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>/api/system/lms-status</t>
+          <t>/api/exams/{exam_id}/moodle/offlinequiz/files/{filename}</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -8722,7 +9172,7 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>lms_status</t>
+          <t>offlinequiz_file</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
@@ -8747,17 +9197,17 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/overview</t>
+          <t>/api/exams/{exam_id}/moodle/offlinequiz/files.zip</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>UC-04 Thống kê lớp học</t>
+          <t>Tích hợp Moodle (Web Service)</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>overview</t>
+          <t>offlinequiz_zip</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
@@ -8767,7 +9217,7 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_moodle_web_service_flows</t>
         </is>
       </c>
     </row>
@@ -8782,17 +9232,17 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/item-stats</t>
+          <t>/api/exams/{exam_id}/moodle/results-preview</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>UC-04 Thống kê lớp học</t>
+          <t>Tích hợp Moodle (Web Service)</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>item_stats</t>
+          <t>results_preview</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
@@ -8802,7 +9252,7 @@
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>test_item_stats_flags_trap_question, test_manual_exam_grid_excel_and_analysis, test_timing_thresholds_timeline_and_export</t>
+          <t>test_results_for_moodle</t>
         </is>
       </c>
     </row>
@@ -8812,22 +9262,22 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/students</t>
+          <t>/api/exams/{exam_id}/moodle/push-results</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>UC-04 Thống kê lớp học</t>
+          <t>Tích hợp Moodle (Web Service)</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>exam_students</t>
+          <t>push_results</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
@@ -8837,7 +9287,7 @@
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_moodle_web_service_flows</t>
         </is>
       </c>
     </row>
@@ -8852,17 +9302,17 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/clo-results</t>
+          <t>/api/system/lms-status</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>UC-04 Thống kê lớp học</t>
+          <t>Tích hợp Moodle (Web Service)</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>BM6b – kết quả tổng hợp của từng CĐR môn học (E1: rỗng nếu chưa phân tích).</t>
+          <t>lms_status</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
@@ -8872,7 +9322,7 @@
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>test_clo_results_bm6b</t>
+          <t>test_moodle_web_service_flows</t>
         </is>
       </c>
     </row>
@@ -8887,7 +9337,7 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/clo-results/{clo_id}/evidence</t>
+          <t>/api/exams/{exam_id}/overview</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -8897,7 +9347,7 @@
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>BM6c/6d – bảng minh chứng: điểm từng SV trên các câu thuộc CLO, theo từng bài KT; câu hỏi có DI thấp.</t>
+          <t>overview</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
@@ -8907,7 +9357,7 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>test_sync_analyze_runs_and_bridge</t>
+          <t>test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
     </row>
@@ -8917,12 +9367,12 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/clo-results/{clo_id}</t>
+          <t>/api/exams/{exam_id}/item-stats</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -8932,7 +9382,7 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>clo_narrative</t>
+          <t>item_stats</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
@@ -8942,7 +9392,7 @@
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>test_clo_narrative</t>
+          <t>test_item_stats_flags_trap_question, test_manual_exam_grid_excel_and_analysis, test_timing_thresholds_timeline_and_export</t>
         </is>
       </c>
     </row>
@@ -8957,7 +9407,7 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/timing</t>
+          <t>/api/exams/{exam_id}/students</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -8967,7 +9417,7 @@
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>Thời gian làm bài của từng SV và các dấu hiệu bất thường (làm quá nhanh/chọn đại, bỏ dở, treo máy chờ hết giờ…).</t>
+          <t>exam_students</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
@@ -8977,7 +9427,7 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>test_timing_report_flags_planted_students, test_timing_thresholds_timeline_and_export</t>
+          <t>test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
     </row>
@@ -8992,7 +9442,7 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/timing/students/{student_id}</t>
+          <t>/api/exams/{exam_id}/clo-summary</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -9002,7 +9452,7 @@
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>Diễn biến làm bài của một SV: thời điểm chọn, thời gian trả lời, số lần đổi đáp án từng câu.</t>
+          <t>Tổng hợp CẢ LỚP theo từng CLO của bài KT: số SV đạt / số SV được đánh giá (không trả kết quả riêng của từng SV).</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
@@ -9012,7 +9462,7 @@
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>test_timing_thresholds_timeline_and_export</t>
+          <t>test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
     </row>
@@ -9027,7 +9477,7 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/timing.xlsx</t>
+          <t>/api/class-sections/{cs_id}/clo-results</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -9037,7 +9487,7 @@
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>Xuất Excel danh sách cảnh báo và thời gian trả lời từng câu.</t>
+          <t>BM6b – kết quả tổng hợp của từng CĐR môn học (E1: rỗng nếu chưa phân tích).</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
@@ -9047,7 +9497,7 @@
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>test_timing_thresholds_timeline_and_export</t>
+          <t>test_clo_results_bm6b</t>
         </is>
       </c>
     </row>
@@ -9062,17 +9512,17 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/students/{student_id}/profile</t>
+          <t>/api/class-sections/{cs_id}/clo-results/{clo_id}/evidence</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>UC-04 Hồ sơ SV &amp; thống kê lớp</t>
+          <t>UC-04 Thống kê lớp học</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>student_profile</t>
+          <t>BM6c/6d – bảng minh chứng: điểm từng SV trên các câu thuộc CLO, theo từng bài KT; câu hỏi có DI thấp.</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
@@ -9082,7 +9532,7 @@
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>test_student_profile, test_timing_thresholds_timeline_and_export</t>
+          <t>test_sync_analyze_runs_and_bridge</t>
         </is>
       </c>
     </row>
@@ -9092,22 +9542,22 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/stats</t>
+          <t>/api/class-sections/{cs_id}/clo-results/{clo_id}</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>UC-04 Hồ sơ SV &amp; thống kê lớp</t>
+          <t>UC-04 Thống kê lớp học</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>section_stats</t>
+          <t>clo_narrative</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
@@ -9117,7 +9567,7 @@
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>test_section_stats, test_student_profile</t>
+          <t>test_clo_narrative</t>
         </is>
       </c>
     </row>
@@ -9132,17 +9582,17 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/class-sections/{cs_id}/bm6.xlsx</t>
+          <t>/api/exams/{exam_id}/timing</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>UC-07 Báo cáo đo lường CĐR</t>
+          <t>UC-04 Thống kê lớp học</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>bm6</t>
+          <t>Thời gian làm bài của từng SV và các dấu hiệu bất thường (làm quá nhanh/chọn đại, bỏ dở, treo máy chờ hết giờ…).</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
@@ -9152,7 +9602,7 @@
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>test_bm6_evidence_follows_plan_and_matches_bm6b, test_bm6_workbook, test_http_errors_and_inputs</t>
+          <t>test_timing_report_flags_planted_students, test_timing_thresholds_timeline_and_export</t>
         </is>
       </c>
     </row>
@@ -9167,17 +9617,17 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/exams/{exam_id}/bm6c.xlsx</t>
+          <t>/api/exams/{exam_id}/timing/students/{student_id}</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>UC-07 Báo cáo đo lường CĐR</t>
+          <t>UC-04 Thống kê lớp học</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>BM6c riêng cho một bài kiểm tra – minh chứng từng CLO bài KT đo (kèm MSSV, họ tên).</t>
+          <t>Diễn biến làm bài của một SV: thời điểm chọn, thời gian trả lời, số lần đổi đáp án từng câu.</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
@@ -9187,7 +9637,7 @@
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>test_bm6c_per_exam</t>
+          <t>test_timing_thresholds_timeline_and_export</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9652,17 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/programs/{pid}/bm3.xlsx</t>
+          <t>/api/exams/{exam_id}/timing.xlsx</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>UC-07 Báo cáo đo lường CĐR</t>
+          <t>UC-04 Thống kê lớp học</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>bm3</t>
+          <t>Xuất Excel danh sách cảnh báo và thời gian trả lời từng câu.</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
@@ -9222,7 +9672,7 @@
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>test_bm3_workbook</t>
+          <t>test_timing_thresholds_timeline_and_export</t>
         </is>
       </c>
     </row>
@@ -9237,17 +9687,17 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/programs/{pid}/bm2.docx</t>
+          <t>/api/class-sections/{cs_id}/students/{student_id}/profile</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>UC-07 Báo cáo đo lường CĐR</t>
+          <t>UC-04 Hồ sơ SV &amp; thống kê lớp</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>BM2 dạng Word như biểu mẫu gốc: BM2a (kế hoạch) + BM2b (báo cáo tổng kết).</t>
+          <t>student_profile</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
@@ -9257,7 +9707,7 @@
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>test_bm2_docx</t>
+          <t>test_student_profile, test_timing_thresholds_timeline_and_export</t>
         </is>
       </c>
     </row>
@@ -9272,17 +9722,17 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/semesters/{sem_id}/assignments.xlsx</t>
+          <t>/api/class-sections/{cs_id}/stats</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>UC-07 Báo cáo đo lường CĐR</t>
+          <t>UC-04 Hồ sơ SV &amp; thống kê lớp</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>Bảng "Phân công đánh giá PIs" của một học kỳ.</t>
+          <t>section_stats</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
@@ -9292,7 +9742,7 @@
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>test_assignments_xlsx</t>
+          <t>test_section_stats, test_student_profile</t>
         </is>
       </c>
     </row>
@@ -9307,7 +9757,7 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/programs/{pid}/plo-summary</t>
+          <t>/api/reports/class-sections/{cs_id}/bm6.xlsx</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -9317,7 +9767,7 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>plo_summary</t>
+          <t>bm6</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
@@ -9327,7 +9777,7 @@
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>test_plo_summary_is_sum_of_pi</t>
+          <t>test_bm6_evidence_follows_plan_and_matches_bm6b, test_bm6_workbook, test_http_errors_and_inputs</t>
         </is>
       </c>
     </row>
@@ -9337,12 +9787,12 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/programs/{pid}/recompute</t>
+          <t>/api/reports/exams/{exam_id}/bm6c.xlsx</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -9352,7 +9802,7 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>recompute</t>
+          <t>BM6c riêng cho một bài kiểm tra – minh chứng từng CLO bài KT đo (kèm MSSV, họ tên).</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
@@ -9362,7 +9812,7 @@
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>test_programs_plo_and_pi_plans</t>
+          <t>test_bm6c_per_exam</t>
         </is>
       </c>
     </row>
@@ -9372,12 +9822,12 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/plo-results/{plo_id}/{academic_year}</t>
+          <t>/api/reports/programs/{pid}/bm3.xlsx</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -9387,7 +9837,7 @@
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>plo_narrative</t>
+          <t>bm3</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
@@ -9397,7 +9847,7 @@
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>test_plo_narrative</t>
+          <t>test_bm3_workbook</t>
         </is>
       </c>
     </row>
@@ -9412,17 +9862,17 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>/api/health</t>
+          <t>/api/reports/programs/{pid}/bm2.docx</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống</t>
+          <t>UC-07 Báo cáo đo lường CĐR</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra dịch vụ</t>
+          <t>BM2 dạng Word như biểu mẫu gốc: BM2a (kế hoạch) + BM2b (báo cáo tổng kết).</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
@@ -9432,7 +9882,7 @@
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>test_auth_me_and_catalogs</t>
+          <t>test_bm2_docx</t>
         </is>
       </c>
     </row>
@@ -9447,25 +9897,200 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
+          <t>/api/reports/semesters/{sem_id}/assignments.xlsx</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>UC-07 Báo cáo đo lường CĐR</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>Bảng "Phân công đánh giá PIs" của một học kỳ.</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>test_assignments_xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>/api/reports/programs/{pid}/plo-summary</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>UC-07 Báo cáo đo lường CĐR</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>plo_summary</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>test_plo_summary_is_sum_of_pi</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>/api/reports/programs/{pid}/recompute</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>UC-07 Báo cáo đo lường CĐR</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>recompute</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>test_programs_plo_and_pi_plans</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>/api/reports/plo-results/{plo_id}/{academic_year}</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>UC-07 Báo cáo đo lường CĐR</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>plo_narrative</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>test_plo_narrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>/api/health</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>Hệ thống</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>Kiểm tra dịch vụ</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>test_auth_me_and_catalogs</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
           <t>/api/public-config</t>
         </is>
       </c>
-      <c r="D134" s="4" t="inlineStr">
+      <c r="D139" s="4" t="inlineStr">
         <is>
           <t>Hệ thống</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
+      <c r="E139" s="4" t="inlineStr">
         <is>
           <t>Cấu hình công khai cho giao diện</t>
         </is>
       </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="G134" s="4" t="inlineStr">
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
         <is>
           <t>test_auth_me_and_catalogs</t>
         </is>
@@ -9979,12 +10604,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Tạo Quiz trên Moodle</t>
+          <t>Tạo bài trắc nghiệm trên Moodle</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Bài trực tuyến mới → Tạo Quiz trên Moodle</t>
+          <t>Bài trực tuyến mới → Tạo bài trắc nghiệm trên Moodle</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -10245,7 +10870,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Bài Thi cuối kỳ → Đồng bộ &amp; phân tích</t>
+          <t>Bài Thi cuối kỳ → Lấy bài làm &amp; phân tích</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -10303,7 +10928,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Trang môn → Gộp bài KT đánh giá CĐR → chọn 3 bài → Phân tích gộp</t>
+          <t>Trang môn → Chọn bài tính vào kết quả → chọn 3 bài → Phân tích gộp</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -10356,17 +10981,17 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Phụ đạo</t>
+          <t>Ôn tập theo chương</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Lớp 01 → Phụ đạo (câu sai) → bấm 'Câu sai' của 1 SV → Tạo bài phụ đạo</t>
+          <t>Lớp 01 → Ôn tập → chọn các chương có nhiều SV yếu → 'Tạo bài kiểm tra lại cho nhóm SV yếu…'</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Danh sách câu sai đúng; bài phụ đạo không gộp minh chứng</t>
+          <t>Nhóm SV và danh sách câu sai đúng theo chương; bài kiểm tra lại không tính vào kết quả CLO</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
@@ -10385,12 +11010,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Kết quả CĐR (BM6), xuất biểu mẫu</t>
+          <t>Kết quả chuẩn đầu ra của lớp (BM6), xuất biểu mẫu</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Lớp 01 → Kết quả CĐR (BM6) → Xuất Excel; BM6c từng bài</t>
+          <t>Lớp 01 → Kết quả chuẩn đầu ra của lớp (BM6) → Xuất Excel; BM6c từng bài</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -10453,7 +11078,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>SV nhận thông báo; trên Moodle thấy radar CLO, lộ trình</t>
+          <t>SV nhận thông báo; trên Moodle thấy điểm, nhận xét và kế hoạch ôn theo chương (không có CLO riêng từng SV)</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr"/>
@@ -10593,7 +11218,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Môn học của tôi → '+ Tạo bài KT' ở môn DBMS330284 → chọn hình thức (3 thẻ) → soạn đề → Lưu đề của môn → 'Giao cho lớp HP / Xuất' → chọn lớp 02</t>
+          <t>Môn học của tôi → '+ Tạo bài kiểm tra' ở môn DBMS330284 → chọn hình thức (3 thẻ) → soạn đề → Lưu đề của môn → 'Giao cho lớp HP / Xuất' → chọn lớp 02</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -10632,371 +11257,6 @@
       </c>
       <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Điều kiện ảnh / kiểu tô</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>MSSV đúng (ảnh) · Câu đọc đúng (kiểu tô)</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Mã đề đúng (ảnh) · Số câu bị cảnh báo (kiểu tô)</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Câu đọc đúng</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Phiếu lỗi định vị</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Thời gian/phiếu</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Bản quét 150 dpi</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>30/30</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>30/30</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>1200/1200</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>err=0</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>117ms</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Quét nghiêng ±7°, thu nhỏ</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>30/30</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>30/30</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>1200/1200</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>err=0</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>115ms</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Ảnh chụp điện thoại (phối cảnh, ánh sáng lệch, mờ, JPEG 60)</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>30/30</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>30/30</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>1200/1200</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>err=0</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>227ms</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Đặt ngược 180°</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>30/30</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>30/30</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>1200/1200</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>err=0</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>107ms</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Ảnh xoay ngang 90°</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>30/30</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>30/30</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>1200/1200</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>err=0</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>125ms</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Nét bút vẽ lung tung (kể cả đè lên ô định vị)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>30/30</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>30/30</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>1200/1200</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>err=0</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>108ms</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Tô bút chì đậm vừa (xám 110)</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>100/100</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>cảnh báo 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Tô bút chì nhạt (xám 150)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>120/120</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>cảnh báo 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Tô không kín (≈60% ô)</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>120/120</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>cảnh báo 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Vết tẩy còn mờ (xám 215) + ô tô mới</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>120/120</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>cảnh báo 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Gạch chéo ô cũ + tô ô mới</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>120/120</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>cảnh báo 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Tô 2 ô (phải được cảnh báo)</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>120/120</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>cảnh báo 120</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Bỏ trống</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>100/100</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>cảnh báo 0</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/kiem_thu/KET_QUA_KIEM_THU.xlsx
+++ b/docs/kiem_thu/KET_QUA_KIEM_THU.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -491,14 +491,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Thời điểm chạy: 24/10/2026 10:06 · Python 3.13.17 · CSDL: kiểm thử dựng lại assessment_db</t>
+          <t>Thời điểm chạy: 24/10/2026 20:08 · Python 3.13.17 · CSDL: kiểm thử dựng lại assessment_db</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Ca kiểm thử tự động: 112/112 đạt · Độ phủ API: 137/138 endpoint được gọi thành công</t>
+          <t>Ca kiểm thử tự động: 129/129 đạt · Độ phủ API: 147/148 endpoint được gọi thành công</t>
         </is>
       </c>
     </row>
@@ -788,10 +788,10 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>0</v>
@@ -805,14 +805,14 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>TỔNG</t>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>0</v>
@@ -823,8 +823,29 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>TỔNG</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>129</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>129</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Kiểm thử bổ sung (ngoài pytest): tools/moodle_e2e/run_real_moodle_e2e.py (Moodle 4.5 thật), tools/moodle_e2e/kiem_tra_dong_bo_cau_hoi.py, tools/kiem_tra_do_luong.py (tính lại độc lập các độ đo), tools/omr/kiem_tra_omr.py (độ bền chấm phiếu), backend/tests/ui_screens.py (duyệt giao diện).</t>
         </is>
@@ -841,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I113"/>
+  <dimension ref="A1:I130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -932,7 +953,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>15.76</v>
+        <v>22.52</v>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
@@ -971,7 +992,7 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
@@ -1010,7 +1031,7 @@
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
@@ -1049,7 +1070,7 @@
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -1088,7 +1109,7 @@
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -1127,7 +1148,7 @@
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -1244,7 +1265,7 @@
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
@@ -1283,7 +1304,7 @@
         </is>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -1361,7 +1382,7 @@
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
@@ -1400,7 +1421,7 @@
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
@@ -1478,7 +1499,7 @@
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.41</v>
+        <v>0.16</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
@@ -1595,7 +1616,7 @@
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -1634,7 +1655,7 @@
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
@@ -1673,7 +1694,7 @@
         </is>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
@@ -1868,7 +1889,7 @@
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
@@ -1985,7 +2006,7 @@
         </is>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
@@ -2063,7 +2084,7 @@
         </is>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
@@ -2258,7 +2279,7 @@
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
@@ -2297,7 +2318,7 @@
         </is>
       </c>
       <c r="G37" s="4" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
@@ -2336,7 +2357,7 @@
         </is>
       </c>
       <c r="G38" s="4" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
@@ -2375,7 +2396,7 @@
         </is>
       </c>
       <c r="G39" s="4" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
@@ -2531,7 +2552,7 @@
         </is>
       </c>
       <c r="G43" s="4" t="n">
-        <v>8.220000000000001</v>
+        <v>11.33</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
@@ -2570,7 +2591,7 @@
         </is>
       </c>
       <c r="G44" s="4" t="n">
-        <v>16.82</v>
+        <v>21.8</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
@@ -2609,7 +2630,7 @@
         </is>
       </c>
       <c r="G45" s="4" t="n">
-        <v>8.56</v>
+        <v>11.35</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
@@ -2804,7 +2825,7 @@
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>4.54</v>
+        <v>6.05</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
@@ -2843,7 +2864,7 @@
         </is>
       </c>
       <c r="G51" s="4" t="n">
-        <v>0.37</v>
+        <v>0.75</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
@@ -2921,7 +2942,7 @@
         </is>
       </c>
       <c r="G53" s="4" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
@@ -3350,7 +3371,7 @@
         </is>
       </c>
       <c r="G64" s="4" t="n">
-        <v>1.19</v>
+        <v>2.59</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
@@ -3428,7 +3449,7 @@
         </is>
       </c>
       <c r="G66" s="4" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
@@ -3467,7 +3488,7 @@
         </is>
       </c>
       <c r="G67" s="4" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
@@ -3506,7 +3527,7 @@
         </is>
       </c>
       <c r="G68" s="4" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
@@ -3545,7 +3566,7 @@
         </is>
       </c>
       <c r="G69" s="4" t="n">
-        <v>0.45</v>
+        <v>0.28</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
@@ -3584,7 +3605,7 @@
         </is>
       </c>
       <c r="G70" s="4" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
@@ -3623,7 +3644,7 @@
         </is>
       </c>
       <c r="G71" s="4" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
@@ -3662,7 +3683,7 @@
         </is>
       </c>
       <c r="G72" s="4" t="n">
-        <v>0.13</v>
+        <v>0.04</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
@@ -3701,7 +3722,7 @@
         </is>
       </c>
       <c r="G73" s="4" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
@@ -3779,7 +3800,7 @@
         </is>
       </c>
       <c r="G75" s="4" t="n">
-        <v>0.74</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
@@ -3818,7 +3839,7 @@
         </is>
       </c>
       <c r="G76" s="4" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
@@ -3857,7 +3878,7 @@
         </is>
       </c>
       <c r="G77" s="4" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
@@ -3896,7 +3917,7 @@
         </is>
       </c>
       <c r="G78" s="4" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
@@ -3974,7 +3995,7 @@
         </is>
       </c>
       <c r="G80" s="4" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
@@ -4052,7 +4073,7 @@
         </is>
       </c>
       <c r="G82" s="4" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
@@ -4091,7 +4112,7 @@
         </is>
       </c>
       <c r="G83" s="4" t="n">
-        <v>1.93</v>
+        <v>2.72</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
@@ -4130,7 +4151,7 @@
         </is>
       </c>
       <c r="G84" s="4" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
@@ -4169,7 +4190,7 @@
         </is>
       </c>
       <c r="G85" s="4" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
@@ -4208,7 +4229,7 @@
         </is>
       </c>
       <c r="G86" s="4" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
@@ -4442,7 +4463,7 @@
         </is>
       </c>
       <c r="G92" s="4" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
@@ -4481,7 +4502,7 @@
         </is>
       </c>
       <c r="G93" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
@@ -4559,7 +4580,7 @@
         </is>
       </c>
       <c r="G95" s="4" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
@@ -4598,7 +4619,7 @@
         </is>
       </c>
       <c r="G96" s="4" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
@@ -4637,7 +4658,7 @@
         </is>
       </c>
       <c r="G97" s="4" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
@@ -4676,7 +4697,7 @@
         </is>
       </c>
       <c r="G98" s="4" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
@@ -4715,7 +4736,7 @@
         </is>
       </c>
       <c r="G99" s="4" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
@@ -4793,7 +4814,7 @@
         </is>
       </c>
       <c r="G101" s="4" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
@@ -4813,11 +4834,19 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>test_seed_backfilled_clo_pi</t>
-        </is>
-      </c>
-      <c r="D102" s="4" t="inlineStr"/>
-      <c r="E102" s="4" t="inlineStr"/>
+          <t>Tính thời gian trả lời từng câu</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Dãy thời điểm chọn đáp án; nhiều câu cùng một trang (cùng thời điểm)</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>Thời gian = khoảng cách tới lần chọn trước; câu cùng trang chia đều; báo độ phân giải theo trang</t>
+        </is>
+      </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
           <t>ĐẠT</t>
@@ -4828,7 +4857,7 @@
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>test_clo_pi::test_seed_backfilled_clo_pi</t>
+          <t>test_timing::test_response_time_split_and_page_resolution</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr"/>
@@ -4844,22 +4873,30 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>test_clo_pi_mapping_derives_plo</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="inlineStr"/>
-      <c r="E103" s="4" t="inlineStr"/>
+          <t>Đồng bộ thời điểm chọn đáp án từ Moodle</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Đồng bộ Quiz có giới hạn 45 phút, tự nộp khi hết giờ</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lần chọn đầu/cuối, số lần lưu từng câu; giới hạn thời gian; lượt hết giờ tự nộp</t>
+        </is>
+      </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
       </c>
       <c r="G103" s="4" t="n">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>test_clo_pi::test_clo_pi_mapping_derives_plo</t>
+          <t>test_timing::test_sync_stores_answer_times</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr"/>
@@ -4875,22 +4912,30 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>test_backfill_from_legacy_plo</t>
-        </is>
-      </c>
-      <c r="D104" s="4" t="inlineStr"/>
-      <c r="E104" s="4" t="inlineStr"/>
+          <t>Cảnh báo SV chọn đại / chọn xong để hết giờ</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Dữ liệu có 2 SV chọn ~20 câu trong 1 phút và 2 SV chọn xong không nộp chờ hết giờ</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>Đúng 4 SV bị cảnh báo đúng loại; SV bình thường không bị gắn cờ; số cảnh báo hiện ở danh sách bài KT</t>
+        </is>
+      </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
       </c>
       <c r="G104" s="4" t="n">
-        <v>0.03</v>
+        <v>0.41</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>test_clo_pi::test_backfill_from_legacy_plo</t>
+          <t>test_timing::test_timing_report_flags_planted_students</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr"/>
@@ -4906,22 +4951,30 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>test_question_outcome_tree</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr"/>
-      <c r="E105" s="4" t="inlineStr"/>
+          <t>Đổi ngưỡng, diễn biến từng SV, xuất Excel</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Gửi ngưỡng tùy chỉnh / sai; xem diễn biến 1 SV; tải Excel; bài giấy</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>Kết quả theo ngưỡng; ngưỡng sai 422; SV không làm 404; Excel 2 sheet; bài giấy báo không áp dụng</t>
+        </is>
+      </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
       </c>
       <c r="G105" s="4" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>test_clo_pi::test_question_outcome_tree</t>
+          <t>test_timing::test_timing_thresholds_timeline_and_export</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr"/>
@@ -4932,12 +4985,12 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>test_demo_syllabus_approved</t>
+          <t>test_seed_backfilled_clo_pi</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr"/>
@@ -4948,11 +5001,11 @@
         </is>
       </c>
       <c r="G106" s="4" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>test_syllabus_versions::test_demo_syllabus_approved</t>
+          <t>test_clo_pi::test_seed_backfilled_clo_pi</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr"/>
@@ -4963,12 +5016,12 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>test_syllabus_version_flow</t>
+          <t>test_clo_pi_mapping_derives_plo</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr"/>
@@ -4979,11 +5032,11 @@
         </is>
       </c>
       <c r="G107" s="4" t="n">
-        <v>0.38</v>
+        <v>0.14</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>test_syllabus_versions::test_syllabus_version_flow</t>
+          <t>test_clo_pi::test_clo_pi_mapping_derives_plo</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr"/>
@@ -4994,12 +5047,12 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>test_outline_detail</t>
+          <t>test_backfill_from_legacy_plo</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr"/>
@@ -5010,11 +5063,11 @@
         </is>
       </c>
       <c r="G108" s="4" t="n">
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>test_syllabus_versions::test_outline_detail</t>
+          <t>test_clo_pi::test_backfill_from_legacy_plo</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr"/>
@@ -5025,12 +5078,12 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>test_new_course_without_syllabus</t>
+          <t>test_question_outcome_tree</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr"/>
@@ -5041,11 +5094,11 @@
         </is>
       </c>
       <c r="G109" s="4" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>test_syllabus_versions::test_new_course_without_syllabus</t>
+          <t>test_clo_pi::test_question_outcome_tree</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr"/>
@@ -5056,22 +5109,22 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Tính thời gian trả lời từng câu</t>
+          <t>Học liệu mẫu có sẵn</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Dãy thời điểm chọn đáp án; nhiều câu cùng một trang (cùng thời điểm)</t>
+          <t>Danh sách học liệu của môn DBMS330284</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>Thời gian = khoảng cách tới lần chọn trước; câu cùng trang chia đều; báo độ phân giải theo trang</t>
+          <t>7 học liệu (6 slide + 1 giáo trình), số trang khớp nội dung đã sinh</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
@@ -5080,11 +5133,11 @@
         </is>
       </c>
       <c r="G110" s="4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>test_timing::test_response_time_split_and_page_resolution</t>
+          <t>test_hoc_lieu_rag::test_seed_co_hoc_lieu</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr"/>
@@ -5095,24 +5148,16 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ thời điểm chọn đáp án từ Moodle</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr">
-        <is>
-          <t>Đồng bộ Quiz có giới hạn 45 phút, tự nộp khi hết giờ</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>Lưu lần chọn đầu/cuối, số lần lưu từng câu; giới hạn thời gian; lượt hết giờ tự nộp</t>
-        </is>
-      </c>
+          <t>test_tim_dung_slide[T\u1ec7p nh\u1eadt k\xfd giao t\xe1c (.ldf) trong SQL Server \u0111\u01b0\u1ee3c d\xf9ng ch\u1ee7 y\u1ebfu \u0111\u1ec3 ph\u1ee5c h\u1ed3i-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 1-4]</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr"/>
+      <c r="E111" s="4" t="inlineStr"/>
       <c r="F111" s="5" t="inlineStr">
         <is>
           <t>ĐẠT</t>
@@ -5123,7 +5168,7 @@
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>test_timing::test_sync_stores_answer_times</t>
+          <t>test_hoc_lieu_rag::test_tim_dung_slide[T\u1ec7p nh\u1eadt k\xfd giao t\xe1c (.ldf) trong SQL Server \u0111\u01b0\u1ee3c d\xf9ng ch\u1ee7 y\u1ebfu \u0111\u1ec3 ph\u1ee5c h\u1ed3i-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 1-4]</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr"/>
@@ -5134,35 +5179,27 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Cảnh báo SV chọn đại / chọn xong để hết giờ</t>
-        </is>
-      </c>
-      <c r="D112" s="4" t="inlineStr">
-        <is>
-          <t>Dữ liệu có 2 SV chọn ~20 câu trong 1 phút và 2 SV chọn xong không nộp chờ hết giờ</t>
-        </is>
-      </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>Đúng 4 SV bị cảnh báo đúng loại; SV bình thường không bị gắn cờ; số cảnh báo hiện ở danh sách bài KT</t>
-        </is>
-      </c>
+          <t>test_tim_dung_slide[Trong trigger AFTER UPDATE b\u1ea3ng t\u1ea1m n\xe0o ch\u1ee9a gi\xe1 tr\u1ecb C\u0168 c\u1ee7a c\xe1c d\xf2ng b\u1ecb c\u1eadp nh\u1eadt-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 3-1]</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr"/>
+      <c r="E112" s="4" t="inlineStr"/>
       <c r="F112" s="5" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
       </c>
       <c r="G112" s="4" t="n">
-        <v>0.21</v>
+        <v>0.01</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>test_timing::test_timing_report_flags_planted_students</t>
+          <t>test_hoc_lieu_rag::test_tim_dung_slide[Trong trigger AFTER UPDATE b\u1ea3ng t\u1ea1m n\xe0o ch\u1ee9a gi\xe1 tr\u1ecb C\u0168 c\u1ee7a c\xe1c d\xf2ng b\u1ecb c\u1eadp nh\u1eadt-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 3-1]</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr"/>
@@ -5173,38 +5210,637 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Đổi ngưỡng, diễn biến từng SV, xuất Excel</t>
-        </is>
-      </c>
-      <c r="D113" s="4" t="inlineStr">
-        <is>
-          <t>Gửi ngưỡng tùy chỉnh / sai; xem diễn biến 1 SV; tải Excel; bài giấy</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>Kết quả theo ngưỡng; ngưỡng sai 422; SV không làm 404; Excel 2 sheet; bài giấy báo không áp dụng</t>
-        </is>
-      </c>
+          <t>test_tim_dung_slide[Hai giao t\xe1c gi\u1eef kh\xf3a ch\u1edd nhau deadlock ch\u1ecdn n\u1ea1n nh\xe2n victim-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 4-4]</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr"/>
+      <c r="E113" s="4" t="inlineStr"/>
       <c r="F113" s="5" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
       </c>
       <c r="G113" s="4" t="n">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>test_timing::test_timing_thresholds_timeline_and_export</t>
+          <t>test_hoc_lieu_rag::test_tim_dung_slide[Hai giao t\xe1c gi\u1eef kh\xf3a ch\u1edd nhau deadlock ch\u1ecdn n\u1ea1n nh\xe2n victim-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 4-4]</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>test_tim_dung_slide[M\u1ed7i b\u1ea3ng trong SQL Server c\xf3 t\u1ed1i \u0111a bao nhi\xeau ch\u1ec9 m\u1ee5c clustered-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 5-1]</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr"/>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>test_hoc_lieu_rag::test_tim_dung_slide[M\u1ed7i b\u1ea3ng trong SQL Server c\xf3 t\u1ed1i \u0111a bao nhi\xeau ch\u1ec9 m\u1ee5c clustered-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 5-1]</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>test_tim_dung_slide[B\u1ea3n sao l\u01b0u differential ch\u1ee9a g\xec-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 6-3]</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr"/>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>test_hoc_lieu_rag::test_tim_dung_slide[B\u1ea3n sao l\u01b0u differential ch\u1ee9a g\xec-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 6-3]</t>
+        </is>
+      </c>
+      <c r="I115" s="4" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>Câu ngoài phạm vi học liệu</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>Tìm một câu hỏi không liên quan môn</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>Kết quả rỗng, không gợi ý bừa</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>test_hoc_lieu_rag::test_cau_ngoai_pham_vi_khong_goi_y</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>Chỉ tìm trong học liệu của đúng môn</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>Tải tài liệu vào môn khác rồi tìm ở cả hai môn</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>Mỗi môn chỉ thấy tài liệu của mình</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>test_hoc_lieu_rag::test_chi_tim_trong_hoc_lieu_cua_dung_khoa</t>
+        </is>
+      </c>
+      <c r="I117" s="4" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>Tải học liệu DOCX/TXT và các lỗi</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Tải DOCX, TXT; tệp .exe, tệp rỗng, loại học liệu sai</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>201 và có chỉ mục; 422 cho các trường hợp lỗi</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>test_hoc_lieu_rag::test_tai_len_docx_txt_va_loi</t>
+        </is>
+      </c>
+      <c r="I118" s="4" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>Gợi ý đọc cho sinh viên làm sai</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>Dữ liệu kết quả gửi Moodle của bài đã phân tích</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>Mỗi SV có danh sách trang/slide thuộc học liệu của môn; không lộ mã câu hỏi</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>test_hoc_lieu_rag::test_goi_y_doc_cho_sv_lam_sai</t>
+        </is>
+      </c>
+      <c r="I119" s="4" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>Tạo lại gợi ý đọc</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>Thêm học liệu rồi gọi readings/rebuild; bài không tồn tại</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>Hầu hết SV có gợi ý; 404</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>test_hoc_lieu_rag::test_tai_tao_goi_y_sau_khi_them_hoc_lieu</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>Lấy học liệu từ khóa học Moodle</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>Moodle giả lập trả danh sách tệp; lấy lần 2; đẩy ngược tệp lấy từ Moodle</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>Thêm tệp mới, không trùng; 409 khi đẩy ngược</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>test_hoc_lieu_rag::test_lay_hoc_lieu_tu_moodle_ve</t>
+        </is>
+      </c>
+      <c r="I121" s="4" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>Đưa học liệu lên Moodle</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>Gọi local_clo_add_resource (giả lập)</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>Nhận course module id; lưu lại để SV mở được</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>test_hoc_lieu_rag::test_day_hoc_lieu_len_moodle</t>
+        </is>
+      </c>
+      <c r="I122" s="4" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>Moodle báo lỗi khi đồng bộ học liệu</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Web Service giả lập trả lỗi</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>502 kèm thông báo</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>test_hoc_lieu_rag::test_moodle_loi_tra_502</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>Gợi ý đọc ở trang Ôn tập</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>Tổng quan Ôn tập của lớp</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>Mỗi SV yếu và mỗi chương có danh sách trang nên đọc</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>test_hoc_lieu_rag::test_on_tap_co_goi_y_doc</t>
+        </is>
+      </c>
+      <c r="I124" s="4" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>Xem lại trang, tải tệp gốc, lập lại chỉ mục</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>Mở trang 2 của slide chương 4; trang không có; tải tệp; lập lại chỉ mục</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>Trang đúng nội dung; 404; tệp PPTX; số trang không đổi</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>test_hoc_lieu_rag::test_xem_tep_goc_trang_va_lap_lai_chi_muc</t>
+        </is>
+      </c>
+      <c r="I125" s="4" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>test_lay_ve_khong_trung_voi_tep_da_day_len</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr"/>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>test_hoc_lieu_rag::test_lay_ve_khong_trung_voi_tep_da_day_len</t>
+        </is>
+      </c>
+      <c r="I126" s="4" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>test_demo_syllabus_approved</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr"/>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t>test_syllabus_versions::test_demo_syllabus_approved</t>
+        </is>
+      </c>
+      <c r="I127" s="4" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>test_syllabus_version_flow</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr"/>
+      <c r="E128" s="4" t="inlineStr"/>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>test_syllabus_versions::test_syllabus_version_flow</t>
+        </is>
+      </c>
+      <c r="I128" s="4" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>test_outline_detail</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr"/>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H129" s="4" t="inlineStr">
+        <is>
+          <t>test_syllabus_versions::test_outline_detail</t>
+        </is>
+      </c>
+      <c r="I129" s="4" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>test_new_course_without_syllabus</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr"/>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>test_syllabus_versions::test_new_course_without_syllabus</t>
+        </is>
+      </c>
+      <c r="I130" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5217,7 +5853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G139"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8202,7 +8838,7 @@
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>test_overview_theo_chuong_va_loc_chuong, test_remedial_flow</t>
+          <t>test_on_tap_co_goi_y_doc, test_overview_theo_chuong_va_loc_chuong, test_remedial_flow</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9888,7 @@
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>test_results_for_moodle</t>
+          <t>test_goi_y_doc_cho_sv_lam_sai, test_results_for_moodle</t>
         </is>
       </c>
     </row>
@@ -10037,17 +10673,17 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>/api/health</t>
+          <t>/api/courses/{cid}/materials</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống</t>
+          <t>Học liệu và gợi ý đọc (RAG)</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra dịch vụ</t>
+          <t>list_materials</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
@@ -10057,7 +10693,7 @@
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>test_auth_me_and_catalogs</t>
+          <t>test_day_hoc_lieu_len_moodle, test_lay_hoc_lieu_tu_moodle_ve, test_lay_ve_khong_trung_voi_tep_da_day_len, test_seed_co_hoc_lieu, test_tai_len_docx_txt_va_loi, test_xem_tep_goc_trang_va_lap_lai_chi_muc</t>
         </is>
       </c>
     </row>
@@ -10067,30 +10703,380 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>/api/courses/{cid}/materials</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>Học liệu và gợi ý đọc (RAG)</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>upload_material</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>test_day_hoc_lieu_len_moodle, test_lay_ve_khong_trung_voi_tep_da_day_len, test_tai_len_docx_txt_va_loi</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>/api/materials/{mid}</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>Học liệu và gợi ý đọc (RAG)</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>delete_material</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>test_chi_tim_trong_hoc_lieu_cua_dung_khoa, test_day_hoc_lieu_len_moodle, test_lay_hoc_lieu_tu_moodle_ve, test_lay_ve_khong_trung_voi_tep_da_day_len, test_tai_len_docx_txt_va_loi</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>/api/materials/{mid}/reindex</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>Học liệu và gợi ý đọc (RAG)</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>reindex</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>test_xem_tep_goc_trang_va_lap_lai_chi_muc</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="C139" s="4" t="inlineStr">
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>/api/materials/{mid}/file</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>Học liệu và gợi ý đọc (RAG)</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>download</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>test_xem_tep_goc_trang_va_lap_lai_chi_muc</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>/api/materials/{mid}/pages/{page}</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>Học liệu và gợi ý đọc (RAG)</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>page_text</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>test_xem_tep_goc_trang_va_lap_lai_chi_muc</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>/api/courses/{cid}/materials/search</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>Học liệu và gợi ý đọc (RAG)</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>Thử truy xuất: gõ câu hỏi/thuật ngữ → trang/slide của học liệu thuộc học phần này.</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>test_cau_ngoai_pham_vi_khong_goi_y, test_chi_tim_trong_hoc_lieu_cua_dung_khoa, test_lay_hoc_lieu_tu_moodle_ve, test_tai_len_docx_txt_va_loi, test_tim_dung_slide[B\u1ea3n, test_tim_dung_slide[Hai</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>/api/exams/{eid}/readings/rebuild</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>Học liệu và gợi ý đọc (RAG)</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>Tạo lại gợi ý đọc của cả bài KT từ học liệu hiện có (dùng sau khi tải thêm học liệu, không cần phân tích lại).</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>test_tai_tao_goi_y_sau_khi_them_hoc_lieu</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>/api/courses/{cid}/materials/sync-moodle</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>Học liệu và gợi ý đọc (RAG)</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>Lấy học liệu đã có trong khóa học Moodle (hoạt động Tệp/Thư mục: PDF, PPTX, DOCX, TXT, MD) về lập chỉ mục.</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>test_lay_hoc_lieu_tu_moodle_ve, test_lay_ve_khong_trung_voi_tep_da_day_len</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>/api/materials/{mid}/push-moodle</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>Học liệu và gợi ý đọc (RAG)</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>Đẩy học liệu lên khóa học Moodle thành hoạt động Tệp để sinh viên xem ngay trên Moodle.</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>test_day_hoc_lieu_len_moodle, test_lay_ve_khong_trung_voi_tep_da_day_len</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>/api/health</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>Hệ thống</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>Kiểm tra dịch vụ</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>test_auth_me_and_catalogs</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
         <is>
           <t>/api/public-config</t>
         </is>
       </c>
-      <c r="D139" s="4" t="inlineStr">
+      <c r="D149" s="4" t="inlineStr">
         <is>
           <t>Hệ thống</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
+      <c r="E149" s="4" t="inlineStr">
         <is>
           <t>Cấu hình công khai cho giao diện</t>
         </is>
       </c>
-      <c r="F139" s="5" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="G139" s="4" t="inlineStr">
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
         <is>
           <t>test_auth_me_and_catalogs</t>
         </is>
@@ -10107,7 +11093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11242,21 +12228,166 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Thời gian làm bài &amp; cảnh báo</t>
+          <t>Học liệu của môn</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Bài Thi cuối kỳ (Moodle) &gt; thẻ 'Thời gian làm bài'; bấm 'Diễn biến' của SV 22130017; đổi ngưỡng giây/câu rồi Áp dụng; Xuất Excel</t>
+          <t>Trang môn học &gt; tab Học liệu: tải lên slide/giáo trình; bấm Lập lại chỉ mục; gõ một câu hỏi vào ô tìm thử</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>4 SV bị cảnh báo (2 làm quá nhanh, 2 để hết giờ tự nộp); biểu đồ từng câu; danh sách đổi theo ngưỡng; tải được Excel</t>
+          <t>Danh sách có số trang đã lập chỉ mục; kết quả tìm là trang/slide đúng kèm độ khớp và đoạn trích</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>GD-39</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>GV</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Gợi ý đọc trong hồ sơ sinh viên</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Lớp học phần &gt; Thống kê &gt; chọn một sinh viên</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Mục Cần đọc lại ở đâu: tên tài liệu, trang/slide, các câu làm sai dẫn tới đó</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>GD-40</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>GV</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Gợi ý đọc ở trang Ôn tập</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Lớp học phần &gt; Ôn tập &gt; tab Theo chương</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Cột Nên đọc lại cho từng chương; tích chọn chương rồi tạo bài kiểm tra cho nhóm vẫn dùng được</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>GD-41</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>GV</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Đồng bộ học liệu với Moodle</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Tab Học liệu: Đưa lên Moodle một tệp; Lấy từ Moodle</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Tệp xuất hiện trong khóa học Moodle; tệp mới trên Moodle được lấy về, không trùng</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>GD-42</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Gợi ý đọc trên Moodle</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Đăng nhập Moodle bằng tài khoản sinh viên &gt; khóa học &gt; Kết quả phân tích CĐR</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Mục Nên đọc lại ở đâu liệt kê trang/slide; bấm tên tài liệu mở được tài nguyên trong khóa học</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>GD-43</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>GV</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Thời gian làm bài &amp; cảnh báo</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Bài Thi cuối kỳ (Moodle) &gt; thẻ 'Thời gian làm bài'; bấm 'Diễn biến' của SV 22130017; đổi ngưỡng giây/câu rồi Áp dụng; Xuất Excel</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>4 SV bị cảnh báo (2 làm quá nhanh, 2 để hết giờ tự nộp); biểu đồ từng câu; danh sách đổi theo ngưỡng; tải được Excel</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/kiem_thu/KET_QUA_KIEM_THU.xlsx
+++ b/docs/kiem_thu/KET_QUA_KIEM_THU.xlsx
@@ -491,14 +491,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Thời điểm chạy: 24/10/2026 20:08 · Python 3.13.17 · CSDL: kiểm thử dựng lại assessment_db</t>
+          <t>Thời điểm chạy: 25/10/2026 10:55 · Python 3.13.17 · CSDL: kiểm thử dựng lại assessment_db</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Ca kiểm thử tự động: 129/129 đạt · Độ phủ API: 147/148 endpoint được gọi thành công</t>
+          <t>Ca kiểm thử tự động: 134/134 đạt · Độ phủ API: 148/149 endpoint được gọi thành công</t>
         </is>
       </c>
     </row>
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>0</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I130"/>
+  <dimension ref="A1:I135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>22.52</v>
+        <v>19.98</v>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="G37" s="4" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="G38" s="4" t="n">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="G39" s="4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="G43" s="4" t="n">
-        <v>11.33</v>
+        <v>10.32</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="G44" s="4" t="n">
-        <v>21.8</v>
+        <v>22.06</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="G45" s="4" t="n">
-        <v>11.35</v>
+        <v>10.56</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>6.05</v>
+        <v>5.85</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         </is>
       </c>
       <c r="G51" s="4" t="n">
-        <v>0.75</v>
+        <v>0.62</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="G53" s="4" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         </is>
       </c>
       <c r="G64" s="4" t="n">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="G66" s="4" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="G67" s="4" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="G68" s="4" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="G69" s="4" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="G70" s="4" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         </is>
       </c>
       <c r="G71" s="4" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="G72" s="4" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="G73" s="4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="G75" s="4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="G76" s="4" t="n">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="G77" s="4" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="G78" s="4" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="G80" s="4" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="G81" s="4" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="G82" s="4" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="G83" s="4" t="n">
-        <v>2.72</v>
+        <v>2.21</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         </is>
       </c>
       <c r="G84" s="4" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="G85" s="4" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="G87" s="4" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="G88" s="4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="G92" s="4" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="G93" s="4" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
@@ -4522,17 +4522,17 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Liên kết mã lớp ⇄ khóa học Moodle</t>
+          <t>Tạo lớp HP tự tạo khóa học Moodle</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Tự nối theo shortname, nối cả môn, gắn thủ công</t>
+          <t>Bộ môn tạo lớp mới khi đã cấu hình Moodle</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Chỉ nối khi GV là giảng viên khóa; chặn trùng</t>
+          <t>Gọi local_clo_provision_course với mã lớp, GV; lưu moodle_course_id</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
@@ -4541,11 +4541,11 @@
         </is>
       </c>
       <c r="G94" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>test_z_toan_bo_chuc_nang::test_link_section_with_moodle_both_ways</t>
+          <t>test_tao_khoa_hoc_moodle::test_tao_lop_tu_tao_khoa_hoc_moodle</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr"/>
@@ -4561,17 +4561,17 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Web Service: Quiz, Offline Quiz, công bố</t>
+          <t>Tạo lớp khi chưa nối Moodle</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Tạo Quiz, tạo đề giấy, trạng thái, xử lý phiếu, tải tệp/.zip, công bố, gửi kết quả, trạng thái WS</t>
+          <t>Tạo lớp HP khi chưa có token Web Service</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Đúng tham số gửi Moodle; không lộ token; 40 kết quả</t>
+          <t>Lớp vẫn được tạo, trạng thái 'skipped'</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
@@ -4580,11 +4580,11 @@
         </is>
       </c>
       <c r="G95" s="4" t="n">
-        <v>0.31</v>
+        <v>0.01</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>test_z_toan_bo_chuc_nang::test_moodle_web_service_flows</t>
+          <t>test_tao_khoa_hoc_moodle::test_tao_lop_khi_chua_cau_hinh_moodle_van_thanh_cong</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr"/>
@@ -4600,17 +4600,17 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ ngân hàng câu hỏi hai chiều</t>
+          <t>Lỗi Moodle không làm hỏng việc tạo lớp</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Đẩy câu mới, nhập câu soạn trên Moodle, Moodle sửa (phiên bản 2) → kéo về</t>
+          <t>Web Service báo lỗi khi tạo lớp; bấm tạo khóa học lại</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Trạng thái đúng từng bước; câu có kết quả không bị ghi đè</t>
+          <t>Lớp vẫn có, trạng thái 'error'; nút tạo lại trả 502</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
@@ -4619,11 +4619,11 @@
         </is>
       </c>
       <c r="G96" s="4" t="n">
-        <v>0.8</v>
+        <v>0.02</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>test_z_toan_bo_chuc_nang::test_question_bank_two_way_sync</t>
+          <t>test_tao_khoa_hoc_moodle::test_loi_moodle_khong_lam_hong_viec_tao_lop</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr"/>
@@ -4634,22 +4634,22 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>11. Thống kê lớp, hồ sơ sinh viên</t>
+          <t>10. Tích hợp Moodle: Web Service, SSO, đồng bộ câu hỏi, liên kết lớp</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Thống kê lớp học phần</t>
+          <t>Ghi danh SV và lưu mã người dùng Moodle</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Chỉ số tổng quan, CLO, Bloom, chương cần ôn, bản đồ nhiệt</t>
+          <t>Lớp có 3 SV, bấm Tạo khóa học trên Moodle, gọi lại lần hai</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Khớp BM6</t>
+          <t>Gửi đủ 3 SV (họ, tên tách đúng); lưu moodle_user_id; gọi lại vẫn thành công</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
@@ -4658,11 +4658,11 @@
         </is>
       </c>
       <c r="G97" s="4" t="n">
-        <v>0.26</v>
+        <v>0.03</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>test_insights::test_section_stats</t>
+          <t>test_tao_khoa_hoc_moodle::test_nut_tao_khoa_hoc_ghi_danh_sv_va_luu_mdl_user_id</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr"/>
@@ -4673,22 +4673,22 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>11. Thống kê lớp, hồ sơ sinh viên</t>
+          <t>10. Tích hợp Moodle: Web Service, SSO, đồng bộ câu hỏi, liên kết lớp</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Hồ sơ từng sinh viên</t>
+          <t>Phân quyền khi tạo khóa học Moodle</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Điểm, thứ hạng, CLO qua các bài, phần cần học lại</t>
+          <t>GV không phụ trách bấm tạo khóa học cho lớp</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Đúng số liệu</t>
+          <t>403</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -4697,11 +4697,11 @@
         </is>
       </c>
       <c r="G98" s="4" t="n">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>test_insights::test_student_profile</t>
+          <t>test_tao_khoa_hoc_moodle::test_gv_khac_khong_tao_duoc_khoa_hoc_cua_lop_nguoi_khac</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr"/>
@@ -4712,22 +4712,22 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>11. Thống kê lớp, hồ sơ sinh viên</t>
+          <t>10. Tích hợp Moodle: Web Service, SSO, đồng bộ câu hỏi, liên kết lớp</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Phân quyền hồ sơ SV</t>
+          <t>Liên kết mã lớp ⇄ khóa học Moodle</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>GV khác, token SV</t>
+          <t>Tự nối theo shortname, nối cả môn, gắn thủ công</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>Chỉ nối khi GV là giảng viên khóa; chặn trùng</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
@@ -4736,11 +4736,11 @@
         </is>
       </c>
       <c r="G99" s="4" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>test_insights::test_profile_access</t>
+          <t>test_z_toan_bo_chuc_nang::test_link_section_with_moodle_both_ways</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr"/>
@@ -4751,22 +4751,22 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>12. Nâng cấp CSDL, cầu nối</t>
+          <t>10. Tích hợp Moodle: Web Service, SSO, đồng bộ câu hỏi, liên kết lớp</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Cầu nối khi Moodle chưa cài Offline Quiz</t>
+          <t>Web Service: Quiz, Offline Quiz, công bố</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Cài cầu nối</t>
+          <t>Tạo Quiz, tạo đề giấy, trạng thái, xử lý phiếu, tải tệp/.zip, công bố, gửi kết quả, trạng thái WS</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Vẫn chạy cho Quiz</t>
+          <t>Đúng tham số gửi Moodle; không lộ token; 40 kết quả</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
@@ -4775,11 +4775,11 @@
         </is>
       </c>
       <c r="G100" s="4" t="n">
-        <v>0.04</v>
+        <v>0.29</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>test_upgrade::test_bridge_without_offlinequiz_plugin</t>
+          <t>test_z_toan_bo_chuc_nang::test_moodle_web_service_flows</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr"/>
@@ -4790,22 +4790,22 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>12. Nâng cấp CSDL, cầu nối</t>
+          <t>10. Tích hợp Moodle: Web Service, SSO, đồng bộ câu hỏi, liên kết lớp</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Nâng cấp CSDL phiên bản cũ</t>
+          <t>Đồng bộ ngân hàng câu hỏi hai chiều</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>CSDL thiếu cột mới, CHECK cũ</t>
+          <t>Đẩy câu mới, nhập câu soạn trên Moodle, Moodle sửa (phiên bản 2) → kéo về</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Tự thêm cột, thay CHECK, nạp CTĐT 2026</t>
+          <t>Trạng thái đúng từng bước; câu có kết quả không bị ghi đè</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
@@ -4814,11 +4814,11 @@
         </is>
       </c>
       <c r="G101" s="4" t="n">
-        <v>0.24</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>test_upgrade::test_upgrade_old_database_adds_offlinequiz_column</t>
+          <t>test_z_toan_bo_chuc_nang::test_question_bank_two_way_sync</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr"/>
@@ -4829,22 +4829,22 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+          <t>11. Thống kê lớp, hồ sơ sinh viên</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Tính thời gian trả lời từng câu</t>
+          <t>Thống kê lớp học phần</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Dãy thời điểm chọn đáp án; nhiều câu cùng một trang (cùng thời điểm)</t>
+          <t>Chỉ số tổng quan, CLO, Bloom, chương cần ôn, bản đồ nhiệt</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Thời gian = khoảng cách tới lần chọn trước; câu cùng trang chia đều; báo độ phân giải theo trang</t>
+          <t>Khớp BM6</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
@@ -4853,11 +4853,11 @@
         </is>
       </c>
       <c r="G102" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>test_timing::test_response_time_split_and_page_resolution</t>
+          <t>test_insights::test_section_stats</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr"/>
@@ -4868,22 +4868,22 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+          <t>11. Thống kê lớp, hồ sơ sinh viên</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ thời điểm chọn đáp án từ Moodle</t>
+          <t>Hồ sơ từng sinh viên</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ Quiz có giới hạn 45 phút, tự nộp khi hết giờ</t>
+          <t>Điểm, thứ hạng, CLO qua các bài, phần cần học lại</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Lưu lần chọn đầu/cuối, số lần lưu từng câu; giới hạn thời gian; lượt hết giờ tự nộp</t>
+          <t>Đúng số liệu</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
@@ -4892,11 +4892,11 @@
         </is>
       </c>
       <c r="G103" s="4" t="n">
-        <v>0.01</v>
+        <v>0.17</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>test_timing::test_sync_stores_answer_times</t>
+          <t>test_insights::test_student_profile</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr"/>
@@ -4907,22 +4907,22 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+          <t>11. Thống kê lớp, hồ sơ sinh viên</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Cảnh báo SV chọn đại / chọn xong để hết giờ</t>
+          <t>Phân quyền hồ sơ SV</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Dữ liệu có 2 SV chọn ~20 câu trong 1 phút và 2 SV chọn xong không nộp chờ hết giờ</t>
+          <t>GV khác, token SV</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Đúng 4 SV bị cảnh báo đúng loại; SV bình thường không bị gắn cờ; số cảnh báo hiện ở danh sách bài KT</t>
+          <t>403</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
@@ -4931,11 +4931,11 @@
         </is>
       </c>
       <c r="G104" s="4" t="n">
-        <v>0.41</v>
+        <v>0.13</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>test_timing::test_timing_report_flags_planted_students</t>
+          <t>test_insights::test_profile_access</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr"/>
@@ -4946,22 +4946,22 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
+          <t>12. Nâng cấp CSDL, cầu nối</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Đổi ngưỡng, diễn biến từng SV, xuất Excel</t>
+          <t>Cầu nối khi Moodle chưa cài Offline Quiz</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Gửi ngưỡng tùy chỉnh / sai; xem diễn biến 1 SV; tải Excel; bài giấy</t>
+          <t>Cài cầu nối</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Kết quả theo ngưỡng; ngưỡng sai 422; SV không làm 404; Excel 2 sheet; bài giấy báo không áp dụng</t>
+          <t>Vẫn chạy cho Quiz</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
@@ -4970,11 +4970,11 @@
         </is>
       </c>
       <c r="G105" s="4" t="n">
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>test_timing::test_timing_thresholds_timeline_and_export</t>
+          <t>test_upgrade::test_bridge_without_offlinequiz_plugin</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr"/>
@@ -4985,27 +4985,35 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+          <t>12. Nâng cấp CSDL, cầu nối</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>test_seed_backfilled_clo_pi</t>
-        </is>
-      </c>
-      <c r="D106" s="4" t="inlineStr"/>
-      <c r="E106" s="4" t="inlineStr"/>
+          <t>Nâng cấp CSDL phiên bản cũ</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>CSDL thiếu cột mới, CHECK cũ</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>Tự thêm cột, thay CHECK, nạp CTĐT 2026</t>
+        </is>
+      </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
       </c>
       <c r="G106" s="4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>test_clo_pi::test_seed_backfilled_clo_pi</t>
+          <t>test_upgrade::test_upgrade_old_database_adds_offlinequiz_column</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr"/>
@@ -5016,27 +5024,35 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>test_clo_pi_mapping_derives_plo</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr"/>
-      <c r="E107" s="4" t="inlineStr"/>
+          <t>Tính thời gian trả lời từng câu</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Dãy thời điểm chọn đáp án; nhiều câu cùng một trang (cùng thời điểm)</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>Thời gian = khoảng cách tới lần chọn trước; câu cùng trang chia đều; báo độ phân giải theo trang</t>
+        </is>
+      </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
       </c>
       <c r="G107" s="4" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>test_clo_pi::test_clo_pi_mapping_derives_plo</t>
+          <t>test_timing::test_response_time_split_and_page_resolution</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr"/>
@@ -5047,27 +5063,35 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>test_backfill_from_legacy_plo</t>
-        </is>
-      </c>
-      <c r="D108" s="4" t="inlineStr"/>
-      <c r="E108" s="4" t="inlineStr"/>
+          <t>Đồng bộ thời điểm chọn đáp án từ Moodle</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>Đồng bộ Quiz có giới hạn 45 phút, tự nộp khi hết giờ</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>Lưu lần chọn đầu/cuối, số lần lưu từng câu; giới hạn thời gian; lượt hết giờ tự nộp</t>
+        </is>
+      </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
       </c>
       <c r="G108" s="4" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>test_clo_pi::test_backfill_from_legacy_plo</t>
+          <t>test_timing::test_sync_stores_answer_times</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr"/>
@@ -5078,27 +5102,35 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>test_question_outcome_tree</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr"/>
-      <c r="E109" s="4" t="inlineStr"/>
+          <t>Cảnh báo SV chọn đại / chọn xong để hết giờ</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Dữ liệu có 2 SV chọn ~20 câu trong 1 phút và 2 SV chọn xong không nộp chờ hết giờ</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>Đúng 4 SV bị cảnh báo đúng loại; SV bình thường không bị gắn cờ; số cảnh báo hiện ở danh sách bài KT</t>
+        </is>
+      </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
       </c>
       <c r="G109" s="4" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>test_clo_pi::test_question_outcome_tree</t>
+          <t>test_timing::test_timing_report_flags_planted_students</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr"/>
@@ -5109,22 +5141,22 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+          <t>13. Thời gian làm bài &amp; cảnh báo bất thường</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Học liệu mẫu có sẵn</t>
+          <t>Đổi ngưỡng, diễn biến từng SV, xuất Excel</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Danh sách học liệu của môn DBMS330284</t>
+          <t>Gửi ngưỡng tùy chỉnh / sai; xem diễn biến 1 SV; tải Excel; bài giấy</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>7 học liệu (6 slide + 1 giáo trình), số trang khớp nội dung đã sinh</t>
+          <t>Kết quả theo ngưỡng; ngưỡng sai 422; SV không làm 404; Excel 2 sheet; bài giấy báo không áp dụng</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
@@ -5133,11 +5165,11 @@
         </is>
       </c>
       <c r="G110" s="4" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>test_hoc_lieu_rag::test_seed_co_hoc_lieu</t>
+          <t>test_timing::test_timing_thresholds_timeline_and_export</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr"/>
@@ -5153,7 +5185,7 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>test_tim_dung_slide[T\u1ec7p nh\u1eadt k\xfd giao t\xe1c (.ldf) trong SQL Server \u0111\u01b0\u1ee3c d\xf9ng ch\u1ee7 y\u1ebfu \u0111\u1ec3 ph\u1ee5c h\u1ed3i-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 1-4]</t>
+          <t>test_seed_backfilled_clo_pi</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr"/>
@@ -5164,11 +5196,11 @@
         </is>
       </c>
       <c r="G111" s="4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>test_hoc_lieu_rag::test_tim_dung_slide[T\u1ec7p nh\u1eadt k\xfd giao t\xe1c (.ldf) trong SQL Server \u0111\u01b0\u1ee3c d\xf9ng ch\u1ee7 y\u1ebfu \u0111\u1ec3 ph\u1ee5c h\u1ed3i-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 1-4]</t>
+          <t>test_clo_pi::test_seed_backfilled_clo_pi</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr"/>
@@ -5184,7 +5216,7 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>test_tim_dung_slide[Trong trigger AFTER UPDATE b\u1ea3ng t\u1ea1m n\xe0o ch\u1ee9a gi\xe1 tr\u1ecb C\u0168 c\u1ee7a c\xe1c d\xf2ng b\u1ecb c\u1eadp nh\u1eadt-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 3-1]</t>
+          <t>test_clo_pi_mapping_derives_plo</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr"/>
@@ -5195,11 +5227,11 @@
         </is>
       </c>
       <c r="G112" s="4" t="n">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>test_hoc_lieu_rag::test_tim_dung_slide[Trong trigger AFTER UPDATE b\u1ea3ng t\u1ea1m n\xe0o ch\u1ee9a gi\xe1 tr\u1ecb C\u0168 c\u1ee7a c\xe1c d\xf2ng b\u1ecb c\u1eadp nh\u1eadt-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 3-1]</t>
+          <t>test_clo_pi::test_clo_pi_mapping_derives_plo</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr"/>
@@ -5215,7 +5247,7 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>test_tim_dung_slide[Hai giao t\xe1c gi\u1eef kh\xf3a ch\u1edd nhau deadlock ch\u1ecdn n\u1ea1n nh\xe2n victim-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 4-4]</t>
+          <t>test_backfill_from_legacy_plo</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr"/>
@@ -5226,11 +5258,11 @@
         </is>
       </c>
       <c r="G113" s="4" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>test_hoc_lieu_rag::test_tim_dung_slide[Hai giao t\xe1c gi\u1eef kh\xf3a ch\u1edd nhau deadlock ch\u1ecdn n\u1ea1n nh\xe2n victim-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 4-4]</t>
+          <t>test_clo_pi::test_backfill_from_legacy_plo</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr"/>
@@ -5246,7 +5278,7 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>test_tim_dung_slide[M\u1ed7i b\u1ea3ng trong SQL Server c\xf3 t\u1ed1i \u0111a bao nhi\xeau ch\u1ec9 m\u1ee5c clustered-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 5-1]</t>
+          <t>test_question_outcome_tree</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr"/>
@@ -5257,11 +5289,11 @@
         </is>
       </c>
       <c r="G114" s="4" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>test_hoc_lieu_rag::test_tim_dung_slide[M\u1ed7i b\u1ea3ng trong SQL Server c\xf3 t\u1ed1i \u0111a bao nhi\xeau ch\u1ec9 m\u1ee5c clustered-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 5-1]</t>
+          <t>test_clo_pi::test_question_outcome_tree</t>
         </is>
       </c>
       <c r="I114" s="4" t="inlineStr"/>
@@ -5277,11 +5309,19 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>test_tim_dung_slide[B\u1ea3n sao l\u01b0u differential ch\u1ee9a g\xec-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 6-3]</t>
-        </is>
-      </c>
-      <c r="D115" s="4" t="inlineStr"/>
-      <c r="E115" s="4" t="inlineStr"/>
+          <t>Học liệu mẫu có sẵn</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Danh sách học liệu của môn DBMS330284</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>7 học liệu (6 slide + 1 giáo trình), số trang khớp nội dung đã sinh</t>
+        </is>
+      </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
           <t>ĐẠT</t>
@@ -5292,7 +5332,7 @@
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>test_hoc_lieu_rag::test_tim_dung_slide[B\u1ea3n sao l\u01b0u differential ch\u1ee9a g\xec-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 6-3]</t>
+          <t>test_hoc_lieu_rag::test_seed_co_hoc_lieu</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr"/>
@@ -5308,19 +5348,11 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Câu ngoài phạm vi học liệu</t>
-        </is>
-      </c>
-      <c r="D116" s="4" t="inlineStr">
-        <is>
-          <t>Tìm một câu hỏi không liên quan môn</t>
-        </is>
-      </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>Kết quả rỗng, không gợi ý bừa</t>
-        </is>
-      </c>
+          <t>test_tim_dung_slide[T\u1ec7p nh\u1eadt k\xfd giao t\xe1c (.ldf) trong SQL Server \u0111\u01b0\u1ee3c d\xf9ng ch\u1ee7 y\u1ebfu \u0111\u1ec3 ph\u1ee5c h\u1ed3i-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 1-4]</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr"/>
+      <c r="E116" s="4" t="inlineStr"/>
       <c r="F116" s="5" t="inlineStr">
         <is>
           <t>ĐẠT</t>
@@ -5331,7 +5363,7 @@
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>test_hoc_lieu_rag::test_cau_ngoai_pham_vi_khong_goi_y</t>
+          <t>test_hoc_lieu_rag::test_tim_dung_slide[T\u1ec7p nh\u1eadt k\xfd giao t\xe1c (.ldf) trong SQL Server \u0111\u01b0\u1ee3c d\xf9ng ch\u1ee7 y\u1ebfu \u0111\u1ec3 ph\u1ee5c h\u1ed3i-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 1-4]</t>
         </is>
       </c>
       <c r="I116" s="4" t="inlineStr"/>
@@ -5347,30 +5379,22 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Chỉ tìm trong học liệu của đúng môn</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="inlineStr">
-        <is>
-          <t>Tải tài liệu vào môn khác rồi tìm ở cả hai môn</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>Mỗi môn chỉ thấy tài liệu của mình</t>
-        </is>
-      </c>
+          <t>test_tim_dung_slide[Trong trigger AFTER UPDATE b\u1ea3ng t\u1ea1m n\xe0o ch\u1ee9a gi\xe1 tr\u1ecb C\u0168 c\u1ee7a c\xe1c d\xf2ng b\u1ecb c\u1eadp nh\u1eadt-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 3-1]</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr"/>
+      <c r="E117" s="4" t="inlineStr"/>
       <c r="F117" s="5" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
       </c>
       <c r="G117" s="4" t="n">
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>test_hoc_lieu_rag::test_chi_tim_trong_hoc_lieu_cua_dung_khoa</t>
+          <t>test_hoc_lieu_rag::test_tim_dung_slide[Trong trigger AFTER UPDATE b\u1ea3ng t\u1ea1m n\xe0o ch\u1ee9a gi\xe1 tr\u1ecb C\u0168 c\u1ee7a c\xe1c d\xf2ng b\u1ecb c\u1eadp nh\u1eadt-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 3-1]</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr"/>
@@ -5386,30 +5410,22 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Tải học liệu DOCX/TXT và các lỗi</t>
-        </is>
-      </c>
-      <c r="D118" s="4" t="inlineStr">
-        <is>
-          <t>Tải DOCX, TXT; tệp .exe, tệp rỗng, loại học liệu sai</t>
-        </is>
-      </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>201 và có chỉ mục; 422 cho các trường hợp lỗi</t>
-        </is>
-      </c>
+          <t>test_tim_dung_slide[Hai giao t\xe1c gi\u1eef kh\xf3a ch\u1edd nhau deadlock ch\u1ecdn n\u1ea1n nh\xe2n victim-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 4-4]</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr"/>
+      <c r="E118" s="4" t="inlineStr"/>
       <c r="F118" s="5" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
       </c>
       <c r="G118" s="4" t="n">
-        <v>0.16</v>
+        <v>0.01</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>test_hoc_lieu_rag::test_tai_len_docx_txt_va_loi</t>
+          <t>test_hoc_lieu_rag::test_tim_dung_slide[Hai giao t\xe1c gi\u1eef kh\xf3a ch\u1edd nhau deadlock ch\u1ecdn n\u1ea1n nh\xe2n victim-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 4-4]</t>
         </is>
       </c>
       <c r="I118" s="4" t="inlineStr"/>
@@ -5425,30 +5441,22 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Gợi ý đọc cho sinh viên làm sai</t>
-        </is>
-      </c>
-      <c r="D119" s="4" t="inlineStr">
-        <is>
-          <t>Dữ liệu kết quả gửi Moodle của bài đã phân tích</t>
-        </is>
-      </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>Mỗi SV có danh sách trang/slide thuộc học liệu của môn; không lộ mã câu hỏi</t>
-        </is>
-      </c>
+          <t>test_tim_dung_slide[M\u1ed7i b\u1ea3ng trong SQL Server c\xf3 t\u1ed1i \u0111a bao nhi\xeau ch\u1ec9 m\u1ee5c clustered-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 5-1]</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr"/>
+      <c r="E119" s="4" t="inlineStr"/>
       <c r="F119" s="5" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
       </c>
       <c r="G119" s="4" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>test_hoc_lieu_rag::test_goi_y_doc_cho_sv_lam_sai</t>
+          <t>test_hoc_lieu_rag::test_tim_dung_slide[M\u1ed7i b\u1ea3ng trong SQL Server c\xf3 t\u1ed1i \u0111a bao nhi\xeau ch\u1ec9 m\u1ee5c clustered-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 5-1]</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr"/>
@@ -5464,30 +5472,22 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Tạo lại gợi ý đọc</t>
-        </is>
-      </c>
-      <c r="D120" s="4" t="inlineStr">
-        <is>
-          <t>Thêm học liệu rồi gọi readings/rebuild; bài không tồn tại</t>
-        </is>
-      </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>Hầu hết SV có gợi ý; 404</t>
-        </is>
-      </c>
+          <t>test_tim_dung_slide[B\u1ea3n sao l\u01b0u differential ch\u1ee9a g\xec-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 6-3]</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr"/>
+      <c r="E120" s="4" t="inlineStr"/>
       <c r="F120" s="5" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
       </c>
       <c r="G120" s="4" t="n">
-        <v>0.34</v>
+        <v>0.01</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>test_hoc_lieu_rag::test_tai_tao_goi_y_sau_khi_them_hoc_lieu</t>
+          <t>test_hoc_lieu_rag::test_tim_dung_slide[B\u1ea3n sao l\u01b0u differential ch\u1ee9a g\xec-Slide b\xe0i gi\u1ea3ng \u2013 Ch\u01b0\u01a1ng 6-3]</t>
         </is>
       </c>
       <c r="I120" s="4" t="inlineStr"/>
@@ -5503,17 +5503,17 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Lấy học liệu từ khóa học Moodle</t>
+          <t>Câu ngoài phạm vi học liệu</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Moodle giả lập trả danh sách tệp; lấy lần 2; đẩy ngược tệp lấy từ Moodle</t>
+          <t>Tìm một câu hỏi không liên quan môn</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>Thêm tệp mới, không trùng; 409 khi đẩy ngược</t>
+          <t>Kết quả rỗng, không gợi ý bừa</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
@@ -5522,11 +5522,11 @@
         </is>
       </c>
       <c r="G121" s="4" t="n">
-        <v>0.14</v>
+        <v>0.01</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>test_hoc_lieu_rag::test_lay_hoc_lieu_tu_moodle_ve</t>
+          <t>test_hoc_lieu_rag::test_cau_ngoai_pham_vi_khong_goi_y</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr"/>
@@ -5542,17 +5542,17 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Đưa học liệu lên Moodle</t>
+          <t>Chỉ tìm trong học liệu của đúng môn</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Gọi local_clo_add_resource (giả lập)</t>
+          <t>Tải tài liệu vào môn khác rồi tìm ở cả hai môn</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>Nhận course module id; lưu lại để SV mở được</t>
+          <t>Mỗi môn chỉ thấy tài liệu của mình</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
@@ -5561,11 +5561,11 @@
         </is>
       </c>
       <c r="G122" s="4" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>test_hoc_lieu_rag::test_day_hoc_lieu_len_moodle</t>
+          <t>test_hoc_lieu_rag::test_chi_tim_trong_hoc_lieu_cua_dung_khoa</t>
         </is>
       </c>
       <c r="I122" s="4" t="inlineStr"/>
@@ -5581,17 +5581,17 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Moodle báo lỗi khi đồng bộ học liệu</t>
+          <t>Tải học liệu DOCX/TXT và các lỗi</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Web Service giả lập trả lỗi</t>
+          <t>Tải DOCX, TXT; tệp .exe, tệp rỗng, loại học liệu sai</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>502 kèm thông báo</t>
+          <t>201 và có chỉ mục; 422 cho các trường hợp lỗi</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
@@ -5600,11 +5600,11 @@
         </is>
       </c>
       <c r="G123" s="4" t="n">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>test_hoc_lieu_rag::test_moodle_loi_tra_502</t>
+          <t>test_hoc_lieu_rag::test_tai_len_docx_txt_va_loi</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr"/>
@@ -5620,17 +5620,17 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Gợi ý đọc ở trang Ôn tập</t>
+          <t>Gợi ý đọc cho sinh viên làm sai</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Tổng quan Ôn tập của lớp</t>
+          <t>Dữ liệu kết quả gửi Moodle của bài đã phân tích</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>Mỗi SV yếu và mỗi chương có danh sách trang nên đọc</t>
+          <t>Mỗi SV có danh sách trang/slide thuộc học liệu của môn; không lộ mã câu hỏi</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
@@ -5639,11 +5639,11 @@
         </is>
       </c>
       <c r="G124" s="4" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>test_hoc_lieu_rag::test_on_tap_co_goi_y_doc</t>
+          <t>test_hoc_lieu_rag::test_goi_y_doc_cho_sv_lam_sai</t>
         </is>
       </c>
       <c r="I124" s="4" t="inlineStr"/>
@@ -5659,17 +5659,17 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Xem lại trang, tải tệp gốc, lập lại chỉ mục</t>
+          <t>Tạo lại gợi ý đọc</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Mở trang 2 của slide chương 4; trang không có; tải tệp; lập lại chỉ mục</t>
+          <t>Thêm học liệu rồi gọi readings/rebuild; bài không tồn tại</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>Trang đúng nội dung; 404; tệp PPTX; số trang không đổi</t>
+          <t>Hầu hết SV có gợi ý; 404</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
@@ -5678,11 +5678,11 @@
         </is>
       </c>
       <c r="G125" s="4" t="n">
-        <v>0.06</v>
+        <v>0.29</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>test_hoc_lieu_rag::test_xem_tep_goc_trang_va_lap_lai_chi_muc</t>
+          <t>test_hoc_lieu_rag::test_tai_tao_goi_y_sau_khi_them_hoc_lieu</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr"/>
@@ -5698,22 +5698,30 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>test_lay_ve_khong_trung_voi_tep_da_day_len</t>
-        </is>
-      </c>
-      <c r="D126" s="4" t="inlineStr"/>
-      <c r="E126" s="4" t="inlineStr"/>
+          <t>Lấy học liệu từ khóa học Moodle</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>Moodle giả lập trả danh sách tệp; lấy lần 2; đẩy ngược tệp lấy từ Moodle</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>Thêm tệp mới, không trùng; 409 khi đẩy ngược</t>
+        </is>
+      </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
       </c>
       <c r="G126" s="4" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>test_hoc_lieu_rag::test_lay_ve_khong_trung_voi_tep_da_day_len</t>
+          <t>test_hoc_lieu_rag::test_lay_hoc_lieu_tu_moodle_ve</t>
         </is>
       </c>
       <c r="I126" s="4" t="inlineStr"/>
@@ -5729,11 +5737,19 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>test_demo_syllabus_approved</t>
-        </is>
-      </c>
-      <c r="D127" s="4" t="inlineStr"/>
-      <c r="E127" s="4" t="inlineStr"/>
+          <t>Đưa học liệu lên Moodle</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>Gọi local_clo_add_resource (giả lập)</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>Nhận course module id; lưu lại để SV mở được</t>
+        </is>
+      </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
           <t>ĐẠT</t>
@@ -5744,7 +5760,7 @@
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>test_syllabus_versions::test_demo_syllabus_approved</t>
+          <t>test_hoc_lieu_rag::test_day_hoc_lieu_len_moodle</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr"/>
@@ -5760,22 +5776,30 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>test_syllabus_version_flow</t>
-        </is>
-      </c>
-      <c r="D128" s="4" t="inlineStr"/>
-      <c r="E128" s="4" t="inlineStr"/>
+          <t>Moodle báo lỗi khi đồng bộ học liệu</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>Web Service giả lập trả lỗi</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>502 kèm thông báo</t>
+        </is>
+      </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
       </c>
       <c r="G128" s="4" t="n">
-        <v>0.37</v>
+        <v>0.01</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>test_syllabus_versions::test_syllabus_version_flow</t>
+          <t>test_hoc_lieu_rag::test_moodle_loi_tra_502</t>
         </is>
       </c>
       <c r="I128" s="4" t="inlineStr"/>
@@ -5791,22 +5815,30 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>test_outline_detail</t>
-        </is>
-      </c>
-      <c r="D129" s="4" t="inlineStr"/>
-      <c r="E129" s="4" t="inlineStr"/>
+          <t>Gợi ý đọc ở trang Ôn tập</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>Tổng quan Ôn tập của lớp</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>Mỗi SV yếu và mỗi chương có danh sách trang nên đọc</t>
+        </is>
+      </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
           <t>ĐẠT</t>
         </is>
       </c>
       <c r="G129" s="4" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>test_syllabus_versions::test_outline_detail</t>
+          <t>test_hoc_lieu_rag::test_on_tap_co_goi_y_doc</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr"/>
@@ -5822,25 +5854,188 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
+          <t>Xem lại trang, tải tệp gốc, lập lại chỉ mục</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>Mở trang 2 của slide chương 4; trang không có; tải tệp; lập lại chỉ mục</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>Trang đúng nội dung; 404; tệp PPTX; số trang không đổi</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>test_hoc_lieu_rag::test_xem_tep_goc_trang_va_lap_lai_chi_muc</t>
+        </is>
+      </c>
+      <c r="I130" s="4" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>test_lay_ve_khong_trung_voi_tep_da_day_len</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr"/>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t>test_hoc_lieu_rag::test_lay_ve_khong_trung_voi_tep_da_day_len</t>
+        </is>
+      </c>
+      <c r="I131" s="4" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>test_demo_syllabus_approved</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr"/>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>test_syllabus_versions::test_demo_syllabus_approved</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>test_syllabus_version_flow</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr"/>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>test_syllabus_versions::test_syllabus_version_flow</t>
+        </is>
+      </c>
+      <c r="I133" s="4" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>test_outline_detail</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr"/>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>test_syllabus_versions::test_outline_detail</t>
+        </is>
+      </c>
+      <c r="I134" s="4" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>14. Học liệu và gợi ý đọc (RAG theo trang)</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
           <t>test_new_course_without_syllabus</t>
         </is>
       </c>
-      <c r="D130" s="4" t="inlineStr"/>
-      <c r="E130" s="4" t="inlineStr"/>
-      <c r="F130" s="5" t="inlineStr">
-        <is>
-          <t>ĐẠT</t>
-        </is>
-      </c>
-      <c r="G130" s="4" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H130" s="4" t="inlineStr">
+      <c r="D135" s="4" t="inlineStr"/>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H135" s="4" t="inlineStr">
         <is>
           <t>test_syllabus_versions::test_new_course_without_syllabus</t>
         </is>
       </c>
-      <c r="I130" s="4" t="inlineStr"/>
+      <c r="I135" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5853,7 +6048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7278,7 +7473,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections</t>
+          <t>/api/class-sections/{cs_id}/moodle-provision</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -7288,7 +7483,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>create_section</t>
+          <t>Tạo khóa học Moodle cho lớp (nếu chưa có) và ghi danh GV phụ trách + SV đang học; gọi lại để bổ sung người còn thiếu.</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -7298,7 +7493,7 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>test_new_course_setup_flow</t>
+          <t>test_nut_tao_khoa_hoc_ghi_danh_sv_va_luu_mdl_user_id</t>
         </is>
       </c>
     </row>
@@ -7308,12 +7503,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}</t>
+          <t>/api/class-sections</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -7323,7 +7518,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>update_section</t>
+          <t>create_section</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -7333,7 +7528,7 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>test_new_course_setup_flow</t>
+          <t>test_gv_khac_khong_tao_duoc_khoa_hoc_cua_lop_nguoi_khac, test_loi_moodle_khong_lam_hong_viec_tao_lop, test_new_course_setup_flow, test_nut_tao_khoa_hoc_ghi_danh_sv_va_luu_mdl_user_id, test_tao_lop_khi_chua_cau_hinh_moodle_van_thanh_cong, test_tao_lop_tu_tao_khoa_hoc_moodle</t>
         </is>
       </c>
     </row>
@@ -7343,7 +7538,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -7358,7 +7553,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>delete_section</t>
+          <t>update_section</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -7368,7 +7563,7 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>test_import_moodle_course, test_new_course_setup_flow</t>
+          <t>test_new_course_setup_flow</t>
         </is>
       </c>
     </row>
@@ -7378,12 +7573,12 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>/api/moodle/my-courses</t>
+          <t>/api/class-sections/{cs_id}</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -7393,7 +7588,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Khóa học trên Moodle của GV (Bộ môn: mọi khóa học) kèm lớp HP đã gắn, hoặc gợi ý môn học / học kỳ / GV để đưa vào hệ thống.</t>
+          <t>delete_section</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -7403,7 +7598,7 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>test_import_moodle_course</t>
+          <t>test_import_moodle_course, test_new_course_setup_flow</t>
         </is>
       </c>
     </row>
@@ -7413,12 +7608,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>/api/moodle/courses/{mid}/import</t>
+          <t>/api/moodle/my-courses</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -7428,7 +7623,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Tạo lớp HP từ một khóa học Moodle và lấy danh sách SV đang ghi danh. GV chỉ đưa vào khóa học mình là giảng viên</t>
+          <t>Khóa học trên Moodle của GV (Bộ môn: mọi khóa học) kèm lớp HP đã gắn, hoặc gợi ý môn học / học kỳ / GV để đưa vào hệ thống.</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -7453,7 +7648,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/moodle-roster</t>
+          <t>/api/moodle/courses/{mid}/import</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -7463,7 +7658,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Cập nhật danh sách SV của lớp HP theo ghi danh hiện tại của khóa học Moodle đã gắn (chỉ thêm, không xóa).</t>
+          <t>Tạo lớp HP từ một khóa học Moodle và lấy danh sách SV đang ghi danh. GV chỉ đưa vào khóa học mình là giảng viên</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -7488,7 +7683,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/moodle-autolink</t>
+          <t>/api/class-sections/{cs_id}/moodle-roster</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -7498,7 +7693,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>moodle_autolink</t>
+          <t>Cập nhật danh sách SV của lớp HP theo ghi danh hiện tại của khóa học Moodle đã gắn (chỉ thêm, không xóa).</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -7508,7 +7703,7 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>test_link_section_with_moodle_both_ways</t>
+          <t>test_import_moodle_course</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7718,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{cid}/moodle-sync-sections</t>
+          <t>/api/class-sections/{cs_id}/moodle-autolink</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -7533,7 +7728,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Một lần bấm cho cả môn: gắn các lớp HP (của GV) với khóa học Moodle trùng mã lớp và cập nhật danh sách SV từ Moodle.</t>
+          <t>moodle_autolink</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -7553,22 +7748,22 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>/api/questions/import-template</t>
+          <t>/api/courses/{cid}/moodle-sync-sections</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>UC-01 Nhập câu hỏi &amp; gán CLO từ file</t>
+          <t>UC-12 Học phần, chương, CLO, lớp học phần</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>import_template</t>
+          <t>Một lần bấm cho cả môn: gắn các lớp HP (của GV) với khóa học Moodle trùng mã lớp và cập nhật danh sách SV từ Moodle.</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -7578,7 +7773,7 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>test_clo_lifecycle_cancel_question_and_template</t>
+          <t>test_link_section_with_moodle_both_ways</t>
         </is>
       </c>
     </row>
@@ -7588,12 +7783,12 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>/api/questions/import</t>
+          <t>/api/questions/import-template</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -7603,7 +7798,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>import_questions</t>
+          <t>import_template</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -7613,7 +7808,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>test_aiken_and_moodle_xml, test_bulk_import_then_tag</t>
+          <t>test_clo_lifecycle_cancel_question_and_template</t>
         </is>
       </c>
     </row>
@@ -7623,12 +7818,12 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>/api/questions/tagging-template</t>
+          <t>/api/questions/import</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -7638,7 +7833,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>tagging_template</t>
+          <t>import_questions</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
@@ -7648,7 +7843,7 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>test_bulk_import_then_tag</t>
+          <t>test_aiken_and_moodle_xml, test_bulk_import_then_tag</t>
         </is>
       </c>
     </row>
@@ -7658,12 +7853,12 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>/api/questions/tagging-import</t>
+          <t>/api/questions/tagging-template</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -7673,7 +7868,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>tagging_import</t>
+          <t>tagging_template</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -7683,7 +7878,7 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>test_bulk_import_then_tag, test_tagging_locks_used_questions</t>
+          <t>test_bulk_import_then_tag</t>
         </is>
       </c>
     </row>
@@ -7693,22 +7888,22 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>/api/questions</t>
+          <t>/api/questions/tagging-import</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>UC-01 Ngân hàng câu hỏi</t>
+          <t>UC-01 Nhập câu hỏi &amp; gán CLO từ file</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>list_questions</t>
+          <t>tagging_import</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
@@ -7718,7 +7913,7 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>test_assignment_all_supervisors, test_bulk_import_then_tag, test_copy_exam_manual_items_and_paper_versions, test_course_level_access, test_manual_exam_grid_excel_and_analysis, test_moodle_web_service_flows</t>
+          <t>test_bulk_import_then_tag, test_tagging_locks_used_questions</t>
         </is>
       </c>
     </row>
@@ -7733,7 +7928,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>/api/questions/tree</t>
+          <t>/api/questions</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -7743,7 +7938,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Cây CTĐT → PLO → PI → CLO của học phần với số câu hỏi đang dùng ở mỗi nút (góp ý F2a);</t>
+          <t>list_questions</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -7753,7 +7948,7 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>test_question_outcome_tree</t>
+          <t>test_assignment_all_supervisors, test_bulk_import_then_tag, test_copy_exam_manual_items_and_paper_versions, test_course_level_access, test_manual_exam_grid_excel_and_analysis, test_moodle_web_service_flows</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7963,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>/api/questions/{qid}</t>
+          <t>/api/questions/tree</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -7778,7 +7973,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>get_question</t>
+          <t>Cây CTĐT → PLO → PI → CLO của học phần với số câu hỏi đang dùng ở mỗi nút (góp ý F2a);</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
@@ -7788,7 +7983,7 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>test_bulk_import_then_tag, test_clo_lifecycle_cancel_question_and_template, test_question_bank_two_way_sync, test_question_edit_rules, test_tagging_locks_used_questions</t>
+          <t>test_question_outcome_tree</t>
         </is>
       </c>
     </row>
@@ -7798,12 +7993,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>/api/questions</t>
+          <t>/api/questions/{qid}</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -7813,7 +8008,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>create_question</t>
+          <t>get_question</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
@@ -7823,7 +8018,7 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>test_clo_lifecycle_cancel_question_and_template, test_new_course_setup_flow, test_question_bank_two_way_sync, test_question_crud</t>
+          <t>test_bulk_import_then_tag, test_clo_lifecycle_cancel_question_and_template, test_question_bank_two_way_sync, test_question_edit_rules, test_tagging_locks_used_questions</t>
         </is>
       </c>
     </row>
@@ -7833,12 +8028,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>/api/questions/{qid}</t>
+          <t>/api/questions</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -7848,7 +8043,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>update_question</t>
+          <t>create_question</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -7858,7 +8053,7 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>test_question_crud</t>
+          <t>test_clo_lifecycle_cancel_question_and_template, test_new_course_setup_flow, test_question_bank_two_way_sync, test_question_crud</t>
         </is>
       </c>
     </row>
@@ -7868,12 +8063,12 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>/api/questions/{qid}/cancel</t>
+          <t>/api/questions/{qid}</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -7883,7 +8078,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>cancel_question</t>
+          <t>update_question</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
@@ -7893,7 +8088,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>test_clo_lifecycle_cancel_question_and_template</t>
+          <t>test_question_crud</t>
         </is>
       </c>
     </row>
@@ -7903,12 +8098,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>/api/questions/{qid}</t>
+          <t>/api/questions/{qid}/cancel</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -7918,7 +8113,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>delete_question</t>
+          <t>cancel_question</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
@@ -7928,7 +8123,7 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>test_bulk_import_then_tag, test_clo_lifecycle_cancel_question_and_template, test_question_crud</t>
+          <t>test_clo_lifecycle_cancel_question_and_template</t>
         </is>
       </c>
     </row>
@@ -7938,22 +8133,22 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{course_id}/exams</t>
+          <t>/api/questions/{qid}</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>UC-02 Đề thi</t>
+          <t>UC-01 Ngân hàng câu hỏi</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Đề của môn (tạo ở trang môn học, chưa gắn lớp) kèm các lớp đã giao; và các lớp HP của người dùng để giao đề.</t>
+          <t>delete_question</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
@@ -7963,7 +8158,7 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>test_course_exam_create_and_blocked_actions</t>
+          <t>test_bulk_import_then_tag, test_clo_lifecycle_cancel_question_and_template, test_question_crud</t>
         </is>
       </c>
     </row>
@@ -7978,7 +8173,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/exams</t>
+          <t>/api/courses/{course_id}/exams</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -7988,7 +8183,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>list_exams</t>
+          <t>Đề của môn (tạo ở trang môn học, chưa gắn lớp) kèm các lớp đã giao; và các lớp HP của người dùng để giao đề.</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
@@ -7998,7 +8193,7 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>test_profile_access, test_section_stats, test_student_profile, test_timing_report_flags_planted_students</t>
+          <t>test_course_exam_create_and_blocked_actions</t>
         </is>
       </c>
     </row>
@@ -8013,7 +8208,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/exam-blueprint/pool</t>
+          <t>/api/class-sections/{cs_id}/exams</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -8023,7 +8218,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Số câu sẵn có theo từng ô ma trận (chương × mức Bloom) và theo CLO – để GV lập ma trận đề.</t>
+          <t>list_exams</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
@@ -8033,7 +8228,7 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>test_blueprint_api</t>
+          <t>test_profile_access, test_section_stats, test_student_profile, test_timing_report_flags_planted_students</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8243,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{course_id}/exam-blueprint/pool</t>
+          <t>/api/class-sections/{cs_id}/exam-blueprint/pool</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -8058,7 +8253,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Như trên, cho đề của môn (tạo ở trang môn học).</t>
+          <t>Số câu sẵn có theo từng ô ma trận (chương × mức Bloom) và theo CLO – để GV lập ma trận đề.</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
@@ -8068,7 +8263,7 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>test_course_exam_create_and_blocked_actions</t>
+          <t>test_blueprint_api</t>
         </is>
       </c>
     </row>
@@ -8078,12 +8273,12 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/exam-blueprint</t>
+          <t>/api/courses/{course_id}/exam-blueprint/pool</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -8093,7 +8288,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Sinh đề theo ma trận: trả về danh sách câu + điểm, ma trận mục tiêu/đạt được, độ phủ CLO, lỗi thiếu câu và cảnh báo.</t>
+          <t>Như trên, cho đề của môn (tạo ở trang môn học).</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
@@ -8103,7 +8298,7 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>test_blueprint_api</t>
+          <t>test_course_exam_create_and_blocked_actions</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8313,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{course_id}/exam-blueprint</t>
+          <t>/api/class-sections/{cs_id}/exam-blueprint</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -8128,7 +8323,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Như trên, cho đề của môn (tạo ở trang môn học).</t>
+          <t>Sinh đề theo ma trận: trả về danh sách câu + điểm, ma trận mục tiêu/đạt được, độ phủ CLO, lỗi thiếu câu và cảnh báo.</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
@@ -8138,7 +8333,7 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>test_course_exam_create_and_blocked_actions</t>
+          <t>test_blueprint_api</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8348,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>/api/exams</t>
+          <t>/api/courses/{course_id}/exam-blueprint</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -8163,7 +8358,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Bài KT của một lớp HP, hoặc đề của môn (course_id) – giao cho các lớp HP khi xuất (POST /exams/{id}/copy).</t>
+          <t>Như trên, cho đề của môn (tạo ở trang môn học).</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
@@ -8173,7 +8368,7 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>test_blueprint_api, test_bm6c_per_exam, test_bulk_import_then_tag, test_copy_exam_manual_items_and_paper_versions, test_course_exam_create_and_blocked_actions, test_course_exam_deploy_to_sections</t>
+          <t>test_course_exam_create_and_blocked_actions</t>
         </is>
       </c>
     </row>
@@ -8183,12 +8378,12 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}</t>
+          <t>/api/exams</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -8198,7 +8393,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>get_exam</t>
+          <t>Bài KT của một lớp HP, hoặc đề của môn (course_id) – giao cho các lớp HP khi xuất (POST /exams/{id}/copy).</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
@@ -8208,7 +8403,7 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>test_course_exam_create_and_blocked_actions, test_course_exam_deploy_to_sections, test_course_manual_exam_deploy_and_grade, test_exam_online_xml, test_manual_exam_grid_excel_and_analysis, test_moodle_web_service_flows</t>
+          <t>test_blueprint_api, test_bm6c_per_exam, test_bulk_import_then_tag, test_copy_exam_manual_items_and_paper_versions, test_course_exam_create_and_blocked_actions, test_course_exam_deploy_to_sections</t>
         </is>
       </c>
     </row>
@@ -8218,7 +8413,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -8233,7 +8428,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Xóa bài KT chưa có kết quả. Xóa đề của môn không ảnh hưởng các bài đã giao cho lớp.</t>
+          <t>get_exam</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
@@ -8243,7 +8438,7 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>test_blueprint_api, test_bulk_import_then_tag, test_course_exam_deploy_to_sections, test_course_manual_exam_deploy_and_grade, test_exam_online_xml, test_link_quiz_must_belong_to_teacher_course</t>
+          <t>test_course_exam_create_and_blocked_actions, test_course_exam_deploy_to_sections, test_course_manual_exam_deploy_and_grade, test_exam_online_xml, test_manual_exam_grid_excel_and_analysis, test_moodle_web_service_flows</t>
         </is>
       </c>
     </row>
@@ -8253,12 +8448,12 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle-xml</t>
+          <t>/api/exams/{exam_id}</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -8268,7 +8463,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>moodle_xml</t>
+          <t>Xóa bài KT chưa có kết quả. Xóa đề của môn không ảnh hưởng các bài đã giao cho lớp.</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
@@ -8278,7 +8473,7 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>test_course_exam_create_and_blocked_actions, test_exam_online_xml</t>
+          <t>test_blueprint_api, test_bulk_import_then_tag, test_course_exam_deploy_to_sections, test_course_manual_exam_deploy_and_grade, test_exam_online_xml, test_link_quiz_must_belong_to_teacher_course</t>
         </is>
       </c>
     </row>
@@ -8288,12 +8483,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/link-quiz</t>
+          <t>/api/exams/{exam_id}/moodle-xml</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -8303,7 +8498,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>link_quiz</t>
+          <t>moodle_xml</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
@@ -8313,7 +8508,7 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>test_link_quiz_must_belong_to_teacher_course</t>
+          <t>test_course_exam_create_and_blocked_actions, test_exam_online_xml</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8523,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/publish</t>
+          <t>/api/exams/{exam_id}/link-quiz</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -8338,7 +8533,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>publish</t>
+          <t>link_quiz</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
@@ -8348,7 +8543,7 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>test_moodle_web_service_flows</t>
+          <t>test_link_quiz_must_belong_to_teacher_course</t>
         </is>
       </c>
     </row>
@@ -8358,12 +8553,12 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/copy</t>
+          <t>/api/exams/{exam_id}/publish</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -8373,7 +8568,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Giao đề cho lớp HP: đề của môn (tạo ở trang môn học) được giao khi xuất cho các lớp GV chọn; bài của một lớp được</t>
+          <t>publish</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
@@ -8383,7 +8578,7 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>test_copy_exam_manual_items_and_paper_versions, test_course_exam_deploy_to_sections, test_course_manual_exam_deploy_and_grade</t>
+          <t>test_moodle_web_service_flows</t>
         </is>
       </c>
     </row>
@@ -8398,17 +8593,17 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/manual-exams</t>
+          <t>/api/exams/{exam_id}/copy</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Nhập điểm thủ công &amp; gộp bài KT</t>
+          <t>UC-02 Đề thi</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>create_manual_exam</t>
+          <t>Giao đề cho lớp HP: đề của môn (tạo ở trang môn học) được giao khi xuất cho các lớp GV chọn; bài của một lớp được</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
@@ -8418,7 +8613,7 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>test_copy_exam_manual_items_and_paper_versions, test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_copy_exam_manual_items_and_paper_versions, test_course_exam_deploy_to_sections, test_course_manual_exam_deploy_and_grade</t>
         </is>
       </c>
     </row>
@@ -8433,7 +8628,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{course_id}/manual-exams</t>
+          <t>/api/class-sections/{cs_id}/manual-exams</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -8443,7 +8638,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Đề nhập điểm của môn (tạo ở trang môn học): khai báo câu/ý gắn CLO một lần, giao cho các lớp HP để nhập điểm.</t>
+          <t>create_manual_exam</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
@@ -8453,7 +8648,7 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>test_course_manual_exam_deploy_and_grade</t>
+          <t>test_copy_exam_manual_items_and_paper_versions, test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
     </row>
@@ -8463,12 +8658,12 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/manual-items</t>
+          <t>/api/courses/{course_id}/manual-exams</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -8478,7 +8673,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>replace_items</t>
+          <t>Đề nhập điểm của môn (tạo ở trang môn học): khai báo câu/ý gắn CLO một lần, giao cho các lớp HP để nhập điểm.</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
@@ -8488,7 +8683,7 @@
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>test_copy_exam_manual_items_and_paper_versions</t>
+          <t>test_course_manual_exam_deploy_and_grade</t>
         </is>
       </c>
     </row>
@@ -8498,12 +8693,12 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/grades</t>
+          <t>/api/exams/{exam_id}/manual-items</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -8513,7 +8708,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>get_grades</t>
+          <t>replace_items</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
@@ -8523,7 +8718,7 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>test_copy_exam_manual_items_and_paper_versions, test_course_manual_exam_deploy_and_grade, test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_copy_exam_manual_items_and_paper_versions</t>
         </is>
       </c>
     </row>
@@ -8533,7 +8728,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -8548,7 +8743,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>put_grades</t>
+          <t>get_grades</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
@@ -8558,7 +8753,7 @@
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>test_course_manual_exam_deploy_and_grade, test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_copy_exam_manual_items_and_paper_versions, test_course_manual_exam_deploy_and_grade, test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
     </row>
@@ -8568,12 +8763,12 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/grades.xlsx</t>
+          <t>/api/exams/{exam_id}/grades</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -8583,7 +8778,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>grades_template</t>
+          <t>put_grades</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
@@ -8593,7 +8788,7 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_course_manual_exam_deploy_and_grade, test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
     </row>
@@ -8603,12 +8798,12 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/grades/import</t>
+          <t>/api/exams/{exam_id}/grades.xlsx</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -8618,7 +8813,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Nhập điểm từ Excel vào bài đã có: khớp cột theo mã câu (bảng điểm mẫu), theo tên câu/ý, hoặc theo thứ tự cột.</t>
+          <t>grades_template</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -8643,7 +8838,7 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/manual-exams/import</t>
+          <t>/api/exams/{exam_id}/grades/import</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -8653,7 +8848,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Tạo bài nhập điểm từ một file Excel bất kỳ (bài làm ngoài hệ thống) và nhập luôn điểm.</t>
+          <t>Nhập điểm từ Excel vào bài đã có: khớp cột theo mã câu (bảng điểm mẫu), theo tên câu/ý, hoặc theo thứ tự cột.</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
@@ -8663,7 +8858,7 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>test_create_exam_from_any_excel</t>
+          <t>test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
     </row>
@@ -8673,12 +8868,12 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/evidence</t>
+          <t>/api/class-sections/{cs_id}/manual-exams/import</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -8688,7 +8883,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Bài có được gộp vào kết quả CLO của lớp (BM6, PI, PLO) hay không.</t>
+          <t>Tạo bài nhập điểm từ một file Excel bất kỳ (bài làm ngoài hệ thống) và nhập luôn điểm.</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
@@ -8698,7 +8893,7 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>test_combine_exams_and_evidence_flag</t>
+          <t>test_create_exam_from_any_excel</t>
         </is>
       </c>
     </row>
@@ -8708,12 +8903,12 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{course_id}/analyzed-exams</t>
+          <t>/api/exams/{exam_id}/evidence</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -8723,7 +8918,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Các bài đã phân tích của môn trong các lớp HP người dùng phụ trách – để chọn bài gộp.</t>
+          <t>Bài có được gộp vào kết quả CLO của lớp (BM6, PI, PLO) hay không.</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
@@ -8743,12 +8938,12 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>/api/combined-analysis</t>
+          <t>/api/courses/{course_id}/analyzed-exams</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -8758,7 +8953,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>combined</t>
+          <t>Các bài đã phân tích của môn trong các lớp HP người dùng phụ trách – để chọn bài gộp.</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
@@ -8778,12 +8973,12 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>/api/combined-analysis.xlsx</t>
+          <t>/api/combined-analysis</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -8793,7 +8988,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>combined_xlsx</t>
+          <t>combined</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
@@ -8818,17 +9013,17 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/remedial</t>
+          <t>/api/combined-analysis.xlsx</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập theo câu trả lời sai (phụ đạo)</t>
+          <t>Nhập điểm thủ công &amp; gộp bài KT</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Bảng tổng hợp: mỗi SV sai bao nhiêu câu (trên các bài chọn), CLO chưa đạt; mỗi câu bao nhiêu SV sai.</t>
+          <t>combined_xlsx</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
@@ -8838,7 +9033,7 @@
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>test_on_tap_co_goi_y_doc, test_overview_theo_chuong_va_loc_chuong, test_remedial_flow</t>
+          <t>test_combine_exams_and_evidence_flag</t>
         </is>
       </c>
     </row>
@@ -8853,7 +9048,7 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/remedial-exams</t>
+          <t>/api/class-sections/{cs_id}/remedial</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -8863,7 +9058,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Các bài phụ đạo của lớp và tiến bộ của từng SV được giao (góp ý F5):</t>
+          <t>Bảng tổng hợp: mỗi SV sai bao nhiêu câu (trên các bài chọn), CLO chưa đạt; mỗi câu bao nhiêu SV sai.</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
@@ -8873,7 +9068,7 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>test_progress_after_attempt, test_progress_before_attempt</t>
+          <t>test_on_tap_co_goi_y_doc, test_overview_theo_chuong_va_loc_chuong, test_remedial_flow</t>
         </is>
       </c>
     </row>
@@ -8888,7 +9083,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/remedial/students/{student_id}</t>
+          <t>/api/class-sections/{cs_id}/remedial-exams</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -8898,7 +9093,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Danh sách câu SV trả lời sai/bỏ trống (kèm phương án đã chọn, đáp án đúng, chương).</t>
+          <t>Các bài phụ đạo của lớp và tiến bộ của từng SV được giao (góp ý F5):</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
@@ -8908,7 +9103,7 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>test_remedial_flow</t>
+          <t>test_progress_after_attempt, test_progress_before_attempt</t>
         </is>
       </c>
     </row>
@@ -8918,12 +9113,12 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/remedial-exams</t>
+          <t>/api/class-sections/{cs_id}/remedial/students/{student_id}</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -8933,7 +9128,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Tạo bài KT phụ đạo: câu trắc nghiệm các SV đã chọn làm sai (+ câu tương tự cùng chương chưa gặp).</t>
+          <t>Danh sách câu SV trả lời sai/bỏ trống (kèm phương án đã chọn, đáp án đúng, chương).</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
@@ -8943,7 +9138,7 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>test_overview_theo_chuong_va_loc_chuong, test_progress_before_attempt, test_remedial_flow</t>
+          <t>test_remedial_flow</t>
         </is>
       </c>
     </row>
@@ -8953,22 +9148,22 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper</t>
+          <t>/api/class-sections/{cs_id}/remedial-exams</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Đề thi giấy &amp; chấm phiếu trên hệ thống</t>
+          <t>Ôn tập theo câu trả lời sai (phụ đạo)</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Trạng thái đề giấy: chế độ (hệ thống tự in &amp; chấm / Moodle Offline Quiz), các mã đề với đầy đủ câu, đáp án; tùy chọn in.</t>
+          <t>Tạo bài KT phụ đạo: câu trắc nghiệm các SV đã chọn làm sai (+ câu tương tự cùng chương chưa gặp).</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
@@ -8978,7 +9173,7 @@
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>test_copy_exam_manual_items_and_paper_versions, test_paper_exam_two_modes, test_system_paper_exam_end_to_end</t>
+          <t>test_overview_theo_chuong_va_loc_chuong, test_progress_before_attempt, test_remedial_flow</t>
         </is>
       </c>
     </row>
@@ -8988,12 +9183,12 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper/versions</t>
+          <t>/api/exams/{exam_id}/paper</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -9003,7 +9198,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>make_versions</t>
+          <t>Trạng thái đề giấy: chế độ (hệ thống tự in &amp; chấm / Moodle Offline Quiz), các mã đề với đầy đủ câu, đáp án; tùy chọn in.</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
@@ -9013,7 +9208,7 @@
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>test_copy_exam_manual_items_and_paper_versions, test_course_exam_deploy_to_sections, test_system_paper_exam_end_to_end</t>
+          <t>test_copy_exam_manual_items_and_paper_versions, test_paper_exam_two_modes, test_system_paper_exam_end_to_end</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9218,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -9038,7 +9233,7 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Bỏ các mã đề hệ thống đã sinh (khi chưa chấm phiếu) – để sinh lại hoặc chuyển sang Moodle Offline Quiz.</t>
+          <t>make_versions</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
@@ -9048,7 +9243,7 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>test_copy_exam_manual_items_and_paper_versions, test_course_exam_deploy_to_sections</t>
+          <t>test_copy_exam_manual_items_and_paper_versions, test_course_exam_deploy_to_sections, test_system_paper_exam_end_to_end</t>
         </is>
       </c>
     </row>
@@ -9058,12 +9253,12 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper/settings</t>
+          <t>/api/exams/{exam_id}/paper/versions</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -9073,7 +9268,7 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>save_settings</t>
+          <t>Bỏ các mã đề hệ thống đã sinh (khi chưa chấm phiếu) – để sinh lại hoặc chuyển sang Moodle Offline Quiz.</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
@@ -9083,7 +9278,7 @@
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>test_system_paper_exam_end_to_end</t>
+          <t>test_copy_exam_manual_items_and_paper_versions, test_course_exam_deploy_to_sections</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9288,12 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper/exam.{fmt}</t>
+          <t>/api/exams/{exam_id}/paper/settings</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -9108,7 +9303,7 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>exam_file</t>
+          <t>save_settings</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
@@ -9133,7 +9328,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper/answer-sheet.{fmt}</t>
+          <t>/api/exams/{exam_id}/paper/exam.{fmt}</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -9143,7 +9338,7 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Phiếu trả lời: png = ảnh xem trước (theo tham số đang chỉnh); pdf = tệp in (theo cài đặt đã lưu).</t>
+          <t>exam_file</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
@@ -9168,7 +9363,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper/answer-key.pdf</t>
+          <t>/api/exams/{exam_id}/paper/answer-sheet.{fmt}</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -9178,7 +9373,7 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>answer_key</t>
+          <t>Phiếu trả lời: png = ảnh xem trước (theo tham số đang chỉnh); pdf = tệp in (theo cài đặt đã lưu).</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
@@ -9203,7 +9398,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/paper/package.zip</t>
+          <t>/api/exams/{exam_id}/paper/answer-key.pdf</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -9213,7 +9408,7 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Trọn bộ để in: đề từng mã đề (PDF + Word), phiếu trả lời, đáp án.</t>
+          <t>answer_key</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
@@ -9233,12 +9428,12 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/scan</t>
+          <t>/api/exams/{exam_id}/paper/package.zip</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -9248,7 +9443,7 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Nhận diện phiếu từ ảnh quét / ảnh chụp (JPG, PNG) hoặc PDF nhiều trang. Chưa ghi CSDL – GV soát rồi lưu (scan/commit).</t>
+          <t>Trọn bộ để in: đề từng mã đề (PDF + Word), phiếu trả lời, đáp án.</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
@@ -9273,7 +9468,7 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/scan/commit</t>
+          <t>/api/exams/{exam_id}/scan</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -9283,7 +9478,7 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Lưu kết quả phiếu đã soát: Reverse Shuffle nhãn in trên mã đề -&gt; phương án gốc, chấm và phân tích.</t>
+          <t>Nhận diện phiếu từ ảnh quét / ảnh chụp (JPG, PNG) hoặc PDF nhiều trang. Chưa ghi CSDL – GV soát rồi lưu (scan/commit).</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -9303,22 +9498,22 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{course_id}/moodle-sync/targets</t>
+          <t>/api/exams/{exam_id}/scan/commit</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Đồng bộ ngân hàng câu hỏi với Moodle</t>
+          <t>Đề thi giấy &amp; chấm phiếu trên hệ thống</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>targets</t>
+          <t>Lưu kết quả phiếu đã soát: Reverse Shuffle nhãn in trên mã đề -&gt; phương án gốc, chấm và phân tích.</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
@@ -9328,7 +9523,7 @@
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>test_question_bank_two_way_sync</t>
+          <t>test_system_paper_exam_end_to_end</t>
         </is>
       </c>
     </row>
@@ -9343,7 +9538,7 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{course_id}/moodle-sync</t>
+          <t>/api/courses/{course_id}/moodle-sync/targets</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -9353,7 +9548,7 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>compare</t>
+          <t>targets</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
@@ -9373,7 +9568,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -9388,7 +9583,7 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>apply</t>
+          <t>compare</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
@@ -9413,17 +9608,17 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/sync</t>
+          <t>/api/courses/{course_id}/moodle-sync</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>UC-03 Đồng bộ &amp; phân tích</t>
+          <t>Đồng bộ ngân hàng câu hỏi với Moodle</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>sync_moodle</t>
+          <t>apply</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
@@ -9433,7 +9628,7 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>test_paper_resync_is_idempotent, test_resync_is_idempotent, test_sync_stops_when_question_edited_on_moodle, test_sync_warns_average_grade_method</t>
+          <t>test_question_bank_two_way_sync</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9643,7 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/analyze</t>
+          <t>/api/exams/{exam_id}/sync</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -9458,7 +9653,7 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>analyze</t>
+          <t>sync_moodle</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
@@ -9468,7 +9663,7 @@
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>test_sync_analyze_runs_and_bridge</t>
+          <t>test_paper_resync_is_idempotent, test_resync_is_idempotent, test_sync_stops_when_question_edited_on_moodle, test_sync_warns_average_grade_method</t>
         </is>
       </c>
     </row>
@@ -9478,12 +9673,12 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/sync-runs</t>
+          <t>/api/exams/{exam_id}/analyze</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -9493,7 +9688,7 @@
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>sync_runs</t>
+          <t>analyze</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
@@ -9518,7 +9713,7 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>/api/system/moodle-status</t>
+          <t>/api/exams/{exam_id}/sync-runs</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -9528,7 +9723,7 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>moodle_status</t>
+          <t>sync_runs</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
@@ -9548,12 +9743,12 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>/api/system/install-bridge</t>
+          <t>/api/system/moodle-status</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -9563,7 +9758,7 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>install_bridge</t>
+          <t>moodle_status</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
@@ -9583,22 +9778,22 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/moodle-course</t>
+          <t>/api/system/install-bridge</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Tích hợp Moodle (Web Service)</t>
+          <t>UC-03 Đồng bộ &amp; phân tích</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>set_moodle_course</t>
+          <t>install_bridge</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
@@ -9608,7 +9803,7 @@
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>test_link_section_with_moodle_both_ways</t>
+          <t>test_sync_analyze_runs_and_bridge</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9813,12 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/create-quiz</t>
+          <t>/api/class-sections/{cs_id}/moodle-course</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -9633,7 +9828,7 @@
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>create_quiz</t>
+          <t>set_moodle_course</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
@@ -9643,7 +9838,7 @@
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>test_moodle_web_service_flows</t>
+          <t>test_link_section_with_moodle_both_ways</t>
         </is>
       </c>
     </row>
@@ -9658,7 +9853,7 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/restrict</t>
+          <t>/api/exams/{exam_id}/moodle/create-quiz</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -9668,17 +9863,17 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Bài phụ đạo đã có Quiz: (đồng bộ lại) nhóm Moodle gồm đúng các SV được giao và điều kiện truy cập của Quiz.</t>
-        </is>
-      </c>
-      <c r="F109" s="6" t="inlineStr">
-        <is>
-          <t>Chỉ lỗi</t>
+          <t>create_quiz</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>test_restrict_requires_moodle_accounts</t>
+          <t>test_moodle_web_service_flows</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9888,7 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/create-offlinequiz</t>
+          <t>/api/exams/{exam_id}/moodle/restrict</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -9703,17 +9898,17 @@
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>create_offlinequiz</t>
-        </is>
-      </c>
-      <c r="F110" s="5" t="inlineStr">
-        <is>
-          <t>Có</t>
+          <t>Bài phụ đạo đã có Quiz: (đồng bộ lại) nhóm Moodle gồm đúng các SV được giao và điều kiện truy cập của Quiz.</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>Chỉ lỗi</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>test_moodle_web_service_flows</t>
+          <t>test_restrict_requires_moodle_accounts</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9918,12 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/offlinequiz</t>
+          <t>/api/exams/{exam_id}/moodle/create-offlinequiz</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -9738,7 +9933,7 @@
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>offlinequiz_status</t>
+          <t>create_offlinequiz</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
@@ -9758,12 +9953,12 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/process-scans</t>
+          <t>/api/exams/{exam_id}/moodle/offlinequiz</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -9773,7 +9968,7 @@
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>process_scans</t>
+          <t>offlinequiz_status</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
@@ -9793,12 +9988,12 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/offlinequiz/files/{filename}</t>
+          <t>/api/exams/{exam_id}/moodle/process-scans</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -9808,7 +10003,7 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>offlinequiz_file</t>
+          <t>process_scans</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
@@ -9833,7 +10028,7 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/offlinequiz/files.zip</t>
+          <t>/api/exams/{exam_id}/moodle/offlinequiz/files/{filename}</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -9843,7 +10038,7 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>offlinequiz_zip</t>
+          <t>offlinequiz_file</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
@@ -9868,7 +10063,7 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/results-preview</t>
+          <t>/api/exams/{exam_id}/moodle/offlinequiz/files.zip</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -9878,7 +10073,7 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>results_preview</t>
+          <t>offlinequiz_zip</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
@@ -9888,7 +10083,7 @@
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>test_goi_y_doc_cho_sv_lam_sai, test_results_for_moodle</t>
+          <t>test_moodle_web_service_flows</t>
         </is>
       </c>
     </row>
@@ -9898,12 +10093,12 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/moodle/push-results</t>
+          <t>/api/exams/{exam_id}/moodle/results-preview</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -9913,7 +10108,7 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>push_results</t>
+          <t>results_preview</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
@@ -9923,7 +10118,7 @@
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>test_moodle_web_service_flows</t>
+          <t>test_goi_y_doc_cho_sv_lam_sai, test_results_for_moodle</t>
         </is>
       </c>
     </row>
@@ -9933,12 +10128,12 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>/api/system/lms-status</t>
+          <t>/api/exams/{exam_id}/moodle/push-results</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -9948,7 +10143,7 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>lms_status</t>
+          <t>push_results</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
@@ -9973,17 +10168,17 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/overview</t>
+          <t>/api/system/lms-status</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>UC-04 Thống kê lớp học</t>
+          <t>Tích hợp Moodle (Web Service)</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>overview</t>
+          <t>lms_status</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
@@ -9993,7 +10188,7 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_moodle_web_service_flows</t>
         </is>
       </c>
     </row>
@@ -10008,7 +10203,7 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/item-stats</t>
+          <t>/api/exams/{exam_id}/overview</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -10018,7 +10213,7 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>item_stats</t>
+          <t>overview</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
@@ -10028,7 +10223,7 @@
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>test_item_stats_flags_trap_question, test_manual_exam_grid_excel_and_analysis, test_timing_thresholds_timeline_and_export</t>
+          <t>test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
     </row>
@@ -10043,7 +10238,7 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/students</t>
+          <t>/api/exams/{exam_id}/item-stats</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -10053,7 +10248,7 @@
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>exam_students</t>
+          <t>item_stats</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
@@ -10063,7 +10258,7 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>test_manual_exam_grid_excel_and_analysis</t>
+          <t>test_item_stats_flags_trap_question, test_manual_exam_grid_excel_and_analysis, test_timing_thresholds_timeline_and_export</t>
         </is>
       </c>
     </row>
@@ -10078,7 +10273,7 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/clo-summary</t>
+          <t>/api/exams/{exam_id}/students</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -10088,7 +10283,7 @@
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>Tổng hợp CẢ LỚP theo từng CLO của bài KT: số SV đạt / số SV được đánh giá (không trả kết quả riêng của từng SV).</t>
+          <t>exam_students</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
@@ -10113,7 +10308,7 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/clo-results</t>
+          <t>/api/exams/{exam_id}/clo-summary</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -10123,7 +10318,7 @@
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>BM6b – kết quả tổng hợp của từng CĐR môn học (E1: rỗng nếu chưa phân tích).</t>
+          <t>Tổng hợp CẢ LỚP theo từng CLO của bài KT: số SV đạt / số SV được đánh giá (không trả kết quả riêng của từng SV).</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
@@ -10133,7 +10328,7 @@
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>test_clo_results_bm6b</t>
+          <t>test_manual_exam_grid_excel_and_analysis</t>
         </is>
       </c>
     </row>
@@ -10148,7 +10343,7 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/clo-results/{clo_id}/evidence</t>
+          <t>/api/class-sections/{cs_id}/clo-results</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -10158,7 +10353,7 @@
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>BM6c/6d – bảng minh chứng: điểm từng SV trên các câu thuộc CLO, theo từng bài KT; câu hỏi có DI thấp.</t>
+          <t>BM6b – kết quả tổng hợp của từng CĐR môn học (E1: rỗng nếu chưa phân tích).</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
@@ -10168,7 +10363,7 @@
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>test_sync_analyze_runs_and_bridge</t>
+          <t>test_clo_results_bm6b</t>
         </is>
       </c>
     </row>
@@ -10178,12 +10373,12 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/clo-results/{clo_id}</t>
+          <t>/api/class-sections/{cs_id}/clo-results/{clo_id}/evidence</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -10193,7 +10388,7 @@
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>clo_narrative</t>
+          <t>BM6c/6d – bảng minh chứng: điểm từng SV trên các câu thuộc CLO, theo từng bài KT; câu hỏi có DI thấp.</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
@@ -10203,7 +10398,7 @@
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>test_clo_narrative</t>
+          <t>test_sync_analyze_runs_and_bridge</t>
         </is>
       </c>
     </row>
@@ -10213,12 +10408,12 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/timing</t>
+          <t>/api/class-sections/{cs_id}/clo-results/{clo_id}</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -10228,7 +10423,7 @@
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>Thời gian làm bài của từng SV và các dấu hiệu bất thường (làm quá nhanh/chọn đại, bỏ dở, treo máy chờ hết giờ…).</t>
+          <t>clo_narrative</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
@@ -10238,7 +10433,7 @@
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>test_timing_report_flags_planted_students, test_timing_thresholds_timeline_and_export</t>
+          <t>test_clo_narrative</t>
         </is>
       </c>
     </row>
@@ -10253,7 +10448,7 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/timing/students/{student_id}</t>
+          <t>/api/exams/{exam_id}/timing</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -10263,7 +10458,7 @@
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>Diễn biến làm bài của một SV: thời điểm chọn, thời gian trả lời, số lần đổi đáp án từng câu.</t>
+          <t>Thời gian làm bài của từng SV và các dấu hiệu bất thường (làm quá nhanh/chọn đại, bỏ dở, treo máy chờ hết giờ…).</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
@@ -10273,7 +10468,7 @@
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>test_timing_thresholds_timeline_and_export</t>
+          <t>test_timing_report_flags_planted_students, test_timing_thresholds_timeline_and_export</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10483,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{exam_id}/timing.xlsx</t>
+          <t>/api/exams/{exam_id}/timing/students/{student_id}</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -10298,7 +10493,7 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>Xuất Excel danh sách cảnh báo và thời gian trả lời từng câu.</t>
+          <t>Diễn biến làm bài của một SV: thời điểm chọn, thời gian trả lời, số lần đổi đáp án từng câu.</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
@@ -10323,17 +10518,17 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/students/{student_id}/profile</t>
+          <t>/api/exams/{exam_id}/timing.xlsx</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>UC-04 Hồ sơ SV &amp; thống kê lớp</t>
+          <t>UC-04 Thống kê lớp học</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>student_profile</t>
+          <t>Xuất Excel danh sách cảnh báo và thời gian trả lời từng câu.</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
@@ -10343,7 +10538,7 @@
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>test_student_profile, test_timing_thresholds_timeline_and_export</t>
+          <t>test_timing_thresholds_timeline_and_export</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10553,7 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>/api/class-sections/{cs_id}/stats</t>
+          <t>/api/class-sections/{cs_id}/students/{student_id}/profile</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -10368,7 +10563,7 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>section_stats</t>
+          <t>student_profile</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
@@ -10378,7 +10573,7 @@
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>test_section_stats, test_student_profile</t>
+          <t>test_student_profile, test_timing_thresholds_timeline_and_export</t>
         </is>
       </c>
     </row>
@@ -10393,17 +10588,17 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/class-sections/{cs_id}/bm6.xlsx</t>
+          <t>/api/class-sections/{cs_id}/stats</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>UC-07 Báo cáo đo lường CĐR</t>
+          <t>UC-04 Hồ sơ SV &amp; thống kê lớp</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>bm6</t>
+          <t>section_stats</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
@@ -10413,7 +10608,7 @@
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>test_bm6_evidence_follows_plan_and_matches_bm6b, test_bm6_workbook, test_http_errors_and_inputs</t>
+          <t>test_section_stats, test_student_profile</t>
         </is>
       </c>
     </row>
@@ -10428,7 +10623,7 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/exams/{exam_id}/bm6c.xlsx</t>
+          <t>/api/reports/class-sections/{cs_id}/bm6.xlsx</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -10438,7 +10633,7 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>BM6c riêng cho một bài kiểm tra – minh chứng từng CLO bài KT đo (kèm MSSV, họ tên).</t>
+          <t>bm6</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
@@ -10448,7 +10643,7 @@
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>test_bm6c_per_exam</t>
+          <t>test_bm6_evidence_follows_plan_and_matches_bm6b, test_bm6_workbook, test_http_errors_and_inputs</t>
         </is>
       </c>
     </row>
@@ -10463,7 +10658,7 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/programs/{pid}/bm3.xlsx</t>
+          <t>/api/reports/exams/{exam_id}/bm6c.xlsx</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -10473,7 +10668,7 @@
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>bm3</t>
+          <t>BM6c riêng cho một bài kiểm tra – minh chứng từng CLO bài KT đo (kèm MSSV, họ tên).</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
@@ -10483,7 +10678,7 @@
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>test_bm3_workbook</t>
+          <t>test_bm6c_per_exam</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10693,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/programs/{pid}/bm2.docx</t>
+          <t>/api/reports/programs/{pid}/bm3.xlsx</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -10508,7 +10703,7 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>BM2 dạng Word như biểu mẫu gốc: BM2a (kế hoạch) + BM2b (báo cáo tổng kết).</t>
+          <t>bm3</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
@@ -10518,7 +10713,7 @@
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>test_bm2_docx</t>
+          <t>test_bm3_workbook</t>
         </is>
       </c>
     </row>
@@ -10533,7 +10728,7 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/semesters/{sem_id}/assignments.xlsx</t>
+          <t>/api/reports/programs/{pid}/bm2.docx</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -10543,7 +10738,7 @@
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>Bảng "Phân công đánh giá PIs" của một học kỳ.</t>
+          <t>BM2 dạng Word như biểu mẫu gốc: BM2a (kế hoạch) + BM2b (báo cáo tổng kết).</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
@@ -10553,7 +10748,7 @@
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>test_assignments_xlsx</t>
+          <t>test_bm2_docx</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10763,7 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/programs/{pid}/plo-summary</t>
+          <t>/api/reports/semesters/{sem_id}/assignments.xlsx</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -10578,7 +10773,7 @@
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>plo_summary</t>
+          <t>Bảng "Phân công đánh giá PIs" của một học kỳ.</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
@@ -10588,7 +10783,7 @@
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>test_plo_summary_is_sum_of_pi</t>
+          <t>test_assignments_xlsx</t>
         </is>
       </c>
     </row>
@@ -10598,12 +10793,12 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/programs/{pid}/recompute</t>
+          <t>/api/reports/programs/{pid}/plo-summary</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -10613,7 +10808,7 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>recompute</t>
+          <t>plo_summary</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
@@ -10623,7 +10818,7 @@
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>test_programs_plo_and_pi_plans</t>
+          <t>test_plo_summary_is_sum_of_pi</t>
         </is>
       </c>
     </row>
@@ -10633,12 +10828,12 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>/api/reports/plo-results/{plo_id}/{academic_year}</t>
+          <t>/api/reports/programs/{pid}/recompute</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -10648,7 +10843,7 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>plo_narrative</t>
+          <t>recompute</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
@@ -10658,7 +10853,7 @@
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>test_plo_narrative</t>
+          <t>test_programs_plo_and_pi_plans</t>
         </is>
       </c>
     </row>
@@ -10668,22 +10863,22 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{cid}/materials</t>
+          <t>/api/reports/plo-results/{plo_id}/{academic_year}</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Học liệu và gợi ý đọc (RAG)</t>
+          <t>UC-07 Báo cáo đo lường CĐR</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>list_materials</t>
+          <t>plo_narrative</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
@@ -10693,7 +10888,7 @@
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>test_day_hoc_lieu_len_moodle, test_lay_hoc_lieu_tu_moodle_ve, test_lay_ve_khong_trung_voi_tep_da_day_len, test_seed_co_hoc_lieu, test_tai_len_docx_txt_va_loi, test_xem_tep_goc_trang_va_lap_lai_chi_muc</t>
+          <t>test_plo_narrative</t>
         </is>
       </c>
     </row>
@@ -10703,7 +10898,7 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -10718,7 +10913,7 @@
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>upload_material</t>
+          <t>list_materials</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
@@ -10728,7 +10923,7 @@
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>test_day_hoc_lieu_len_moodle, test_lay_ve_khong_trung_voi_tep_da_day_len, test_tai_len_docx_txt_va_loi</t>
+          <t>test_day_hoc_lieu_len_moodle, test_lay_hoc_lieu_tu_moodle_ve, test_lay_ve_khong_trung_voi_tep_da_day_len, test_seed_co_hoc_lieu, test_tai_len_docx_txt_va_loi, test_xem_tep_goc_trang_va_lap_lai_chi_muc</t>
         </is>
       </c>
     </row>
@@ -10738,12 +10933,12 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>/api/materials/{mid}</t>
+          <t>/api/courses/{cid}/materials</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -10753,7 +10948,7 @@
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>delete_material</t>
+          <t>upload_material</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
@@ -10763,7 +10958,7 @@
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>test_chi_tim_trong_hoc_lieu_cua_dung_khoa, test_day_hoc_lieu_len_moodle, test_lay_hoc_lieu_tu_moodle_ve, test_lay_ve_khong_trung_voi_tep_da_day_len, test_tai_len_docx_txt_va_loi</t>
+          <t>test_day_hoc_lieu_len_moodle, test_lay_ve_khong_trung_voi_tep_da_day_len, test_tai_len_docx_txt_va_loi</t>
         </is>
       </c>
     </row>
@@ -10773,12 +10968,12 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>/api/materials/{mid}/reindex</t>
+          <t>/api/materials/{mid}</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -10788,7 +10983,7 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>reindex</t>
+          <t>delete_material</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
@@ -10798,7 +10993,7 @@
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>test_xem_tep_goc_trang_va_lap_lai_chi_muc</t>
+          <t>test_chi_tim_trong_hoc_lieu_cua_dung_khoa, test_day_hoc_lieu_len_moodle, test_lay_hoc_lieu_tu_moodle_ve, test_lay_ve_khong_trung_voi_tep_da_day_len, test_tai_len_docx_txt_va_loi</t>
         </is>
       </c>
     </row>
@@ -10808,12 +11003,12 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>/api/materials/{mid}/file</t>
+          <t>/api/materials/{mid}/reindex</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -10823,7 +11018,7 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>download</t>
+          <t>reindex</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
@@ -10848,7 +11043,7 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>/api/materials/{mid}/pages/{page}</t>
+          <t>/api/materials/{mid}/file</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -10858,7 +11053,7 @@
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>page_text</t>
+          <t>download</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
@@ -10883,7 +11078,7 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{cid}/materials/search</t>
+          <t>/api/materials/{mid}/pages/{page}</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -10893,7 +11088,7 @@
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>Thử truy xuất: gõ câu hỏi/thuật ngữ → trang/slide của học liệu thuộc học phần này.</t>
+          <t>page_text</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
@@ -10903,7 +11098,7 @@
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>test_cau_ngoai_pham_vi_khong_goi_y, test_chi_tim_trong_hoc_lieu_cua_dung_khoa, test_lay_hoc_lieu_tu_moodle_ve, test_tai_len_docx_txt_va_loi, test_tim_dung_slide[B\u1ea3n, test_tim_dung_slide[Hai</t>
+          <t>test_xem_tep_goc_trang_va_lap_lai_chi_muc</t>
         </is>
       </c>
     </row>
@@ -10913,12 +11108,12 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>/api/exams/{eid}/readings/rebuild</t>
+          <t>/api/courses/{cid}/materials/search</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -10928,7 +11123,7 @@
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>Tạo lại gợi ý đọc của cả bài KT từ học liệu hiện có (dùng sau khi tải thêm học liệu, không cần phân tích lại).</t>
+          <t>Thử truy xuất: gõ câu hỏi/thuật ngữ → trang/slide của học liệu thuộc học phần này.</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
@@ -10938,7 +11133,7 @@
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>test_tai_tao_goi_y_sau_khi_them_hoc_lieu</t>
+          <t>test_cau_ngoai_pham_vi_khong_goi_y, test_chi_tim_trong_hoc_lieu_cua_dung_khoa, test_lay_hoc_lieu_tu_moodle_ve, test_tai_len_docx_txt_va_loi, test_tim_dung_slide[B\u1ea3n, test_tim_dung_slide[Hai</t>
         </is>
       </c>
     </row>
@@ -10953,7 +11148,7 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>/api/courses/{cid}/materials/sync-moodle</t>
+          <t>/api/exams/{eid}/readings/rebuild</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -10963,7 +11158,7 @@
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>Lấy học liệu đã có trong khóa học Moodle (hoạt động Tệp/Thư mục: PDF, PPTX, DOCX, TXT, MD) về lập chỉ mục.</t>
+          <t>Tạo lại gợi ý đọc của cả bài KT từ học liệu hiện có (dùng sau khi tải thêm học liệu, không cần phân tích lại).</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
@@ -10973,7 +11168,7 @@
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>test_lay_hoc_lieu_tu_moodle_ve, test_lay_ve_khong_trung_voi_tep_da_day_len</t>
+          <t>test_tai_tao_goi_y_sau_khi_them_hoc_lieu</t>
         </is>
       </c>
     </row>
@@ -10988,7 +11183,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>/api/materials/{mid}/push-moodle</t>
+          <t>/api/courses/{cid}/materials/sync-moodle</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -10998,7 +11193,7 @@
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>Đẩy học liệu lên khóa học Moodle thành hoạt động Tệp để sinh viên xem ngay trên Moodle.</t>
+          <t>Lấy học liệu đã có trong khóa học Moodle (hoạt động Tệp/Thư mục: PDF, PPTX, DOCX, TXT, MD) về lập chỉ mục.</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
@@ -11008,7 +11203,7 @@
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>test_day_hoc_lieu_len_moodle, test_lay_ve_khong_trung_voi_tep_da_day_len</t>
+          <t>test_lay_hoc_lieu_tu_moodle_ve, test_lay_ve_khong_trung_voi_tep_da_day_len</t>
         </is>
       </c>
     </row>
@@ -11018,22 +11213,22 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>/api/health</t>
+          <t>/api/materials/{mid}/push-moodle</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống</t>
+          <t>Học liệu và gợi ý đọc (RAG)</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra dịch vụ</t>
+          <t>Đẩy học liệu lên khóa học Moodle thành hoạt động Tệp để sinh viên xem ngay trên Moodle.</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
@@ -11043,7 +11238,7 @@
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>test_auth_me_and_catalogs</t>
+          <t>test_day_hoc_lieu_len_moodle, test_lay_ve_khong_trung_voi_tep_da_day_len</t>
         </is>
       </c>
     </row>
@@ -11058,25 +11253,60 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
+          <t>/api/health</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>Hệ thống</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>Kiểm tra dịch vụ</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>test_auth_me_and_catalogs</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
           <t>/api/public-config</t>
         </is>
       </c>
-      <c r="D149" s="4" t="inlineStr">
+      <c r="D150" s="4" t="inlineStr">
         <is>
           <t>Hệ thống</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
+      <c r="E150" s="4" t="inlineStr">
         <is>
           <t>Cấu hình công khai cho giao diện</t>
         </is>
       </c>
-      <c r="F149" s="5" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="G149" s="4" t="inlineStr">
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="inlineStr">
         <is>
           <t>test_auth_me_and_catalogs</t>
         </is>
